--- a/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
+++ b/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V105"/>
+  <dimension ref="A1:V106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>2385</v>
+        <v>2609</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08T11:50:00</t>
+          <t>2026-09-18T14:15:00</t>
         </is>
       </c>
       <c r="J29" s="5" t="n">
@@ -2866,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>422391</v>
+        <v>403520</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>374</v>
+        <v>348</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q29" s="4" t="inlineStr">
@@ -3593,15 +3593,15 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>US.TradeMerchTotal</t>
+          <t>US.TradeMerchGR</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Total trade and share, annual</t>
+          <t>Merchandise: Total trade growth rates, annual</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Export,import,value,share,merchandise,trade</t>
+          <t>Growth rates, export, import, merchandise, trade</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -3634,19 +3634,19 @@
         <v>0</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>424083</v>
+        <v>214725</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>312</v>
+        <v>104</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>19801981</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>20242025</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
@@ -3689,15 +3689,15 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>US.TradeMerchGR</t>
+          <t>US.TradeMerchTotal</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Total trade growth rates, annual</t>
+          <t>Merchandise: Trade - Annual</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Growth rates, export, import, merchandise, trade</t>
+          <t>Export,import,value,share,merchandise,trade</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -3730,19 +3730,19 @@
         <v>0</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>214725</v>
+        <v>424083</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>104</v>
+        <v>312</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>19801981</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>20242025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q38" s="4" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade balance, annual</t>
+          <t>Merchandise: Trade balance - Annual</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -6265,20 +6265,20 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEconActivity</t>
+          <t>US.IctUseTotal</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>2114</v>
+        <v>2347</v>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 3.1) - Annual</t>
+          <t>ICT use in business: Core indicators - Annual</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Information Economy</t>
+          <t>Digital economy</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>ICT indicators, Industrial Classification, economic activity, ISIC</t>
+          <t>ICT indicators</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>2025-12-08T09:44:00</t>
+          <t>2026-09-14T09:05:00</t>
         </is>
       </c>
       <c r="J65" s="5" t="n">
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>83239</v>
+        <v>29937</v>
       </c>
       <c r="N65" s="5" t="n">
         <v>0</v>
@@ -6353,20 +6353,20 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEconActivity_Isic4</t>
+          <t>US.IctUseEconActivity</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>2250</v>
+        <v>2114</v>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 4) - Annual</t>
+          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 3.1) - Annual</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Information economy</t>
+          <t>Information Economy</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>ICT indicators, industrial classification, economic activity, ISIC</t>
+          <t>ICT indicators, Industrial Classification, economic activity, ISIC</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20T14:52:00</t>
+          <t>2025-12-08T09:44:00</t>
         </is>
       </c>
       <c r="J66" s="5" t="n">
@@ -6394,7 +6394,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>663946</v>
+        <v>83239</v>
       </c>
       <c r="N66" s="5" t="n">
         <v>0</v>
@@ -6441,20 +6441,20 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEnterprSize</t>
+          <t>US.IctUseEconActivity_Isic4</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>2266</v>
+        <v>2250</v>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by enterprise size - Annual</t>
+          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 4) - Annual</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Information Economy</t>
+          <t>Information economy</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>ICT indicators, enterprise size</t>
+          <t>ICT indicators, industrial classification, economic activity, ISIC</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20T14:49:00</t>
+          <t>2026-04-20T14:52:00</t>
         </is>
       </c>
       <c r="J67" s="5" t="n">
@@ -6482,7 +6482,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>222567</v>
+        <v>663946</v>
       </c>
       <c r="N67" s="5" t="n">
         <v>0</v>
@@ -6529,15 +6529,15 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseLocation</t>
+          <t>US.IctUseEnterprSize</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>2064</v>
+        <v>2266</v>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by location type - Annual</t>
+          <t>ICT use in business: Core indicators by enterprise size - Annual</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -6552,12 +6552,12 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>ICT indicators, enterprises, location</t>
+          <t>ICT indicators, enterprise size</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>2025-12-08T09:44:00</t>
+          <t>2026-04-20T14:49:00</t>
         </is>
       </c>
       <c r="J68" s="5" t="n">
@@ -6570,7 +6570,7 @@
         <v>0</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>8295</v>
+        <v>222567</v>
       </c>
       <c r="N68" s="5" t="n">
         <v>0</v>
@@ -6617,35 +6617,35 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>US.ECommerceTotal</t>
+          <t>US.IctUseLocation</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>2529</v>
+        <v>2064</v>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: Domestic and international sales - Annual (analytical)</t>
+          <t>ICT use in business: Core indicators by location type - Annual</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>E-commerce</t>
+          <t>Information Economy</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>Digital economy and technology &gt; E-commerce</t>
+          <t>Digital economy and technology &gt; Digital economy</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>e-commerce, digital ordering, digital trade, sales, business statistics</t>
+          <t>ICT indicators, enterprises, location</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T08:57:00</t>
+          <t>2025-12-08T09:44:00</t>
         </is>
       </c>
       <c r="J69" s="5" t="n">
@@ -6658,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>906006</v>
+        <v>8295</v>
       </c>
       <c r="N69" s="5" t="n">
         <v>0</v>
@@ -6705,15 +6705,15 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>US.ECommerceInternational</t>
+          <t>US.ECommerceTotal</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: International digitally ordered trade, bilateral – Annual (analytical)</t>
+          <t>E-commerce: Domestic and international sales - Annual (analytical)</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>e-commerce, digital trade, digital ordering, sales, turnover, business statistics</t>
+          <t>e-commerce, digital ordering, digital trade, sales, business statistics</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>139183</v>
+        <v>906006</v>
       </c>
       <c r="N70" s="5" t="n">
         <v>0</v>
@@ -6793,35 +6793,35 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>US.UCPI_A</t>
+          <t>US.ECommerceInternational</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>2274</v>
+        <v>2530</v>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Commodity prices: UNCTAD Commodity Price Index - Annual</t>
+          <t>E-commerce: International digitally ordered trade, bilateral – Annual (analytical)</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>E-commerce</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Economy, investment and finance &gt; Commodity prices</t>
+          <t>Digital economy and technology &gt; E-commerce</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>commodity, price, index</t>
+          <t>e-commerce, digital trade, digital ordering, sales, turnover, business statistics</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2026-02-10T12:49:00</t>
+          <t>2026-05-21T08:57:00</t>
         </is>
       </c>
       <c r="J71" s="5" t="n">
@@ -6834,7 +6834,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>4615</v>
+        <v>139183</v>
       </c>
       <c r="N71" s="5" t="n">
         <v>0</v>
@@ -6881,20 +6881,20 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>US.UCPI_M</t>
+          <t>US.UCPI_A</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>2570</v>
+        <v>2596</v>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Commodity prices: UNCTAD Commodity Price Index - Monthly</t>
+          <t>Commodity prices: UNCTAD Commodity Price Index - Annual</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Commodities prices</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T07:42:00</t>
+          <t>2026-02-10T13:02:00</t>
         </is>
       </c>
       <c r="J72" s="5" t="n">
@@ -6922,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>66860</v>
+        <v>4615</v>
       </c>
       <c r="N72" s="5" t="n">
         <v>0</v>
@@ -6969,20 +6969,20 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPrice_A</t>
+          <t>US.UCPI_M</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>1663</v>
+        <v>2597</v>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Commodity prices, 1995-2024, annual</t>
+          <t>Commodity prices: UNCTAD Commodity Price Index - Monthly</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Commodities prices</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>commodities, price</t>
+          <t>commodity, price, index</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>2025-03-12T13:35:00</t>
+          <t>2026-09-11T12:02:00</t>
         </is>
       </c>
       <c r="J73" s="5" t="n">
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>9629</v>
+        <v>67024</v>
       </c>
       <c r="N73" s="5" t="n">
         <v>0</v>
@@ -7057,15 +7057,15 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPrice_M</t>
+          <t>US.CommodityPrice_A</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>1899</v>
+        <v>1663</v>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Commodity prices, January 1995 - June 2025, monthly</t>
+          <t>DISCONTINUED - Commodity prices, 1995-2024, annual</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>commodity, price</t>
+          <t>commodities, price</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>2025-08-11T14:32:00</t>
+          <t>2025-03-12T13:35:00</t>
         </is>
       </c>
       <c r="J74" s="5" t="n">
@@ -7098,7 +7098,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>84674</v>
+        <v>9629</v>
       </c>
       <c r="N74" s="5" t="n">
         <v>0</v>
@@ -7145,15 +7145,15 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPriceIndices_A</t>
+          <t>US.CommodityPrice_M</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>1662</v>
+        <v>1899</v>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - UNCTAD Commodity Price Index, 1995-2024, annual (2015=100)</t>
+          <t>DISCONTINUED - Commodity prices, January 1995 - June 2025, monthly</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>commodities, price, index</t>
+          <t>commodity, price</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>2025-03-12T13:35:00</t>
+          <t>2025-08-11T14:32:00</t>
         </is>
       </c>
       <c r="J75" s="5" t="n">
@@ -7186,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>4522</v>
+        <v>84674</v>
       </c>
       <c r="N75" s="5" t="n">
         <v>0</v>
@@ -7233,15 +7233,15 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPriceIndices_M</t>
+          <t>US.CommodityPriceIndices_A</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>1900</v>
+        <v>1662</v>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - UNCTAD Commodity Price Index, January 1995 - June 2025, monthly (2015=100)</t>
+          <t>DISCONTINUED - UNCTAD Commodity Price Index, 1995-2024, annual (2015=100)</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -7256,12 +7256,12 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>commodity, price, index</t>
+          <t>commodities, price, index</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>2025-08-11T14:32:00</t>
+          <t>2025-03-12T13:35:00</t>
         </is>
       </c>
       <c r="J76" s="5" t="n">
@@ -7274,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>66229</v>
+        <v>4522</v>
       </c>
       <c r="N76" s="5" t="n">
         <v>0</v>
@@ -7321,35 +7321,35 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>US.GovExpenditures</t>
+          <t>US.CommodityPriceIndices_M</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>590</v>
+        <v>1900</v>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Government expenditures</t>
+          <t>DISCONTINUED - UNCTAD Commodity Price Index, January 1995 - June 2025, monthly (2015=100)</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Public Finance</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Economy, investment and finance &gt; Public finance</t>
+          <t>Economy, investment and finance &gt; Commodity prices</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Government, expenditures, COFOG</t>
+          <t>commodity, price, index</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>2023-07-18T16:51:00</t>
+          <t>2025-08-11T14:32:00</t>
         </is>
       </c>
       <c r="J77" s="5" t="n">
@@ -7362,7 +7362,7 @@
         <v>0</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>248075</v>
+        <v>66229</v>
       </c>
       <c r="N77" s="5" t="n">
         <v>0</v>
@@ -7409,48 +7409,48 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>US.BiotradeMerch</t>
+          <t>US.GovExpenditures</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>2517</v>
+        <v>590</v>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
+          <t>Government expenditures</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Merchandise biotrade</t>
+          <t>Public Finance</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in biodiversity-based products</t>
+          <t>Economy, investment and finance &gt; Public finance</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>Export, import, balance, value, merchandise, trade, biotrade, biodiversity, growth, rate</t>
+          <t>Government, expenditures, COFOG</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20T06:30:00</t>
+          <t>2023-07-18T16:51:00</t>
         </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>15552119339</v>
+        <v>248075</v>
       </c>
       <c r="N78" s="5" t="n">
         <v>0</v>
@@ -7459,7 +7459,7 @@
       <c r="P78" s="4" t="inlineStr"/>
       <c r="Q78" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R78" s="4" t="inlineStr"/>
@@ -7497,20 +7497,20 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>US.BioTradeMerchMarketIndices</t>
+          <t>US.BiotradeMerch</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>2124</v>
+        <v>2517</v>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Biotrade: Market concentration and structural change indices - Annual (analytical)</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade</t>
+          <t>Merchandise biotrade</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -7520,25 +7520,25 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Export, import, merchandise, trade, market concentration, structural change, biotrade, biodiversity</t>
+          <t>Export, import, balance, value, merchandise, trade, biotrade, biodiversity, growth, rate</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>2025-11-28T16:02:00</t>
+          <t>2026-07-20T06:30:00</t>
         </is>
       </c>
       <c r="J79" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>623798</v>
+        <v>15552119339</v>
       </c>
       <c r="N79" s="5" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
       <c r="P79" s="4" t="inlineStr"/>
       <c r="Q79" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R79" s="4" t="inlineStr"/>
@@ -7585,15 +7585,15 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>US.NonPlasticSubstsTradeByPartner</t>
+          <t>US.BioTradeMerchMarketIndices</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>1884</v>
+        <v>2124</v>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Trade in non-plastic substitutes, annual (analytical)</t>
+          <t>DISCONTINUED - Biotrade: Market concentration and structural change indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -7603,30 +7603,30 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in non-plastic substitutes</t>
+          <t>Environment and related trade &gt; Trade in biodiversity-based products</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>Plastics, trade, export, Non-plastic substitutes</t>
+          <t>Export, import, merchandise, trade, market concentration, structural change, biotrade, biodiversity</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>2025-08-04T06:56:00</t>
+          <t>2025-11-28T16:02:00</t>
         </is>
       </c>
       <c r="J80" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>511626169</v>
+        <v>623798</v>
       </c>
       <c r="N80" s="5" t="n">
         <v>0</v>
@@ -7635,7 +7635,7 @@
       <c r="P80" s="4" t="inlineStr"/>
       <c r="Q80" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R80" s="4" t="inlineStr"/>
@@ -7673,35 +7673,35 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>US.OceanTrade</t>
+          <t>US.NonPlasticSubstsTradeByPartner</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>2426</v>
+        <v>1884</v>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Ocean goods: Bilateral trade by product group - Annual (analytical)</t>
+          <t>Trade in non-plastic substitutes, annual (analytical)</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>Environment and related trade</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in ocean goods and services</t>
+          <t>Environment and related trade &gt; Trade in non-plastic substitutes</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Oceans, international, trade, growth, sectors, maritime, sea</t>
+          <t>Plastics, trade, export, Non-plastic substitutes</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08T11:51:00</t>
+          <t>2025-08-04T06:56:00</t>
         </is>
       </c>
       <c r="J81" s="5" t="n">
@@ -7714,7 +7714,7 @@
         <v>1</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>572108660</v>
+        <v>511626169</v>
       </c>
       <c r="N81" s="5" t="n">
         <v>0</v>
@@ -7761,35 +7761,35 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>US.AssociatedPlasticsTradebyPartner</t>
+          <t>US.OceanTrade</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>2582</v>
+        <v>2426</v>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Associated plastics trade by partner, annual (analytical)</t>
+          <t>Ocean goods: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Plastics trade</t>
+          <t>International trade in goods and services</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in plastic-based products</t>
+          <t>Environment and related trade &gt; Trade in ocean goods and services</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>Associated plastics, trade, partner</t>
+          <t>Oceans, international, trade, growth, sectors, maritime, sea</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T12:05:00</t>
+          <t>2026-06-08T11:51:00</t>
         </is>
       </c>
       <c r="J82" s="5" t="n">
@@ -7802,7 +7802,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>33181670</v>
+        <v>572108660</v>
       </c>
       <c r="N82" s="5" t="n">
         <v>0</v>
@@ -7849,15 +7849,15 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>US.PlasticsTradebyPartner</t>
+          <t>US.AssociatedPlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Plastics trade by partner, annual (analytical)</t>
+          <t>Associated plastics trade by partner, annual (analytical)</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Plastics, trade, export</t>
+          <t>Associated plastics, trade, partner</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -7890,7 +7890,7 @@
         <v>1</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>90879049</v>
+        <v>33181670</v>
       </c>
       <c r="N83" s="5" t="n">
         <v>0</v>
@@ -7937,15 +7937,15 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>US.HiddenPlasticsTradebyPartner</t>
+          <t>US.PlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>2583</v>
+        <v>2581</v>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Spotlight on selected plastic trade trends, by partner (analytical)</t>
+          <t>Plastics trade by partner, annual (analytical)</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>Plastics, trade, partner, hs, product</t>
+          <t>Plastics, trade, export</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -7978,7 +7978,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>55831373</v>
+        <v>90879049</v>
       </c>
       <c r="N84" s="5" t="n">
         <v>0</v>
@@ -8025,48 +8025,48 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodCatByProc</t>
+          <t>US.HiddenPlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>1676</v>
+        <v>2583</v>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Trade by food category, detailed by food processing (analytical)</t>
+          <t>Spotlight on selected plastic trade trends, by partner (analytical)</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>International trade</t>
+          <t>Plastics trade</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Food trade by processing level</t>
+          <t>Environment and related trade &gt; Trade in plastic-based products</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Food processing, food category, trade</t>
+          <t>Plastics, trade, partner, hs, product</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>2025-03-20T12:39:00</t>
+          <t>2026-09-04T12:05:00</t>
         </is>
       </c>
       <c r="J85" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K85" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>2582634489</v>
+        <v>55831373</v>
       </c>
       <c r="N85" s="5" t="n">
         <v>0</v>
@@ -8113,15 +8113,15 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodProcByCat</t>
+          <t>US.TradeFoodCatByProc</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Trade by food processing, detailed by food category (analytical)</t>
+          <t>Trade by food category, detailed by food processing (analytical)</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -8154,7 +8154,7 @@
         <v>2</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>2285091980</v>
+        <v>2582634489</v>
       </c>
       <c r="N86" s="5" t="n">
         <v>0</v>
@@ -8201,48 +8201,48 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeGoodsValue</t>
+          <t>US.TradeFoodProcByCat</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>2222</v>
+        <v>1677</v>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Creative goods: Bilateral trade by product group - Annual (analytical)</t>
+          <t>Trade by food processing, detailed by food category (analytical)</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Creative economy</t>
+          <t>International trade</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in creative goods and services</t>
+          <t>International trade &gt; Food trade by processing level</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Creative goods, trade, exports, imports</t>
+          <t>Food processing, food category, trade</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>2026-04-02T15:01:00</t>
+          <t>2025-03-20T12:39:00</t>
         </is>
       </c>
       <c r="J87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K87" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>335041684</v>
+        <v>2285091980</v>
       </c>
       <c r="N87" s="5" t="n">
         <v>0</v>
@@ -8289,15 +8289,15 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeGoodsGR</t>
+          <t>US.CreativeGoodsValue</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Creative goods: Bilateral trade by product group - Growth rates - Annual (analytical)</t>
+          <t>Creative goods: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Creative goods, trade, exports, imports, growth rates</t>
+          <t>Creative goods, trade, exports, imports</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -8330,7 +8330,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>196623315</v>
+        <v>335041684</v>
       </c>
       <c r="N88" s="5" t="n">
         <v>0</v>
@@ -8377,15 +8377,15 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeServ_Group_E</t>
+          <t>US.CreativeGoodsGR</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>2072</v>
+        <v>2220</v>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Creative services: exports of selected groups of economies - Annual (analytical)</t>
+          <t>Creative goods: Bilateral trade by product group - Growth rates - Annual (analytical)</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -8400,25 +8400,25 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Creative, services, trade, international, economy</t>
+          <t>Creative goods, trade, exports, imports, growth rates</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>2026-04-02T15:05:00</t>
+          <t>2026-04-02T15:01:00</t>
         </is>
       </c>
       <c r="J89" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>15132</v>
+        <v>196623315</v>
       </c>
       <c r="N89" s="5" t="n">
         <v>0</v>
@@ -8427,7 +8427,7 @@
       <c r="P89" s="4" t="inlineStr"/>
       <c r="Q89" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R89" s="4" t="inlineStr"/>
@@ -8465,48 +8465,48 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>US.CriticalMinerals_TradeByPart</t>
+          <t>US.CreativeServ_Group_E</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>2502</v>
+        <v>2072</v>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Critical minerals: Bilateral trade by product group - Annual (analytical)</t>
+          <t>Creative services: exports of selected groups of economies - Annual (analytical)</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>International trade</t>
+          <t>Creative economy</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in critical minerals</t>
+          <t>International trade &gt; Trade in creative goods and services</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Trade, bilateral trade, exports, imports, merchandise trade, critical minerals, energy transition minerals, minerals, commodities, HS, products</t>
+          <t>Creative, services, trade, international, economy</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14T09:51:00</t>
+          <t>2026-04-02T15:05:00</t>
         </is>
       </c>
       <c r="J90" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>544826561</v>
+        <v>15132</v>
       </c>
       <c r="N90" s="5" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
       <c r="P90" s="4" t="inlineStr"/>
       <c r="Q90" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R90" s="4" t="inlineStr"/>
@@ -8553,15 +8553,15 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>US.GSTP_TradeMatrix</t>
+          <t>US.CriticalMinerals_TradeByPart</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>2592</v>
+        <v>2502</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>GSTP: Merchandise trade matrix - Annual (analytical)</t>
+          <t>Critical minerals: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -8571,17 +8571,17 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in merchandise</t>
+          <t>International trade &gt; Trade in critical minerals</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>International trade, structure, partner, economy, product, group, GSTP, Global System of Trade Preferences</t>
+          <t>Trade, bilateral trade, exports, imports, merchandise trade, critical minerals, energy transition minerals, minerals, commodities, HS, products</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14T07:18:00</t>
+          <t>2026-07-14T09:51:00</t>
         </is>
       </c>
       <c r="J91" s="5" t="n">
@@ -8594,7 +8594,7 @@
         <v>1</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>371715547</v>
+        <v>544826561</v>
       </c>
       <c r="N91" s="5" t="n">
         <v>0</v>
@@ -8641,20 +8641,20 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>US.IntraTrade</t>
+          <t>US.GSTP_TradeMatrix</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>2588</v>
+        <v>2592</v>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Intra-trade and extra-trade of country groups by product, annual (analytical)</t>
+          <t>GSTP: Merchandise trade matrix - Annual (analytical)</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>International trade</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Intra-trade, extra-trade, value, share, group, region</t>
+          <t>International trade, structure, partner, economy, product, group, GSTP, Global System of Trade Preferences</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30T07:17:00</t>
+          <t>2026-07-14T07:18:00</t>
         </is>
       </c>
       <c r="J92" s="5" t="n">
@@ -8682,7 +8682,7 @@
         <v>1</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>64011500</v>
+        <v>371715547</v>
       </c>
       <c r="N92" s="5" t="n">
         <v>0</v>
@@ -8729,20 +8729,20 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>US.ConcentStructIndices</t>
+          <t>US.IntraTrade</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>2463</v>
+        <v>2588</v>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Market concentration and structural change indices - Annual (analytical)</t>
+          <t>Merchandise: Intra-trade and extra-trade of country groups by product, annual (analytical)</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>International trade</t>
+          <t>International trade in goods and services</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -8752,25 +8752,25 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Indices, imports, exports, concentration, structural, trade</t>
+          <t>Intra-trade, extra-trade, value, share, group, region</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09T11:36:00</t>
+          <t>2026-06-30T07:17:00</t>
         </is>
       </c>
       <c r="J93" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>210324</v>
+        <v>64011500</v>
       </c>
       <c r="N93" s="5" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
       <c r="P93" s="4" t="inlineStr"/>
       <c r="Q93" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R93" s="4" t="inlineStr"/>
@@ -8817,20 +8817,20 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>US.TradeMatrix</t>
+          <t>US.ConcentStructIndices</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>2590</v>
+        <v>2463</v>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade matrix - Annual (analytical)</t>
+          <t>Merchandise: Market concentration and structural change indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>International trade</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -8840,25 +8840,25 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>International trade, structure, partner, economy, product, group</t>
+          <t>Indices, imports, exports, concentration, structural, trade</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30T07:17:00</t>
+          <t>2026-07-09T11:36:00</t>
         </is>
       </c>
       <c r="J94" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>10989114010</v>
+        <v>210324</v>
       </c>
       <c r="N94" s="5" t="n">
         <v>0</v>
@@ -8867,7 +8867,7 @@
       <c r="P94" s="4" t="inlineStr"/>
       <c r="Q94" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R94" s="4" t="inlineStr"/>
@@ -8905,15 +8905,15 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>US.TradePriceIndices_Q</t>
+          <t>US.TradeMatrix</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>2487</v>
+        <v>2590</v>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade price index - Quarterly (analytical)</t>
+          <t>Merchandise: Trade matrix - Annual (analytical)</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -8928,25 +8928,25 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Merchandises, Trade, Indices, Prices</t>
+          <t>International trade, structure, partner, economy, product, group</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10T15:13:00</t>
+          <t>2026-06-30T07:17:00</t>
         </is>
       </c>
       <c r="J95" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>114018</v>
+        <v>10989114010</v>
       </c>
       <c r="N95" s="5" t="n">
         <v>0</v>
@@ -8955,7 +8955,7 @@
       <c r="P95" s="4" t="inlineStr"/>
       <c r="Q95" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R95" s="4" t="inlineStr"/>
@@ -8993,15 +8993,15 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServCatByPartner</t>
+          <t>US.TradePriceIndices_Q</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>2545</v>
+        <v>2487</v>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Services: Bilateral trade by category - Annual</t>
+          <t>Merchandise: Trade price index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -9011,30 +9011,30 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in services</t>
+          <t>International trade &gt; Trade in merchandise</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>services, exports, imports, trade, bilateral, partner, transport, travel, sector, category</t>
+          <t>Merchandises, Trade, Indices, Prices</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T11:34:00</t>
+          <t>2026-07-10T15:13:00</t>
         </is>
       </c>
       <c r="J96" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>85648480</v>
+        <v>114018</v>
       </c>
       <c r="N96" s="5" t="n">
         <v>0</v>
@@ -9043,7 +9043,7 @@
       <c r="P96" s="4" t="inlineStr"/>
       <c r="Q96" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R96" s="4" t="inlineStr"/>
@@ -9081,48 +9081,48 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>US.TransportCosts</t>
+          <t>US.TradeServCatByPartner</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>1107</v>
+        <v>2545</v>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Trade-and-Transport Dataset, annual, 2016 onward (analytical)</t>
+          <t>Services: Bilateral trade by category - Annual</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>International trade</t>
+          <t>International trade in goods and services</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Global transport of merchandise trade</t>
+          <t>International trade &gt; Trade in services</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>international, trade, transport, cost, merchandise, product, destination, origin</t>
+          <t>services, exports, imports, trade, bilateral, partner, transport, travel, sector, category</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22T09:00:00</t>
+          <t>2026-07-23T11:34:00</t>
         </is>
       </c>
       <c r="J97" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K97" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>34008028962</v>
+        <v>85648480</v>
       </c>
       <c r="N97" s="5" t="n">
         <v>0</v>
@@ -9169,48 +9169,48 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>US.PortCallsArrivals</t>
+          <t>US.TransportCosts</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>1065</v>
+        <v>1107</v>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: number of port calls, annual (analytical)</t>
+          <t>Trade-and-Transport Dataset, annual, 2016 onward (analytical)</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Maritime transport</t>
+          <t>International trade</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Port calls and performance</t>
+          <t>Maritime and other transport &gt; Global transport of merchandise trade</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>ships, port, maritime, transport, port calls, ports, time in port, vessels, services, container</t>
+          <t>international, trade, transport, cost, merchandise, product, destination, origin</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>2024-03-28T16:25:00</t>
+          <t>2024-05-22T09:00:00</t>
         </is>
       </c>
       <c r="J98" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>20304</v>
+        <v>34008028962</v>
       </c>
       <c r="N98" s="5" t="n">
         <v>0</v>
@@ -9219,7 +9219,7 @@
       <c r="P98" s="4" t="inlineStr"/>
       <c r="Q98" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R98" s="4" t="inlineStr"/>
@@ -9257,15 +9257,15 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>US.PortCallsArrivals_S</t>
+          <t>US.PortCallsArrivals</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: number of port calls, semi-annual (analytical)</t>
+          <t>Port call and performance statistics: number of port calls, annual (analytical)</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -9298,7 +9298,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>38910</v>
+        <v>20304</v>
       </c>
       <c r="N99" s="5" t="n">
         <v>0</v>
@@ -9345,15 +9345,15 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>US.PortCalls</t>
+          <t>US.PortCallsArrivals_S</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: time spent in ports, vessel age and size, annual (analytical)</t>
+          <t>Port call and performance statistics: number of port calls, semi-annual (analytical)</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>2024-03-28T16:47:00</t>
+          <t>2024-03-28T16:25:00</t>
         </is>
       </c>
       <c r="J100" s="5" t="n">
@@ -9386,7 +9386,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>19373</v>
+        <v>38910</v>
       </c>
       <c r="N100" s="5" t="n">
         <v>0</v>
@@ -9433,15 +9433,15 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>US.PortCalls_S</t>
+          <t>US.PortCalls</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: time spent in ports, vessel age and size, semi-annual (analytical)</t>
+          <t>Port call and performance statistics: time spent in ports, vessel age and size, annual (analytical)</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -9474,7 +9474,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>36462</v>
+        <v>19373</v>
       </c>
       <c r="N101" s="5" t="n">
         <v>0</v>
@@ -9521,35 +9521,35 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>US.Gender_DomesticValueAdded</t>
+          <t>US.PortCalls_S</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>1315</v>
+        <v>1066</v>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Domestic value added content in gross exports by sex and broad sector (analytical)</t>
+          <t>Port call and performance statistics: time spent in ports, vessel age and size, semi-annual (analytical)</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Maritime transport</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Population and inclusiveness &gt; Gender and trade</t>
+          <t>Maritime and other transport &gt; Port calls and performance</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>Trade, gender, gap, equality, employment, earnings, wages, domestic value added, export</t>
+          <t>ships, port, maritime, transport, port calls, ports, time in port, vessels, services, container</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>2024-10-10T12:39:00</t>
+          <t>2024-03-28T16:47:00</t>
         </is>
       </c>
       <c r="J102" s="5" t="n">
@@ -9562,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>97680</v>
+        <v>36462</v>
       </c>
       <c r="N102" s="5" t="n">
         <v>0</v>
@@ -9609,35 +9609,35 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>US.InclusiveGrowth</t>
+          <t>US.Gender_DomesticValueAdded</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>1631</v>
+        <v>1315</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Inclusive Growth Index (IGI) (analytical)</t>
+          <t>Domestic value added content in gross exports by sex and broad sector (analytical)</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Inclusive Growth</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Population and inclusiveness &gt; Inclusive growth</t>
+          <t>Population and inclusiveness &gt; Gender and trade</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>Inclusive Growth Index, IGI, economic development, living conditions, social inclusion, environmental sustainability, equity</t>
+          <t>Trade, gender, gap, equality, employment, earnings, wages, domestic value added, export</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>2025-03-10T14:55:00</t>
+          <t>2024-10-10T12:39:00</t>
         </is>
       </c>
       <c r="J103" s="5" t="n">
@@ -9650,7 +9650,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>4221</v>
+        <v>97680</v>
       </c>
       <c r="N103" s="5" t="n">
         <v>0</v>
@@ -9697,35 +9697,35 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>US.IFF_CrimesRelated</t>
+          <t>US.InclusiveGrowth</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>2492</v>
+        <v>1631</v>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Indicator 16.4.1: Crime-related illicit financial flows - Annual</t>
+          <t>Inclusive Growth Index (IGI) (analytical)</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>SDG Indicators</t>
+          <t>Inclusive Growth</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>SDG Indicators &gt; Goal 16</t>
+          <t>Population and inclusiveness &gt; Inclusive growth</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>IFF, crime-related, Drug, smuggling, trafficking, SDG 16.4.1, financial, inwards</t>
+          <t>Inclusive Growth Index, IGI, economic development, living conditions, social inclusion, environmental sustainability, equity</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09T09:17:00</t>
+          <t>2025-03-10T14:55:00</t>
         </is>
       </c>
       <c r="J104" s="5" t="n">
@@ -9738,7 +9738,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>2046</v>
+        <v>4221</v>
       </c>
       <c r="N104" s="5" t="n">
         <v>0</v>
@@ -9785,15 +9785,15 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>US.IFF_TradeMisinvoicing</t>
+          <t>US.IFF_CrimesRelated</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Indicator 16.4.1: Trade misinvoicing illicit financial flows - Annual</t>
+          <t>Indicator 16.4.1: Crime-related illicit financial flows - Annual</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>IFF, IFFs, Trade, misinvoicing, SDG, Tax, SDG</t>
+          <t>IFF, crime-related, Drug, smuggling, trafficking, SDG 16.4.1, financial, inwards</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
@@ -9826,7 +9826,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>3342</v>
+        <v>2046</v>
       </c>
       <c r="N105" s="5" t="n">
         <v>0</v>
@@ -9855,6 +9855,94 @@
         </is>
       </c>
       <c r="V105" s="4" t="inlineStr">
+        <is>
+          <t>https://unctadstat.unctad.org/datacentre/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>UNCTADstat - UNCTAD</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela (Bolivarian Rep. of)</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>US.IFF_TradeMisinvoicing</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>2493</v>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Indicator 16.4.1: Trade misinvoicing illicit financial flows - Annual</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>SDG Indicators</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>SDG Indicators &gt; Goal 16</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>IFF, IFFs, Trade, misinvoicing, SDG, Tax, SDG</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-09T09:17:00</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="5" t="n">
+        <v>3342</v>
+      </c>
+      <c r="N106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="4" t="inlineStr"/>
+      <c r="P106" s="4" t="inlineStr"/>
+      <c r="Q106" s="4" t="inlineStr">
+        <is>
+          <t>Sin valores descargados para Venezuela</t>
+        </is>
+      </c>
+      <c r="R106" s="4" t="inlineStr"/>
+      <c r="S106" s="4" t="inlineStr">
+        <is>
+          <t>assets/data/unctad/csv/ove_unctadstat_venezuela_valores.csv.gz</t>
+        </is>
+      </c>
+      <c r="T106" s="4" t="inlineStr">
+        <is>
+          <t>assets/data/unctad/catalog/unctad-catalog.json</t>
+        </is>
+      </c>
+      <c r="U106" s="4" t="inlineStr">
+        <is>
+          <t>assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx</t>
+        </is>
+      </c>
+      <c r="V106" s="4" t="inlineStr">
         <is>
           <t>https://unctadstat.unctad.org/datacentre/</t>
         </is>
@@ -9872,7 +9960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9969,7 +10057,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Total trade and share, annual</t>
+          <t>Merchandise: Trade - Annual</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -10061,7 +10149,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade balance, annual</t>
+          <t>Merchandise: Trade balance - Annual</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -12099,7 +12187,7 @@
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>66860</v>
+        <v>67024</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
@@ -14169,7 +14257,7 @@
         </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>422391</v>
+        <v>403520</v>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
@@ -14177,10 +14265,10 @@
         </is>
       </c>
       <c r="H98" s="5" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>374</v>
+        <v>348</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
@@ -14610,26 +14698,26 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseLocation</t>
+          <t>US.IctUseTotal</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by location type - Annual</t>
+          <t>ICT use in business: Core indicators - Annual</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>US_IctUseLocation</t>
+          <t>US_IctUseTotal</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2015 to 2025</t>
         </is>
       </c>
       <c r="F108" s="5" t="n">
-        <v>8295</v>
+        <v>29937</v>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
@@ -14644,7 +14732,7 @@
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseLocation/US_IctUseLocation</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseTotal/US_IctUseTotal</t>
         </is>
       </c>
     </row>
@@ -14656,26 +14744,26 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEnterprSize</t>
+          <t>US.IctUseLocation</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by enterprise size - Annual</t>
+          <t>ICT use in business: Core indicators by location type - Annual</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>US_IctUseEnterprSize</t>
+          <t>US_IctUseLocation</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2025</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>222567</v>
+        <v>8295</v>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
@@ -14690,7 +14778,7 @@
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEnterprSize/US_IctUseEnterprSize</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseLocation/US_IctUseLocation</t>
         </is>
       </c>
     </row>
@@ -14702,17 +14790,17 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEconActivity_Isic4</t>
+          <t>US.IctUseEnterprSize</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 4) - Annual</t>
+          <t>ICT use in business: Core indicators by enterprise size - Annual</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>US_IctUseEconActivity_Isic4</t>
+          <t>US_IctUseEnterprSize</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -14721,7 +14809,7 @@
         </is>
       </c>
       <c r="F110" s="5" t="n">
-        <v>663946</v>
+        <v>222567</v>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
@@ -14736,7 +14824,7 @@
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEconActivity_Isic4/US_IctUseEconActivity_Isic4</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEnterprSize/US_IctUseEnterprSize</t>
         </is>
       </c>
     </row>
@@ -14748,26 +14836,26 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEconActivity</t>
+          <t>US.IctUseEconActivity_Isic4</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 3.1) - Annual</t>
+          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 4) - Annual</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>US_IctUseEconActivity</t>
+          <t>US_IctUseEconActivity_Isic4</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2021</t>
+          <t>From 2010 to 2025</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
-        <v>83239</v>
+        <v>663946</v>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
@@ -14782,7 +14870,7 @@
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEconActivity/US_IctUseEconActivity</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEconActivity_Isic4/US_IctUseEconActivity_Isic4</t>
         </is>
       </c>
     </row>
@@ -14794,26 +14882,26 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>US.DigitallyDeliverableServices</t>
+          <t>US.IctUseEconActivity</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Digitally deliverable services: Trade – Annual (analytical)</t>
+          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 3.1) - Annual</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>US_DigitallyDeliverableServices</t>
+          <t>US_IctUseEconActivity</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2010 to 2021</t>
         </is>
       </c>
       <c r="F112" s="5" t="n">
-        <v>1525091</v>
+        <v>83239</v>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
@@ -14821,14 +14909,14 @@
         </is>
       </c>
       <c r="H112" s="5" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>577</v>
+        <v>0</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.DigitallyDeliverableServices/US_DigitallyDeliverableServices</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEconActivity/US_IctUseEconActivity</t>
         </is>
       </c>
     </row>
@@ -14840,26 +14928,26 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServICT</t>
+          <t>US.DigitallyDeliverableServices</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>ICT services: Trade – Annual</t>
+          <t>Digitally deliverable services: Trade – Annual (analytical)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>US_TradeServICT</t>
+          <t>US_DigitallyDeliverableServices</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2024</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F113" s="5" t="n">
-        <v>141178</v>
+        <v>1525091</v>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
@@ -14867,14 +14955,14 @@
         </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>40</v>
+        <v>420</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>94</v>
+        <v>577</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServICT/US_TradeServICT</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.DigitallyDeliverableServices/US_DigitallyDeliverableServices</t>
         </is>
       </c>
     </row>
@@ -14886,26 +14974,26 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>US.ECommerceTotal</t>
+          <t>US.TradeServICT</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: Domestic and international sales - Annual (analytical)</t>
+          <t>ICT services: Trade – Annual</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>US_ECommerceTotal</t>
+          <t>US_TradeServICT</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>From 2012 to 2025</t>
+          <t>From 2005 to 2024</t>
         </is>
       </c>
       <c r="F114" s="5" t="n">
-        <v>906006</v>
+        <v>141178</v>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
@@ -14913,14 +15001,14 @@
         </is>
       </c>
       <c r="H114" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ECommerceTotal/US_ECommerceTotal</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServICT/US_TradeServICT</t>
         </is>
       </c>
     </row>
@@ -14932,26 +15020,26 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>US.ECommerceInternational</t>
+          <t>US.ECommerceTotal</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: International digitally ordered trade, bilateral – Annual (analytical)</t>
+          <t>E-commerce: Domestic and international sales - Annual (analytical)</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>US_ECommerceInternational</t>
+          <t>US_ECommerceTotal</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>From 2015 to 2024</t>
+          <t>From 2012 to 2025</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
-        <v>139183</v>
+        <v>906006</v>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
@@ -14966,7 +15054,7 @@
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ECommerceInternational/US_ECommerceInternational</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ECommerceTotal/US_ECommerceTotal</t>
         </is>
       </c>
     </row>
@@ -14978,26 +15066,26 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>US.FTRI</t>
+          <t>US.ECommerceInternational</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Frontier technology readiness index, annual (analytical)</t>
+          <t>E-commerce: International digitally ordered trade, bilateral – Annual (analytical)</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>US_FTRI</t>
+          <t>US_ECommerceInternational</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2023</t>
+          <t>From 2015 to 2024</t>
         </is>
       </c>
       <c r="F116" s="5" t="n">
-        <v>62747</v>
+        <v>139183</v>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
@@ -15005,14 +15093,14 @@
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FTRI/US_FTRI</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ECommerceInternational/US_ECommerceInternational</t>
         </is>
       </c>
     </row>
@@ -15024,26 +15112,26 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>US.PopTotal</t>
+          <t>US.FTRI</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Population: Total - Annual</t>
+          <t>Frontier technology readiness index, annual (analytical)</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>US_PopTotal</t>
+          <t>US_FTRI</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>From 1950 to 2050</t>
+          <t>From 2010 to 2023</t>
         </is>
       </c>
       <c r="F117" s="5" t="n">
-        <v>374021</v>
+        <v>62747</v>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
@@ -15051,14 +15139,14 @@
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>302</v>
+        <v>84</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopTotal/US_PopTotal</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FTRI/US_FTRI</t>
         </is>
       </c>
     </row>
@@ -15070,17 +15158,17 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>US.PopAgeStruct</t>
+          <t>US.PopTotal</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Population: Structure by gender and age group - Annual</t>
+          <t>Population: Total - Annual</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>US_PopAgeStruct</t>
+          <t>US_PopTotal</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -15089,7 +15177,7 @@
         </is>
       </c>
       <c r="F118" s="5" t="n">
-        <v>12550832</v>
+        <v>374021</v>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
@@ -15097,14 +15185,14 @@
         </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>6666</v>
+        <v>101</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>6666</v>
+        <v>302</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopAgeStruct/US_PopAgeStruct</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopTotal/US_PopTotal</t>
         </is>
       </c>
     </row>
@@ -15116,17 +15204,17 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>US.PopDependency</t>
+          <t>US.PopAgeStruct</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Population: Dependency ratios - Annual</t>
+          <t>Population: Structure by gender and age group - Annual</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>US_PopDependency</t>
+          <t>US_PopAgeStruct</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -15135,7 +15223,7 @@
         </is>
       </c>
       <c r="F119" s="5" t="n">
-        <v>494161</v>
+        <v>12550832</v>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
@@ -15143,14 +15231,14 @@
         </is>
       </c>
       <c r="H119" s="5" t="n">
-        <v>303</v>
+        <v>6666</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>303</v>
+        <v>6666</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopDependency/US_PopDependency</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopAgeStruct/US_PopAgeStruct</t>
         </is>
       </c>
     </row>
@@ -15162,26 +15250,26 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>US.InclusiveGrowth</t>
+          <t>US.PopDependency</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Inclusive Growth Index (IGI) (analytical)</t>
+          <t>Population: Dependency ratios - Annual</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>US_InclusiveGrowth</t>
+          <t>US_PopDependency</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>From 2023 to 2023</t>
+          <t>From 1950 to 2050</t>
         </is>
       </c>
       <c r="F120" s="5" t="n">
-        <v>4221</v>
+        <v>494161</v>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
@@ -15189,14 +15277,14 @@
         </is>
       </c>
       <c r="H120" s="5" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.InclusiveGrowth/US_InclusiveGrowth</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopDependency/US_PopDependency</t>
         </is>
       </c>
     </row>
@@ -15208,26 +15296,26 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>US.Gender_DomesticValueAdded</t>
+          <t>US.InclusiveGrowth</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Domestic value added content in gross exports by sex and broad sector (analytical)</t>
+          <t>Inclusive Growth Index (IGI) (analytical)</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>US_Gender_DomesticValueAdded</t>
+          <t>US_InclusiveGrowth</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2020</t>
+          <t>From 2023 to 2023</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
-        <v>97680</v>
+        <v>4221</v>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
@@ -15242,7 +15330,7 @@
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Gender_DomesticValueAdded/US_Gender_DomesticValueAdded</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.InclusiveGrowth/US_InclusiveGrowth</t>
         </is>
       </c>
     </row>
@@ -15254,26 +15342,26 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>US.Gender_TradableIndustries</t>
+          <t>US.Gender_DomesticValueAdded</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Employment and average monthly earnings in tradable and non-tradable industries (analytical)</t>
+          <t>Domestic value added content in gross exports by sex and broad sector (analytical)</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>US_Gender_TradableIndustries</t>
+          <t>US_Gender_DomesticValueAdded</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2023</t>
+          <t>From 2000 to 2020</t>
         </is>
       </c>
       <c r="F122" s="5" t="n">
-        <v>176441</v>
+        <v>97680</v>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
@@ -15281,14 +15369,14 @@
         </is>
       </c>
       <c r="H122" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Gender_TradableIndustries/US_Gender_TradableIndustries</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Gender_DomesticValueAdded/US_Gender_DomesticValueAdded</t>
         </is>
       </c>
     </row>
@@ -15300,26 +15388,26 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>US.SDG_LULFRG</t>
+          <t>US.Gender_TradableIndustries</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2: Freight loaded and unloaded, maritime transport (metric tons) [IS_RDP_LULFRG]</t>
+          <t>Employment and average monthly earnings in tradable and non-tradable industries (analytical)</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>US_SDG_LULFRG</t>
+          <t>US_Gender_TradableIndustries</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2024</t>
+          <t>From 2000 to 2023</t>
         </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>46857</v>
+        <v>176441</v>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
@@ -15327,14 +15415,14 @@
         </is>
       </c>
       <c r="H123" s="5" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SDG_LULFRG/US_SDG_LULFRG</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Gender_TradableIndustries/US_Gender_TradableIndustries</t>
         </is>
       </c>
     </row>
@@ -15346,26 +15434,26 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>US.SDG_PORFVOL</t>
+          <t>US.SDG_LULFRG</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2: Container port traffic, maritime transport (twenty-foot equivalent units – TEUs) [IS_RDP_PORFVOL]</t>
+          <t>Indicator 9.1.2: Freight loaded and unloaded, maritime transport (metric tons) [IS_RDP_LULFRG]</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>US_SDG_PORFVOL</t>
+          <t>US_SDG_LULFRG</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2000 to 2024</t>
         </is>
       </c>
       <c r="F124" s="5" t="n">
-        <v>15386</v>
+        <v>46857</v>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
@@ -15373,14 +15461,14 @@
         </is>
       </c>
       <c r="H124" s="5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SDG_PORFVOL/US_SDG_PORFVOL</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SDG_LULFRG/US_SDG_LULFRG</t>
         </is>
       </c>
     </row>
@@ -15392,26 +15480,26 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>US.IFF_TradeMisinvoicing</t>
+          <t>US.SDG_PORFVOL</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Indicator 16.4.1: Trade misinvoicing illicit financial flows - Annual</t>
+          <t>Indicator 9.1.2: Container port traffic, maritime transport (twenty-foot equivalent units – TEUs) [IS_RDP_PORFVOL]</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>US_IFF_TradeMisinvoicing</t>
+          <t>US_SDG_PORFVOL</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>From 2011 to 2024</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F125" s="5" t="n">
-        <v>3342</v>
+        <v>15386</v>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
@@ -15419,14 +15507,14 @@
         </is>
       </c>
       <c r="H125" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IFF_TradeMisinvoicing/US_IFF_TradeMisinvoicing</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SDG_PORFVOL/US_SDG_PORFVOL</t>
         </is>
       </c>
     </row>
@@ -15438,39 +15526,85 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
+          <t>US.IFF_TradeMisinvoicing</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Indicator 16.4.1: Trade misinvoicing illicit financial flows - Annual</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>US_IFF_TradeMisinvoicing</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>From 2011 to 2024</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>3342</v>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>Procesado</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IFF_TradeMisinvoicing/US_IFF_TradeMisinvoicing</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>UNCTADstat - UNCTAD</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
           <t>US.IFF_CrimesRelated</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
+      <c r="C127" s="4" t="inlineStr">
         <is>
           <t>Indicator 16.4.1: Crime-related illicit financial flows - Annual</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
+      <c r="D127" s="4" t="inlineStr">
         <is>
           <t>US_IFF_CrimesRelated</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="E127" s="4" t="inlineStr">
         <is>
           <t>From 2015 to 2025</t>
         </is>
       </c>
-      <c r="F126" s="5" t="n">
+      <c r="F127" s="5" t="n">
         <v>2046</v>
       </c>
-      <c r="G126" s="4" t="inlineStr">
+      <c r="G127" s="4" t="inlineStr">
         <is>
           <t>Procesado</t>
         </is>
       </c>
-      <c r="H126" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
+      <c r="H127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
         <is>
           <t>https://unctadstat-api.unctad.org/bulkdownload/US.IFF_CrimesRelated/US_IFF_CrimesRelated</t>
         </is>
@@ -15556,7 +15690,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -15639,7 +15773,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -15659,7 +15793,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19">
@@ -15669,7 +15803,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>85325</v>
+        <v>85299</v>
       </c>
     </row>
     <row r="20">

--- a/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
+++ b/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Digitally deliverable services: Trade – Annual (analytical)</t>
+          <t>Digitally deliverable services: Trade - Annual (analytical)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>ICT services: Trade – Annual</t>
+          <t>ICT services: Trade - Annual</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Frontier technology readiness index, annual (analytical)</t>
+          <t>Technology: Frontier technology readiness index - Annual (analytical)</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1951</v>
+        <v>2620</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>2025-09-23T13:48:00</t>
+          <t>2026-09-24T07:08:00</t>
         </is>
       </c>
       <c r="J12" s="5" t="n">
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>120600</v>
+        <v>125296</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
@@ -1577,20 +1577,20 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>US.FdiFlowsStock</t>
+          <t>US.Remittances</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2559</v>
+        <v>1994</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Foreign direct investment: Inward and outward flows and stock, annual</t>
+          <t xml:space="preserve">Balance of payments: Personal remittances - Annual </t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Foreign direct investment</t>
+          <t>External financial resources</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>foreign, direct, investment, flow, stock, inward, outward, FDI</t>
+          <t>remittances, transfers, personal, compensation, employees, payments, receipts</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T12:15:00</t>
+          <t>2025-11-05T13:07:00</t>
         </is>
       </c>
       <c r="J16" s="5" t="n">
@@ -1618,19 +1618,19 @@
         <v>0</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>676265</v>
+        <v>69641</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>576</v>
+        <v>40</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
@@ -1673,20 +1673,20 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>US.Remittances</t>
+          <t>US.FdiFlowsStock</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1994</v>
+        <v>2559</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Personal remittances: receipts and payments, annual</t>
+          <t>Investment: Foreign direct investment - Annual</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>External financial resources</t>
+          <t>Foreign direct investment</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>remittances, transfers, personal, compensation, employees, payments, receipts</t>
+          <t>foreign, direct, investment, flow, stock, inward, outward, FDI</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>2025-11-05T13:07:00</t>
+          <t>2026-08-17T12:15:00</t>
         </is>
       </c>
       <c r="J17" s="5" t="n">
@@ -1714,19 +1714,19 @@
         <v>0</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>69641</v>
+        <v>676265</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>40</v>
+        <v>576</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product: GDP by type of expenditure, VA by kind of economic activity, total and shares, annual</t>
+          <t>Gross domestic product: By expenditure and by sector - Annual</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Productive capacities index, annual, 2000-2024 (analytical)</t>
+          <t>Structural transformation: Productive Capacities Index - Annual (analytical)</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Green industrial goods trade, Revealed comparative advantage index, annual (analytical)</t>
+          <t>Green industrial goods: Revealed comparative advantage index - Annual (analytical)</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2633,15 +2633,15 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>US.WastewaterTreatment</t>
+          <t>US.EnvironmentalGoodsTrade</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Industrial wastewater treatment technologies (analytical)</t>
+          <t>Green industrial goods: Trade - Annual (Analytical)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Trade, exports, imports, industrial wastewater, wastewater treatment, water treatment technologies, wastewater recovery, HS codes, products</t>
+          <t>Trade, exports, imports, green goods, sector, HS, products, industrial</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -2674,10 +2674,10 @@
         <v>0</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>241521</v>
+        <v>2673479</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>145</v>
+        <v>1716</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
@@ -2729,15 +2729,15 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>US.EnvironmentalGoodsTrade</t>
+          <t>US.WastewaterTreatment</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Total trade in green industrial goods (analytical)</t>
+          <t>Industrial wastewater treatment: Trade of associated products - Annul (ananlytical)</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Trade, exports, imports, green goods, sector, HS, products, industrial</t>
+          <t>Trade, exports, imports, industrial wastewater, wastewater treatment, water treatment technologies, wastewater recovery, HS codes, products</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2770,10 +2770,10 @@
         <v>0</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>2673479</v>
+        <v>241521</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>1716</v>
+        <v>145</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Trade by food category, detailed by food processing, RCA (analytical)</t>
+          <t>Food categories: Revealed comparative advantage index by processing level - Annual (analytical)</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Trade by food processing, detailed by food category, RCA (analytical)</t>
+          <t>Food processing: Revealed comparative advantage index by food category - Annual (analytical)</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>1931</v>
+        <v>2587</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>2025-10-15T11:50:00</t>
+          <t>2026-09-28T11:02:00</t>
         </is>
       </c>
       <c r="J33" s="5" t="n">
@@ -3250,14 +3250,14 @@
         <v>0</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>1484011</v>
+        <v>521218</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>2168</v>
+        <v>460</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Revealed Comparative Advantage index - Annual (analytical)</t>
+          <t>Merchandise: Revealed comparative advantage index - Annual (analytical)</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Theil concentration indices - Annual (analytical)</t>
+          <t>Merchandise: Theil indices of product and market concentration - Annual (analytical)</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -3593,15 +3593,15 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>US.TradeMerchGR</t>
+          <t>US.TradeMerchTotal</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Total trade growth rates, annual</t>
+          <t>Merchandise: Trade - Annual</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Growth rates, export, import, merchandise, trade</t>
+          <t>Export,import,value,share,merchandise,trade</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -3634,19 +3634,19 @@
         <v>0</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>214725</v>
+        <v>424083</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>104</v>
+        <v>312</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>19801981</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>20242025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
@@ -3689,15 +3689,15 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>US.TradeMerchTotal</t>
+          <t>US.TradeMerchGR</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade - Annual</t>
+          <t>Merchandise: Trade - Growth rates - Annual</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Export,import,value,share,merchandise,trade</t>
+          <t>Growth rates, export, import, merchandise, trade</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -3730,19 +3730,19 @@
         <v>0</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>424083</v>
+        <v>214725</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>312</v>
+        <v>104</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>19801981</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>20242025</t>
         </is>
       </c>
       <c r="Q38" s="4" t="inlineStr">
@@ -3785,15 +3785,15 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>US.TermsOfTrade</t>
+          <t>US.TradeMerchBalance</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>2512</v>
+        <v>2203</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade - Core indices - Annual (analytical)</t>
+          <t>Merchandise: Trade balance - Annual</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Trade, indices, value, volume, unit value, terms of trade, purchasing power of exports</t>
+          <t>Export, import, value, share, balance, merchandise, trade</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20T11:13:00</t>
+          <t>2026-03-19T13:51:00</t>
         </is>
       </c>
       <c r="J39" s="5" t="n">
@@ -3826,14 +3826,14 @@
         <v>0</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>304595</v>
+        <v>235857</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -3881,15 +3881,15 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>US.TradeMerchBalance</t>
+          <t>US.TermsOfTrade</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>2203</v>
+        <v>2512</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade balance - Annual</t>
+          <t>Merchandise: Trade indicators - Annual (analytical)</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Export, import, value, share, balance, merchandise, trade</t>
+          <t>Trade, indices, value, volume, unit value, terms of trade, purchasing power of exports</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19T13:51:00</t>
+          <t>2026-07-20T11:13:00</t>
         </is>
       </c>
       <c r="J40" s="5" t="n">
@@ -3922,14 +3922,14 @@
         <v>0</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>235857</v>
+        <v>304595</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Container port throughput, annual (analytical)</t>
+          <t>Freight: Container port throughput - Annual (analytical)</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>World seaborne trade by type of cargo, annual (analytical)</t>
+          <t>Freight: Seaborne trade by cargo type - Annual (analytical)</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>2458</v>
+        <v>2595</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23T14:11:00</t>
+          <t>2026-09-28T11:09:00</t>
         </is>
       </c>
       <c r="J47" s="5" t="n">
@@ -4594,10 +4594,10 @@
         <v>0</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>209318</v>
+        <v>215059</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026M06</t>
+          <t>2026M09</t>
         </is>
       </c>
       <c r="Q47" s="4" t="inlineStr">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>2457</v>
+        <v>2594</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23T14:11:00</t>
+          <t>2026-09-28T11:09:00</t>
         </is>
       </c>
       <c r="J48" s="5" t="n">
@@ -4690,10 +4690,10 @@
         <v>0</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>203416</v>
+        <v>205865</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026Q02</t>
+          <t>2026Q03</t>
         </is>
       </c>
       <c r="Q48" s="4" t="inlineStr">
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>2282</v>
+        <v>2584</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26T14:20:00</t>
+          <t>2026-09-28T11:09:00</t>
         </is>
       </c>
       <c r="J49" s="5" t="n">
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>355602</v>
+        <v>359436</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026Q02</t>
+          <t>2026Q03</t>
         </is>
       </c>
       <c r="Q49" s="4" t="inlineStr">
@@ -4841,15 +4841,15 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>US.VesselValueByOwnership</t>
+          <t>US.FleetBeneficialOwners</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by beneficial ownership - Annual (analytical)</t>
+          <t>Merchant fleet: By beneficial ownership - Annual (analytical)</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -4882,14 +4882,14 @@
         <v>0</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>9851</v>
+        <v>412428</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>8</v>
+        <v>897</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
@@ -4937,15 +4937,15 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>US.FleetBeneficialOwners</t>
+          <t>US.MerchantFleet</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>2337</v>
+        <v>2353</v>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by beneficial ownership - Core indicators - Annual (analytical)</t>
+          <t>Merchant fleet: By flag of registration and ship type - Annual (analytical)</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>beneficial, owner, flag, merchant, fleet, maritime, transport</t>
+          <t>merchant, fleet, maritime, transport, container, tanker, bulk, cargo, ship</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18T13:52:00</t>
+          <t>2026-06-18T13:50:00</t>
         </is>
       </c>
       <c r="J51" s="5" t="n">
@@ -4978,14 +4978,14 @@
         <v>0</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>412428</v>
+        <v>938045</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>897</v>
+        <v>1102</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -5033,15 +5033,15 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>US.VesselValueByRegistration</t>
+          <t>US.VesselValueByOwnership</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by flag of registration - Annual (analytical)</t>
+          <t>Merchant fleet: Share by beneficial ownership - Annual (analytical)</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -5074,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>9782</v>
+        <v>9851</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>8</v>
@@ -5129,15 +5129,15 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>US.MerchantFleet</t>
+          <t>US.VesselValueByRegistration</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>2353</v>
+        <v>2339</v>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by flag of registration and ship type - Core indicators - Annual (analytical)</t>
+          <t>Merchant fleet: Share by flag of registration - Annual (analytical)</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>merchant, fleet, maritime, transport, container, tanker, bulk, cargo, ship</t>
+          <t>beneficial, owner, flag, merchant, fleet, maritime, transport</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18T13:50:00</t>
+          <t>2026-06-18T13:52:00</t>
         </is>
       </c>
       <c r="J53" s="5" t="n">
@@ -5170,14 +5170,14 @@
         <v>0</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>938045</v>
+        <v>9782</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>1102</v>
+        <v>8</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Seafarer supply, quinquennial, 2015 and 2021 (analytical)</t>
+          <t>Seafarer: Supply estimates by rank - Quinquennial (analytical)</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Ship building: Merchant fleet built - Annual (analytical)</t>
+          <t>Merchant fleet: Ship building - Annual</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Ship recycling: Merchant fleet recycled - Annual (analytical)</t>
+          <t>Merchant fleet: Ship recycling - Annual</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Employment and average monthly earnings in tradable and non-tradable industries (analytical)</t>
+          <t>Gender: Employment and earnings by sex - Annual (analytical)</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2: Container port traffic, maritime transport (twenty-foot equivalent units – TEUs) [IS_RDP_PORFVOL]</t>
+          <t>Indicator 9.1.2: Container port traffic - Annual</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2: Freight loaded and unloaded, maritime transport (metric tons) [IS_RDP_LULFRG]</t>
+          <t>Indicator 9.1.2: Freight loaded and unloaded - Annual</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: International digitally ordered trade, bilateral – Annual (analytical)</t>
+          <t>E-commerce: International digitally ordered trade, bilateral - Annual (analytical)</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Government expenditures</t>
+          <t>Government expenditures: By function - Annual</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Trade in non-plastic substitutes, annual (analytical)</t>
+          <t>Non-plastics: Bilateral trade of non-plastic substitutes - Annual (analytical)</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -7849,15 +7849,15 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>US.AssociatedPlasticsTradebyPartner</t>
+          <t>US.PlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Associated plastics trade by partner, annual (analytical)</t>
+          <t>Plastics: Bilateral trade across plastics life-cycle stages - Annual (analytical)</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Associated plastics, trade, partner</t>
+          <t>Plastics, trade, export</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -7890,7 +7890,7 @@
         <v>1</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>33181670</v>
+        <v>90879049</v>
       </c>
       <c r="N83" s="5" t="n">
         <v>0</v>
@@ -7937,15 +7937,15 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>US.PlasticsTradebyPartner</t>
+          <t>US.HiddenPlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>2581</v>
+        <v>2583</v>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Plastics trade by partner, annual (analytical)</t>
+          <t>Plastics: Bilateral trade of plastic packaging, synthetic textiles and synthetic rubber - Annual (analytical)</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>Plastics, trade, export</t>
+          <t>Plastics, trade, partner, hs, product</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -7978,7 +7978,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>90879049</v>
+        <v>55831373</v>
       </c>
       <c r="N84" s="5" t="n">
         <v>0</v>
@@ -8025,15 +8025,15 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>US.HiddenPlasticsTradebyPartner</t>
+          <t>US.AssociatedPlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Spotlight on selected plastic trade trends, by partner (analytical)</t>
+          <t>Plastics: Bilateral trade of plastics associated products - Annual (analytical)</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Plastics, trade, partner, hs, product</t>
+          <t>Associated plastics, trade, partner</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -8066,7 +8066,7 @@
         <v>1</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>55831373</v>
+        <v>33181670</v>
       </c>
       <c r="N85" s="5" t="n">
         <v>0</v>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Trade by food category, detailed by food processing (analytical)</t>
+          <t>Food categories: Bilateral trade by processing level - Annual (analytical)</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Trade by food processing, detailed by food category (analytical)</t>
+          <t>Food processing: Bilateral trade by food category - Annual (analytical)</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Intra-trade and extra-trade of country groups by product, annual (analytical)</t>
+          <t>Merchandise: Intra- and extra-trade of country groups by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Trade-and-Transport Dataset, annual, 2016 onward (analytical)</t>
+          <t>Trade and transport: By destination, mode and product group  - Annual (analytical)</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: number of port calls, annual (analytical)</t>
+          <t>Port calls: Calls by commercial market - Annual (analytical)</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: number of port calls, semi-annual (analytical)</t>
+          <t>Port calls: Calls by commercial market - Semi-annual (analytical)</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: time spent in ports, vessel age and size, annual (analytical)</t>
+          <t>Port calls: Performance indicators - Annual (analytical)</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: time spent in ports, vessel age and size, semi-annual (analytical)</t>
+          <t>Port calls: Performance indicators - Semi-annual (analytical)</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Domestic value added content in gross exports by sex and broad sector (analytical)</t>
+          <t>Gender: Domestic value added in gross exports by sex and broad sector - Annual (analytical)</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Inclusive Growth Index (IGI) (analytical)</t>
+          <t>Inclusiveness: Inclusive growth index - Annual (analytical)</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Indicator 16.4.1: Crime-related illicit financial flows - Annual</t>
+          <t>Indicator 16.4.1: Crime-related illicit financial flows, IFFs - Annual</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Indicator 16.4.1: Trade misinvoicing illicit financial flows - Annual</t>
+          <t xml:space="preserve">Indicator 16.4.1: Trade misinvoicing illicit financial flows, IFFs - Annual </t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Total trade growth rates, annual</t>
+          <t>Merchandise: Trade - Growth rates - Annual</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade - Core indices - Annual (analytical)</t>
+          <t>Merchandise: Trade indicators - Annual (analytical)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Intra-trade and extra-trade of country groups by product, annual (analytical)</t>
+          <t>Merchandise: Intra- and extra-trade of country groups by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Theil concentration indices - Annual (analytical)</t>
+          <t>Merchandise: Theil indices of product and market concentration - Annual (analytical)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Revealed Comparative Advantage index - Annual (analytical)</t>
+          <t>Merchandise: Revealed comparative advantage index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -10849,11 +10849,11 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2023</t>
+          <t>From 2019 to 2024</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1484011</v>
+        <v>521218</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>1084</v>
+        <v>230</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>2168</v>
+        <v>460</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Trade by food category, detailed by food processing (analytical)</t>
+          <t>Food categories: Bilateral trade by processing level - Annual (analytical)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Trade by food category, detailed by food processing (analytical)</t>
+          <t>Food categories: Bilateral trade by processing level - Annual (analytical)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Trade by food category, detailed by food processing, RCA (analytical)</t>
+          <t>Food categories: Revealed comparative advantage index by processing level - Annual (analytical)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Trade by food processing, detailed by food category (analytical)</t>
+          <t>Food processing: Bilateral trade by food category - Annual (analytical)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Trade by food processing, detailed by food category (analytical)</t>
+          <t>Food processing: Bilateral trade by food category - Annual (analytical)</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Trade by food processing, detailed by food category, RCA (analytical)</t>
+          <t>Food processing: Revealed comparative advantage index by food category - Annual (analytical)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product: GDP by type of expenditure, VA by kind of economic activity, total and shares, annual</t>
+          <t>Gross domestic product: By expenditure and by sector - Annual</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -11861,11 +11861,11 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>From 1980 to 2024</t>
+          <t>From 1980 to 2025</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>120600</v>
+        <v>125296</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -11892,26 +11892,26 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>US.FdiFlowsStock</t>
+          <t>US.Remittances</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Foreign direct investment: Inward and outward flows and stock, annual</t>
+          <t xml:space="preserve">Balance of payments: Personal remittances - Annual </t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>US_FdiFlowsStock</t>
+          <t>US_Remittances</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>From 1990 to 2025</t>
+          <t>From 2000 to 2024</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>676265</v>
+        <v>69641</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
@@ -11919,14 +11919,14 @@
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>576</v>
+        <v>40</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FdiFlowsStock/US_FdiFlowsStock</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Remittances/US_Remittances</t>
         </is>
       </c>
     </row>
@@ -11938,26 +11938,26 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>US.Remittances</t>
+          <t>US.FdiFlowsStock</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Personal remittances: receipts and payments, annual</t>
+          <t>Investment: Foreign direct investment - Annual</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>US_Remittances</t>
+          <t>US_FdiFlowsStock</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2024</t>
+          <t>From 1990 to 2025</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>69641</v>
+        <v>676265</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
@@ -11965,14 +11965,14 @@
         </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>40</v>
+        <v>576</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Remittances/US_Remittances</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FdiFlowsStock/US_FdiFlowsStock</t>
         </is>
       </c>
     </row>
@@ -11989,7 +11989,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Productive capacities index, annual, 2000-2024 (analytical)</t>
+          <t>Structural transformation: Productive Capacities Index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Government expenditures</t>
+          <t>Government expenditures: By function - Annual</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by flag of registration and ship type - Core indicators - Annual (analytical)</t>
+          <t>Merchant fleet: By flag of registration and ship type - Annual (analytical)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by beneficial ownership - Core indicators - Annual (analytical)</t>
+          <t>Merchant fleet: By beneficial ownership - Annual (analytical)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by flag of registration - Annual (analytical)</t>
+          <t>Merchant fleet: Share by flag of registration - Annual (analytical)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: World fleet by beneficial ownership - Annual (analytical)</t>
+          <t>Merchant fleet: Share by beneficial ownership - Annual (analytical)</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Ship building: Merchant fleet built - Annual (analytical)</t>
+          <t>Merchant fleet: Ship building - Annual</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Ship recycling: Merchant fleet recycled - Annual (analytical)</t>
+          <t>Merchant fleet: Ship recycling - Annual</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>World seaborne trade by type of cargo, annual (analytical)</t>
+          <t>Freight: Seaborne trade by cargo type - Annual (analytical)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Container port throughput, annual (analytical)</t>
+          <t>Freight: Container port throughput - Annual (analytical)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: time spent in ports, vessel age and size, annual (analytical)</t>
+          <t>Port calls: Performance indicators - Annual (analytical)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: time spent in ports, vessel age and size, semi-annual (analytical)</t>
+          <t>Port calls: Performance indicators - Semi-annual (analytical)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: number of port calls, annual (analytical)</t>
+          <t>Port calls: Calls by commercial market - Annual (analytical)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Port call and performance statistics: number of port calls, semi-annual (analytical)</t>
+          <t>Port calls: Calls by commercial market - Semi-annual (analytical)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -13015,7 +13015,7 @@
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>209318</v>
+        <v>215059</v>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>203416</v>
+        <v>205865</v>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
@@ -13069,10 +13069,10 @@
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>355602</v>
+        <v>359436</v>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
@@ -13161,10 +13161,10 @@
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Seafarer supply, quinquennial, 2015 and 2021 (analytical)</t>
+          <t>Seafarer: Supply estimates by rank - Quinquennial (analytical)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Trade-and-Transport Dataset, annual, 2016 onward (analytical)</t>
+          <t>Trade and transport: By destination, mode and product group  - Annual (analytical)</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Trade-and-Transport Dataset, annual, 2016 onward (analytical)</t>
+          <t>Trade and transport: By destination, mode and product group  - Annual (analytical)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Trade-and-Transport Dataset, annual, 2016 onward (analytical)</t>
+          <t>Trade and transport: By destination, mode and product group  - Annual (analytical)</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Trade-and-Transport Dataset, annual, 2016 onward (analytical)</t>
+          <t>Trade and transport: By destination, mode and product group  - Annual (analytical)</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Trade-and-Transport Dataset, annual, 2016 onward (analytical)</t>
+          <t>Trade and transport: By destination, mode and product group  - Annual (analytical)</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Trade-and-Transport Dataset, annual, 2016 onward (analytical)</t>
+          <t>Trade and transport: By destination, mode and product group  - Annual (analytical)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Trade in non-plastic substitutes, annual (analytical)</t>
+          <t>Non-plastics: Bilateral trade of non-plastic substitutes - Annual (analytical)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Plastics trade by partner, annual (analytical)</t>
+          <t>Plastics: Bilateral trade across plastics life-cycle stages - Annual (analytical)</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Associated plastics trade by partner, annual (analytical)</t>
+          <t>Plastics: Bilateral trade of plastics associated products - Annual (analytical)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Spotlight on selected plastic trade trends, by partner (analytical)</t>
+          <t>Plastics: Bilateral trade of plastic packaging, synthetic textiles and synthetic rubber - Annual (analytical)</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Total trade in green industrial goods (analytical)</t>
+          <t>Green industrial goods: Trade - Annual (Analytical)</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Green industrial goods trade, Revealed comparative advantage index, annual (analytical)</t>
+          <t>Green industrial goods: Revealed comparative advantage index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Industrial wastewater treatment technologies (analytical)</t>
+          <t>Industrial wastewater treatment: Trade of associated products - Annul (ananlytical)</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Digitally deliverable services: Trade – Annual (analytical)</t>
+          <t>Digitally deliverable services: Trade - Annual (analytical)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -14979,7 +14979,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>ICT services: Trade – Annual</t>
+          <t>ICT services: Trade - Annual</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: International digitally ordered trade, bilateral – Annual (analytical)</t>
+          <t>E-commerce: International digitally ordered trade, bilateral - Annual (analytical)</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Frontier technology readiness index, annual (analytical)</t>
+          <t>Technology: Frontier technology readiness index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Inclusive Growth Index (IGI) (analytical)</t>
+          <t>Inclusiveness: Inclusive growth index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Domestic value added content in gross exports by sex and broad sector (analytical)</t>
+          <t>Gender: Domestic value added in gross exports by sex and broad sector - Annual (analytical)</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Employment and average monthly earnings in tradable and non-tradable industries (analytical)</t>
+          <t>Gender: Employment and earnings by sex - Annual (analytical)</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2: Freight loaded and unloaded, maritime transport (metric tons) [IS_RDP_LULFRG]</t>
+          <t>Indicator 9.1.2: Freight loaded and unloaded - Annual</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2: Container port traffic, maritime transport (twenty-foot equivalent units – TEUs) [IS_RDP_PORFVOL]</t>
+          <t>Indicator 9.1.2: Container port traffic - Annual</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Indicator 16.4.1: Trade misinvoicing illicit financial flows - Annual</t>
+          <t xml:space="preserve">Indicator 16.4.1: Trade misinvoicing illicit financial flows, IFFs - Annual </t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Indicator 16.4.1: Crime-related illicit financial flows - Annual</t>
+          <t>Indicator 16.4.1: Crime-related illicit financial flows, IFFs - Annual</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>85299</v>
+        <v>83628</v>
       </c>
     </row>
     <row r="20">

--- a/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
+++ b/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V106"/>
+  <dimension ref="A1:V105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1948</v>
+        <v>2631</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>2025-09-26T12:02:00</t>
+          <t>2026-09-29T13:47:00</t>
         </is>
       </c>
       <c r="J7" s="5" t="n">
@@ -754,10 +754,10 @@
         <v>0</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>1525091</v>
+        <v>1410808</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>577</v>
+        <v>790</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1922</v>
+        <v>2636</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>2025-09-26T12:05:00</t>
+          <t>2026-09-29T13:43:00</t>
         </is>
       </c>
       <c r="J8" s="5" t="n">
@@ -850,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>141178</v>
+        <v>146069</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>94</v>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2205</v>
+        <v>2650</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19T13:51:00</t>
+          <t>2026-10-08T12:58:00</t>
         </is>
       </c>
       <c r="J37" s="5" t="n">
@@ -3634,10 +3634,10 @@
         <v>0</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>424083</v>
+        <v>579937</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>312</v>
+        <v>466</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
@@ -3689,15 +3689,15 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>US.TradeMerchGR</t>
+          <t>US.TradeMerchBalance</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>2204</v>
+        <v>2649</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade - Growth rates - Annual</t>
+          <t>Merchandise: Trade balance - Annual</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Growth rates, export, import, merchandise, trade</t>
+          <t>Export, import, value, share, balance, merchandise, trade</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19T13:51:00</t>
+          <t>2026-10-08T12:58:00</t>
         </is>
       </c>
       <c r="J38" s="5" t="n">
@@ -3730,19 +3730,19 @@
         <v>0</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>214725</v>
+        <v>239425</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>19801981</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>20242025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q38" s="4" t="inlineStr">
@@ -3785,15 +3785,15 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>US.TradeMerchBalance</t>
+          <t>US.TermsOfTrade</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>2203</v>
+        <v>2512</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade balance - Annual</t>
+          <t>Merchandise: Trade indicators - Annual (analytical)</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Export, import, value, share, balance, merchandise, trade</t>
+          <t>Trade, indices, value, volume, unit value, terms of trade, purchasing power of exports</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19T13:51:00</t>
+          <t>2026-07-20T11:13:00</t>
         </is>
       </c>
       <c r="J39" s="5" t="n">
@@ -3826,14 +3826,14 @@
         <v>0</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>235857</v>
+        <v>304595</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -3881,15 +3881,15 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>US.TermsOfTrade</t>
+          <t>US.MerchVolumeQuarterly</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>2512</v>
+        <v>2612</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade indicators - Annual (analytical)</t>
+          <t>Merchandise: Trade volume - Growth rates - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Trade, indices, value, volume, unit value, terms of trade, purchasing power of exports</t>
+          <t>International, merchandise, trade, trend, volume, growth, indices</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20T11:13:00</t>
+          <t>2026-10-08T12:58:00</t>
         </is>
       </c>
       <c r="J40" s="5" t="n">
@@ -3922,19 +3922,19 @@
         <v>0</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>304595</v>
+        <v>644857</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>126</v>
+        <v>848</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2005Q01</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026Q02</t>
         </is>
       </c>
       <c r="Q40" s="4" t="inlineStr">
@@ -3977,15 +3977,15 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>US.MerchVolumeQuarterly</t>
+          <t>US.TradeServCatTotal</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>2473</v>
+        <v>2544</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade volume - Growth rates - Quarterly (analytical)</t>
+          <t>Services: Trade by category - Annual</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -3995,17 +3995,17 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in merchandise</t>
+          <t>International trade &gt; Trade in services</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>International, merchandise, trade, trend, volume, growth, indices</t>
+          <t>services, exports, imports, trade, transport, travel, sector, category</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06T15:59:00</t>
+          <t>2026-07-23T11:34:00</t>
         </is>
       </c>
       <c r="J41" s="5" t="n">
@@ -4018,19 +4018,19 @@
         <v>0</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>639637</v>
+        <v>10102418</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>838</v>
+        <v>4793</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>2005Q01</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026Q01</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="Q41" s="4" t="inlineStr">
@@ -4073,15 +4073,15 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServCatTotal</t>
+          <t>US.TotAndComServicesQuarterly</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>2544</v>
+        <v>2541</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Services: Trade by category - Annual</t>
+          <t>Services: Trade by main category - Quarterly</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>services, exports, imports, trade, transport, travel, sector, category</t>
+          <t>Services, exports, imports, seasonal, adjustment, trade, transport, travel, quarterly, growth, BPM6</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T11:34:00</t>
+          <t>2026-07-23T09:54:00</t>
         </is>
       </c>
       <c r="J42" s="5" t="n">
@@ -4114,19 +4114,19 @@
         <v>0</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>10102418</v>
+        <v>4997704</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>4793</v>
+        <v>3610</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2005Q01</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2018Q02</t>
         </is>
       </c>
       <c r="Q42" s="4" t="inlineStr">
@@ -4169,35 +4169,35 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>US.TotAndComServicesQuarterly</t>
+          <t>US.ContPortThroughput</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>2541</v>
+        <v>2263</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Services: Trade by main category - Quarterly</t>
+          <t>Freight: Container port throughput - Annual (analytical)</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>Maritime transport</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in services</t>
+          <t>Maritime and other transport &gt; Freight volumes by sea</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Services, exports, imports, seasonal, adjustment, trade, transport, travel, quarterly, growth, BPM6</t>
+          <t>ship, maritime, transport, container, port, throughput, TEU</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T09:54:00</t>
+          <t>2026-04-15T15:06:00</t>
         </is>
       </c>
       <c r="J43" s="5" t="n">
@@ -4210,19 +4210,19 @@
         <v>0</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>4997704</v>
+        <v>16188</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>3610</v>
+        <v>12</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>2005Q01</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2018Q02</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="Q43" s="4" t="inlineStr">
@@ -4265,15 +4265,15 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>US.ContPortThroughput</t>
+          <t>US.SeaborneTrade</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>2263</v>
+        <v>2231</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Freight: Container port throughput - Annual (analytical)</t>
+          <t>Freight: Seaborne trade by cargo type - Annual (analytical)</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>ship, maritime, transport, container, port, throughput, TEU</t>
+          <t>seaborne, international, maritime, trade, cargo, volume</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>2026-04-15T15:06:00</t>
+          <t>2026-03-17T15:55:00</t>
         </is>
       </c>
       <c r="J44" s="5" t="n">
@@ -4306,19 +4306,19 @@
         <v>0</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>16188</v>
+        <v>462110</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>12</v>
+        <v>225</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="Q44" s="4" t="inlineStr">
@@ -4361,15 +4361,15 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>US.SeaborneTrade</t>
+          <t>US.LSBCI</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>2231</v>
+        <v>2474</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Freight: Seaborne trade by cargo type - Annual (analytical)</t>
+          <t>Liner shipping: Bilateral connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -4379,17 +4379,17 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Freight volumes by sea</t>
+          <t>Maritime and other transport &gt; Maritime connectivity</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>seaborne, international, maritime, trade, cargo, volume</t>
+          <t>Fleet, merchant, transport, maritime, ship, ports, connectivity, connections, index</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>2026-03-17T15:55:00</t>
+          <t>2026-06-26T14:38:00</t>
         </is>
       </c>
       <c r="J45" s="5" t="n">
@@ -4402,19 +4402,19 @@
         <v>0</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>462110</v>
+        <v>3456483</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>225</v>
+        <v>7398</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2006Q01</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026Q01</t>
         </is>
       </c>
       <c r="Q45" s="4" t="inlineStr">
@@ -4457,15 +4457,15 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>US.LSBCI</t>
+          <t>US.LSCI_M</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>2474</v>
+        <v>2595</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Bilateral connectivity index - Quarterly (analytical)</t>
+          <t>Liner shipping: Connectivity index - Monthly (analytical)</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Fleet, merchant, transport, maritime, ship, ports, connectivity, connections, index</t>
+          <t>maritime, transport, connectivity, ports, index</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26T14:38:00</t>
+          <t>2026-09-28T11:09:00</t>
         </is>
       </c>
       <c r="J46" s="5" t="n">
@@ -4498,19 +4498,19 @@
         <v>0</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>3456483</v>
+        <v>215059</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>7398</v>
+        <v>258</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>2006Q01</t>
+          <t>2006M02</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026Q01</t>
+          <t>2026M09</t>
         </is>
       </c>
       <c r="Q46" s="4" t="inlineStr">
@@ -4553,15 +4553,15 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>US.LSCI_M</t>
+          <t>US.LSCI</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Connectivity index - Monthly (analytical)</t>
+          <t>Liner shipping: Connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -4594,19 +4594,19 @@
         <v>0</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>215059</v>
+        <v>205865</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>258</v>
+        <v>327</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>2006M02</t>
+          <t>2006Q01</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026M09</t>
+          <t>2026Q03</t>
         </is>
       </c>
       <c r="Q47" s="4" t="inlineStr">
@@ -4649,15 +4649,15 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>US.LSCI</t>
+          <t>US.PLSCI</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>2594</v>
+        <v>2584</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Connectivity index - Quarterly (analytical)</t>
+          <t>Liner shipping: Port connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -4690,10 +4690,10 @@
         <v>0</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>205865</v>
+        <v>359436</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>327</v>
+        <v>722</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
@@ -4745,15 +4745,15 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>US.PLSCI</t>
+          <t>US.FleetBeneficialOwners</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>2584</v>
+        <v>2337</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Port connectivity index - Quarterly (analytical)</t>
+          <t>Merchant fleet: By beneficial ownership - Annual (analytical)</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -4763,17 +4763,17 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Maritime connectivity</t>
+          <t>Maritime and other transport &gt; Merchant fleet</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>maritime, transport, connectivity, ports, index</t>
+          <t>beneficial, owner, flag, merchant, fleet, maritime, transport</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28T11:09:00</t>
+          <t>2026-06-18T13:52:00</t>
         </is>
       </c>
       <c r="J49" s="5" t="n">
@@ -4786,19 +4786,19 @@
         <v>0</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>359436</v>
+        <v>412428</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>722</v>
+        <v>897</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>2006Q01</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026Q03</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="Q49" s="4" t="inlineStr">
@@ -4841,15 +4841,15 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>US.FleetBeneficialOwners</t>
+          <t>US.MerchantFleet</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>2337</v>
+        <v>2353</v>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: By beneficial ownership - Annual (analytical)</t>
+          <t>Merchant fleet: By flag of registration and ship type - Annual (analytical)</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>beneficial, owner, flag, merchant, fleet, maritime, transport</t>
+          <t>merchant, fleet, maritime, transport, container, tanker, bulk, cargo, ship</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18T13:52:00</t>
+          <t>2026-06-18T13:50:00</t>
         </is>
       </c>
       <c r="J50" s="5" t="n">
@@ -4882,14 +4882,14 @@
         <v>0</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>412428</v>
+        <v>938045</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>897</v>
+        <v>1102</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
@@ -4937,15 +4937,15 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>US.MerchantFleet</t>
+          <t>US.VesselValueByOwnership</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>2353</v>
+        <v>2338</v>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: By flag of registration and ship type - Annual (analytical)</t>
+          <t>Merchant fleet: Share by beneficial ownership - Annual (analytical)</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>merchant, fleet, maritime, transport, container, tanker, bulk, cargo, ship</t>
+          <t>beneficial, owner, flag, merchant, fleet, maritime, transport</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18T13:50:00</t>
+          <t>2026-06-18T13:52:00</t>
         </is>
       </c>
       <c r="J51" s="5" t="n">
@@ -4978,14 +4978,14 @@
         <v>0</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>938045</v>
+        <v>9851</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>1102</v>
+        <v>8</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -5033,15 +5033,15 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>US.VesselValueByOwnership</t>
+          <t>US.VesselValueByRegistration</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: Share by beneficial ownership - Annual (analytical)</t>
+          <t>Merchant fleet: Share by flag of registration - Annual (analytical)</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -5074,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>9851</v>
+        <v>9782</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>8</v>
@@ -5129,15 +5129,15 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>US.VesselValueByRegistration</t>
+          <t>US.Seafarers</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>2339</v>
+        <v>981</v>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: Share by flag of registration - Annual (analytical)</t>
+          <t>Seafarer: Supply estimates by rank - Quinquennial (analytical)</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -5147,17 +5147,17 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Merchant fleet</t>
+          <t>Maritime and other transport &gt; Seafarer supply</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>beneficial, owner, flag, merchant, fleet, maritime, transport</t>
+          <t>Seafarer, officers, ratings, nationality</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18T13:52:00</t>
+          <t>2023-07-18T11:00:00</t>
         </is>
       </c>
       <c r="J53" s="5" t="n">
@@ -5170,19 +5170,19 @@
         <v>0</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>9782</v>
+        <v>11519</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="Q53" s="4" t="inlineStr">
@@ -5225,15 +5225,15 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>US.Seafarers</t>
+          <t>US.ShipBuilding</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>981</v>
+        <v>2439</v>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Seafarer: Supply estimates by rank - Quinquennial (analytical)</t>
+          <t>Merchant fleet: Ship building - Annual</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -5243,17 +5243,17 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Seafarer supply</t>
+          <t>Maritime and other transport &gt; Ship building and recycling</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Seafarer, officers, ratings, nationality</t>
+          <t>ship,building</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>2023-07-18T11:00:00</t>
+          <t>2026-06-18T13:48:00</t>
         </is>
       </c>
       <c r="J54" s="5" t="n">
@@ -5266,19 +5266,19 @@
         <v>0</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>11519</v>
+        <v>11070</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q54" s="4" t="inlineStr">
@@ -5321,15 +5321,15 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>US.ShipBuilding</t>
+          <t>US.ShipScrapping</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: Ship building - Annual</t>
+          <t>Merchant fleet: Ship recycling - Annual</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>ship,building</t>
+          <t>Merchant fleet, ship, scrapping, demolition</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -5362,14 +5362,14 @@
         <v>0</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>11070</v>
+        <v>8908</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
@@ -5417,35 +5417,35 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>US.ShipScrapping</t>
+          <t>US.Gender_TradableIndustries</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>2440</v>
+        <v>1312</v>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: Ship recycling - Annual</t>
+          <t>Gender: Employment and earnings by sex - Annual (analytical)</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Maritime transport</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Ship building and recycling</t>
+          <t>Population and inclusiveness &gt; Gender and trade</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet, ship, scrapping, demolition</t>
+          <t>Trade, gender, employment, earnings, wages, inequality, female, male</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18T13:48:00</t>
+          <t>2024-10-10T12:39:00</t>
         </is>
       </c>
       <c r="J56" s="5" t="n">
@@ -5458,19 +5458,19 @@
         <v>0</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>8908</v>
+        <v>176441</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="Q56" s="4" t="inlineStr">
@@ -5513,35 +5513,35 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>US.Gender_TradableIndustries</t>
+          <t>US.PopDependency</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>1312</v>
+        <v>2331</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Gender: Employment and earnings by sex - Annual (analytical)</t>
+          <t>Population: Dependency ratios - Annual</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Population and inclusiveness</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Population and inclusiveness &gt; Gender and trade</t>
+          <t>Population and inclusiveness &gt; Population</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Trade, gender, employment, earnings, wages, inequality, female, male</t>
+          <t>dependency, total, child, youth, old-age, elderly</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>2024-10-10T12:39:00</t>
+          <t>2026-05-21T18:32:00</t>
         </is>
       </c>
       <c r="J57" s="5" t="n">
@@ -5554,19 +5554,19 @@
         <v>0</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>176441</v>
+        <v>494161</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="Q57" s="4" t="inlineStr">
@@ -5609,15 +5609,15 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>US.PopDependency</t>
+          <t>US.PopAgeStruct</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Population: Dependency ratios - Annual</t>
+          <t>Population: Structure by gender and age group - Annual</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>dependency, total, child, youth, old-age, elderly</t>
+          <t>population, structure, gender, age</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -5650,10 +5650,10 @@
         <v>0</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>494161</v>
+        <v>12550832</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>303</v>
+        <v>6666</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
@@ -5705,15 +5705,15 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>US.PopAgeStruct</t>
+          <t>US.PopTotal</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Population: Structure by gender and age group - Annual</t>
+          <t>Population: Total - Annual</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>population, structure, gender, age</t>
+          <t>Population, urban, population growth rate</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>12550832</v>
+        <v>374021</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>6666</v>
+        <v>302</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
@@ -5801,35 +5801,35 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>US.PopTotal</t>
+          <t>US.SDG_PORFVOL</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>2329</v>
+        <v>2264</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Population: Total - Annual</t>
+          <t>Indicator 9.1.2: Container port traffic - Annual</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Population and inclusiveness</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Population and inclusiveness &gt; Population</t>
+          <t>SDG Indicators &gt; Goal 9</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>Population, urban, population growth rate</t>
+          <t>ship, maritime, transport, container, port, throughput, TEU, SDG Indicator, SDG Goal 9, Indicator 9.1.2</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T18:32:00</t>
+          <t>2026-04-15T15:06:00</t>
         </is>
       </c>
       <c r="J60" s="5" t="n">
@@ -5842,19 +5842,19 @@
         <v>0</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>374021</v>
+        <v>15386</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>302</v>
+        <v>12</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="Q60" s="4" t="inlineStr">
@@ -5897,20 +5897,20 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>US.SDG_PORFVOL</t>
+          <t>US.SDG_LULFRG</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>2264</v>
+        <v>2254</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2: Container port traffic - Annual</t>
+          <t>Indicator 9.1.2: Freight loaded and unloaded - Annual</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>SDG Indicators</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>ship, maritime, transport, container, port, throughput, TEU, SDG Indicator, SDG Goal 9, Indicator 9.1.2</t>
+          <t>seaborne, international, maritime, trade, cargo, volume, SDG Indicator, SDG Goal 9, Indicator 9.1.2</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>2026-04-15T15:06:00</t>
+          <t>2026-04-16T07:41:00</t>
         </is>
       </c>
       <c r="J61" s="5" t="n">
@@ -5938,19 +5938,19 @@
         <v>0</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>15386</v>
+        <v>46857</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="Q61" s="4" t="inlineStr">
@@ -5993,65 +5993,57 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>US.SDG_LULFRG</t>
+          <t>US.IctGoods</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>2254</v>
+        <v>2533</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2: Freight loaded and unloaded - Annual</t>
+          <t>ICT goods: Bilateral trade by category - Annual</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>SDG Indicators</t>
+          <t>Digital economy</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>SDG Indicators &gt; Goal 9</t>
+          <t>Digital economy and technology &gt; Digital economy</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>seaborne, international, maritime, trade, cargo, volume, SDG Indicator, SDG Goal 9, Indicator 9.1.2</t>
+          <t>Digital Economy, Information Economy, International Trade, ICT goods, Imports, Exports, share, bilateral flows</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>2026-04-16T07:41:00</t>
+          <t>2025-12-01T13:16:00</t>
         </is>
       </c>
       <c r="J62" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>46857</v>
+        <v>115739203</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="O62" s="4" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="P62" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O62" s="4" t="inlineStr"/>
+      <c r="P62" s="4" t="inlineStr"/>
       <c r="Q62" s="4" t="inlineStr">
         <is>
-          <t>Con valores para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R62" s="4" t="inlineStr"/>
@@ -6089,20 +6081,20 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>US.IctGoods</t>
+          <t>US.IctProductionSector</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>2533</v>
+        <v>2238</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>ICT goods: Bilateral trade by category - Annual</t>
+          <t>ICT producing sector: Workforce involved and value added - Annual</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Digital economy</t>
+          <t>Information Economy</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -6112,25 +6104,25 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Digital Economy, Information Economy, International Trade, ICT goods, Imports, Exports, share, bilateral flows</t>
+          <t>ICT producing sector, employment, value added</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>2025-12-01T13:16:00</t>
+          <t>2026-04-20T14:48:00</t>
         </is>
       </c>
       <c r="J63" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>115739203</v>
+        <v>6495</v>
       </c>
       <c r="N63" s="5" t="n">
         <v>0</v>
@@ -6139,7 +6131,7 @@
       <c r="P63" s="4" t="inlineStr"/>
       <c r="Q63" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R63" s="4" t="inlineStr"/>
@@ -6177,20 +6169,20 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>US.IctProductionSector</t>
+          <t>US.IctUseTotal</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>2238</v>
+        <v>2347</v>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>ICT producing sector: Workforce involved and value added - Annual</t>
+          <t>ICT use in business: Core indicators - Annual</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Information Economy</t>
+          <t>Digital economy</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -6200,12 +6192,12 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>ICT producing sector, employment, value added</t>
+          <t>ICT indicators</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20T14:48:00</t>
+          <t>2026-09-14T09:05:00</t>
         </is>
       </c>
       <c r="J64" s="5" t="n">
@@ -6218,7 +6210,7 @@
         <v>0</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>6495</v>
+        <v>29937</v>
       </c>
       <c r="N64" s="5" t="n">
         <v>0</v>
@@ -6265,20 +6257,20 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseTotal</t>
+          <t>US.IctUseEconActivity</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>2347</v>
+        <v>2114</v>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators - Annual</t>
+          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 3.1) - Annual</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Digital economy</t>
+          <t>Information Economy</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -6288,12 +6280,12 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>ICT indicators</t>
+          <t>ICT indicators, Industrial Classification, economic activity, ISIC</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T09:05:00</t>
+          <t>2025-12-08T09:44:00</t>
         </is>
       </c>
       <c r="J65" s="5" t="n">
@@ -6306,7 +6298,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>29937</v>
+        <v>83239</v>
       </c>
       <c r="N65" s="5" t="n">
         <v>0</v>
@@ -6353,20 +6345,20 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEconActivity</t>
+          <t>US.IctUseEconActivity_Isic4</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>2114</v>
+        <v>2250</v>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 3.1) - Annual</t>
+          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 4) - Annual</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Information Economy</t>
+          <t>Information economy</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -6376,12 +6368,12 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>ICT indicators, Industrial Classification, economic activity, ISIC</t>
+          <t>ICT indicators, industrial classification, economic activity, ISIC</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>2025-12-08T09:44:00</t>
+          <t>2026-04-20T14:52:00</t>
         </is>
       </c>
       <c r="J66" s="5" t="n">
@@ -6394,7 +6386,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>83239</v>
+        <v>663946</v>
       </c>
       <c r="N66" s="5" t="n">
         <v>0</v>
@@ -6441,20 +6433,20 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEconActivity_Isic4</t>
+          <t>US.IctUseEnterprSize</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>2250</v>
+        <v>2266</v>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 4) - Annual</t>
+          <t>ICT use in business: Core indicators by enterprise size - Annual</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Information economy</t>
+          <t>Information Economy</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -6464,12 +6456,12 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>ICT indicators, industrial classification, economic activity, ISIC</t>
+          <t>ICT indicators, enterprise size</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20T14:52:00</t>
+          <t>2026-04-20T14:49:00</t>
         </is>
       </c>
       <c r="J67" s="5" t="n">
@@ -6482,7 +6474,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>663946</v>
+        <v>222567</v>
       </c>
       <c r="N67" s="5" t="n">
         <v>0</v>
@@ -6529,15 +6521,15 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEnterprSize</t>
+          <t>US.IctUseLocation</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>2266</v>
+        <v>2064</v>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by enterprise size - Annual</t>
+          <t>ICT use in business: Core indicators by location type - Annual</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -6552,12 +6544,12 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>ICT indicators, enterprise size</t>
+          <t>ICT indicators, enterprises, location</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20T14:49:00</t>
+          <t>2025-12-08T09:44:00</t>
         </is>
       </c>
       <c r="J68" s="5" t="n">
@@ -6570,7 +6562,7 @@
         <v>0</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>222567</v>
+        <v>8295</v>
       </c>
       <c r="N68" s="5" t="n">
         <v>0</v>
@@ -6617,35 +6609,35 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseLocation</t>
+          <t>US.ECommerceTotal</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>2064</v>
+        <v>2529</v>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by location type - Annual</t>
+          <t>E-commerce: Domestic and international sales - Annual (analytical)</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Information Economy</t>
+          <t>E-commerce</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>Digital economy and technology &gt; Digital economy</t>
+          <t>Digital economy and technology &gt; E-commerce</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>ICT indicators, enterprises, location</t>
+          <t>e-commerce, digital ordering, digital trade, sales, business statistics</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>2025-12-08T09:44:00</t>
+          <t>2026-05-21T08:57:00</t>
         </is>
       </c>
       <c r="J69" s="5" t="n">
@@ -6658,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>8295</v>
+        <v>906006</v>
       </c>
       <c r="N69" s="5" t="n">
         <v>0</v>
@@ -6705,15 +6697,15 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>US.ECommerceTotal</t>
+          <t>US.ECommerceInternational</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: Domestic and international sales - Annual (analytical)</t>
+          <t>E-commerce: International digitally ordered trade, bilateral – Annual (analytical)</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -6728,7 +6720,7 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>e-commerce, digital ordering, digital trade, sales, business statistics</t>
+          <t>e-commerce, digital trade, digital ordering, sales, turnover, business statistics</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -6746,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>906006</v>
+        <v>139183</v>
       </c>
       <c r="N70" s="5" t="n">
         <v>0</v>
@@ -6793,35 +6785,35 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>US.ECommerceInternational</t>
+          <t>US.UCPI_A</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>2530</v>
+        <v>2596</v>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: International digitally ordered trade, bilateral - Annual (analytical)</t>
+          <t>Commodity prices: UNCTAD Commodity Price Index - Annual</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>E-commerce</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Digital economy and technology &gt; E-commerce</t>
+          <t>Economy, investment and finance &gt; Commodity prices</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>e-commerce, digital trade, digital ordering, sales, turnover, business statistics</t>
+          <t>commodity, price, index</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T08:57:00</t>
+          <t>2026-02-10T13:02:00</t>
         </is>
       </c>
       <c r="J71" s="5" t="n">
@@ -6834,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>139183</v>
+        <v>4615</v>
       </c>
       <c r="N71" s="5" t="n">
         <v>0</v>
@@ -6881,20 +6873,20 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>US.UCPI_A</t>
+          <t>US.UCPI_M</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Commodity prices: UNCTAD Commodity Price Index - Annual</t>
+          <t>Commodity prices: UNCTAD Commodity Price Index - Monthly</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Commodities prices</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -6909,7 +6901,7 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>2026-02-10T13:02:00</t>
+          <t>2026-09-11T12:02:00</t>
         </is>
       </c>
       <c r="J72" s="5" t="n">
@@ -6922,7 +6914,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>4615</v>
+        <v>67024</v>
       </c>
       <c r="N72" s="5" t="n">
         <v>0</v>
@@ -6969,20 +6961,20 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>US.UCPI_M</t>
+          <t>US.CommodityPrice_A</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>2597</v>
+        <v>1663</v>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Commodity prices: UNCTAD Commodity Price Index - Monthly</t>
+          <t>DISCONTINUED - Commodity prices, 1995-2024, annual</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Commodities prices</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -6992,12 +6984,12 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>commodity, price, index</t>
+          <t>commodities, price</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T12:02:00</t>
+          <t>2025-03-12T13:35:00</t>
         </is>
       </c>
       <c r="J73" s="5" t="n">
@@ -7010,7 +7002,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>67024</v>
+        <v>9629</v>
       </c>
       <c r="N73" s="5" t="n">
         <v>0</v>
@@ -7057,15 +7049,15 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPrice_A</t>
+          <t>US.CommodityPrice_M</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>1663</v>
+        <v>1899</v>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Commodity prices, 1995-2024, annual</t>
+          <t>DISCONTINUED - Commodity prices, January 1995 - June 2025, monthly</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -7080,12 +7072,12 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>commodities, price</t>
+          <t>commodity, price</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>2025-03-12T13:35:00</t>
+          <t>2025-08-11T14:32:00</t>
         </is>
       </c>
       <c r="J74" s="5" t="n">
@@ -7098,7 +7090,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>9629</v>
+        <v>84674</v>
       </c>
       <c r="N74" s="5" t="n">
         <v>0</v>
@@ -7145,15 +7137,15 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPrice_M</t>
+          <t>US.CommodityPriceIndices_A</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>1899</v>
+        <v>1662</v>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Commodity prices, January 1995 - June 2025, monthly</t>
+          <t>DISCONTINUED - UNCTAD Commodity Price Index, 1995-2024, annual (2015=100)</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -7168,12 +7160,12 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>commodity, price</t>
+          <t>commodities, price, index</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>2025-08-11T14:32:00</t>
+          <t>2025-03-12T13:35:00</t>
         </is>
       </c>
       <c r="J75" s="5" t="n">
@@ -7186,7 +7178,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>84674</v>
+        <v>4522</v>
       </c>
       <c r="N75" s="5" t="n">
         <v>0</v>
@@ -7233,15 +7225,15 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPriceIndices_A</t>
+          <t>US.CommodityPriceIndices_M</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>1662</v>
+        <v>1900</v>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - UNCTAD Commodity Price Index, 1995-2024, annual (2015=100)</t>
+          <t>DISCONTINUED - UNCTAD Commodity Price Index, January 1995 - June 2025, monthly (2015=100)</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -7256,12 +7248,12 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>commodities, price, index</t>
+          <t>commodity, price, index</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>2025-03-12T13:35:00</t>
+          <t>2025-08-11T14:32:00</t>
         </is>
       </c>
       <c r="J76" s="5" t="n">
@@ -7274,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>4522</v>
+        <v>66229</v>
       </c>
       <c r="N76" s="5" t="n">
         <v>0</v>
@@ -7321,35 +7313,35 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPriceIndices_M</t>
+          <t>US.GovExpenditures</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>1900</v>
+        <v>590</v>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - UNCTAD Commodity Price Index, January 1995 - June 2025, monthly (2015=100)</t>
+          <t>Government expenditures: By function - Annual</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Public Finance</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Economy, investment and finance &gt; Commodity prices</t>
+          <t>Economy, investment and finance &gt; Public finance</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>commodity, price, index</t>
+          <t>Government, expenditures, COFOG</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>2025-08-11T14:32:00</t>
+          <t>2023-07-18T16:51:00</t>
         </is>
       </c>
       <c r="J77" s="5" t="n">
@@ -7362,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>66229</v>
+        <v>248075</v>
       </c>
       <c r="N77" s="5" t="n">
         <v>0</v>
@@ -7409,48 +7401,48 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>US.GovExpenditures</t>
+          <t>US.BiotradeMerch</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>590</v>
+        <v>2517</v>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Government expenditures: By function - Annual</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Public Finance</t>
+          <t>Merchandise biotrade</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Economy, investment and finance &gt; Public finance</t>
+          <t>Environment and related trade &gt; Trade in biodiversity-based products</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>Government, expenditures, COFOG</t>
+          <t>Export, import, balance, value, merchandise, trade, biotrade, biodiversity, growth, rate</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>2023-07-18T16:51:00</t>
+          <t>2026-07-20T06:30:00</t>
         </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>248075</v>
+        <v>15552119339</v>
       </c>
       <c r="N78" s="5" t="n">
         <v>0</v>
@@ -7459,7 +7451,7 @@
       <c r="P78" s="4" t="inlineStr"/>
       <c r="Q78" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R78" s="4" t="inlineStr"/>
@@ -7497,20 +7489,20 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>US.BiotradeMerch</t>
+          <t>US.BioTradeMerchMarketIndices</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>2517</v>
+        <v>2124</v>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
+          <t>DISCONTINUED - Biotrade: Market concentration and structural change indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Merchandise biotrade</t>
+          <t>Environment and related trade</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -7520,25 +7512,25 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Export, import, balance, value, merchandise, trade, biotrade, biodiversity, growth, rate</t>
+          <t>Export, import, merchandise, trade, market concentration, structural change, biotrade, biodiversity</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20T06:30:00</t>
+          <t>2025-11-28T16:02:00</t>
         </is>
       </c>
       <c r="J79" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>15552119339</v>
+        <v>623798</v>
       </c>
       <c r="N79" s="5" t="n">
         <v>0</v>
@@ -7547,7 +7539,7 @@
       <c r="P79" s="4" t="inlineStr"/>
       <c r="Q79" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R79" s="4" t="inlineStr"/>
@@ -7585,15 +7577,15 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>US.BioTradeMerchMarketIndices</t>
+          <t>US.NonPlasticSubstsTradeByPartner</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>2124</v>
+        <v>2610</v>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Biotrade: Market concentration and structural change indices - Annual (analytical)</t>
+          <t>Non-plastics: Bilateral trade of non-plastic substitutes - Annual (analytical)</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -7603,30 +7595,30 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in biodiversity-based products</t>
+          <t>Environment and related trade &gt; Trade in non-plastic substitutes</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>Export, import, merchandise, trade, market concentration, structural change, biotrade, biodiversity</t>
+          <t>Plastics, trade, export, Non-plastic substitutes</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>2025-11-28T16:02:00</t>
+          <t>2026-10-02T12:38:00</t>
         </is>
       </c>
       <c r="J80" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>623798</v>
+        <v>577508294</v>
       </c>
       <c r="N80" s="5" t="n">
         <v>0</v>
@@ -7635,7 +7627,7 @@
       <c r="P80" s="4" t="inlineStr"/>
       <c r="Q80" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R80" s="4" t="inlineStr"/>
@@ -7673,35 +7665,35 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>US.NonPlasticSubstsTradeByPartner</t>
+          <t>US.OceanTrade</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>1884</v>
+        <v>2426</v>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Non-plastics: Bilateral trade of non-plastic substitutes - Annual (analytical)</t>
+          <t>Ocean goods: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade</t>
+          <t>International trade in goods and services</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in non-plastic substitutes</t>
+          <t>Environment and related trade &gt; Trade in ocean goods and services</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Plastics, trade, export, Non-plastic substitutes</t>
+          <t>Oceans, international, trade, growth, sectors, maritime, sea</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>2025-08-04T06:56:00</t>
+          <t>2026-06-08T11:51:00</t>
         </is>
       </c>
       <c r="J81" s="5" t="n">
@@ -7714,7 +7706,7 @@
         <v>1</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>511626169</v>
+        <v>572108660</v>
       </c>
       <c r="N81" s="5" t="n">
         <v>0</v>
@@ -7761,35 +7753,35 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>US.OceanTrade</t>
+          <t>US.PlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>2426</v>
+        <v>2581</v>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Ocean goods: Bilateral trade by product group - Annual (analytical)</t>
+          <t>Plastics: Bilateral trade across plastics life-cycle stages - Annual (analytical)</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>Plastics trade</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in ocean goods and services</t>
+          <t>Environment and related trade &gt; Trade in plastic-based products</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>Oceans, international, trade, growth, sectors, maritime, sea</t>
+          <t>Plastics, trade, export</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08T11:51:00</t>
+          <t>2026-09-04T12:05:00</t>
         </is>
       </c>
       <c r="J82" s="5" t="n">
@@ -7802,7 +7794,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>572108660</v>
+        <v>90879049</v>
       </c>
       <c r="N82" s="5" t="n">
         <v>0</v>
@@ -7849,15 +7841,15 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>US.PlasticsTradebyPartner</t>
+          <t>US.HiddenPlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>2581</v>
+        <v>2583</v>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Plastics: Bilateral trade across plastics life-cycle stages - Annual (analytical)</t>
+          <t>Plastics: Bilateral trade of plastic packaging, synthetic textiles and synthetic rubber - Annual (analytical)</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -7872,7 +7864,7 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Plastics, trade, export</t>
+          <t>Plastics, trade, partner, hs, product</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -7890,7 +7882,7 @@
         <v>1</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>90879049</v>
+        <v>55831373</v>
       </c>
       <c r="N83" s="5" t="n">
         <v>0</v>
@@ -7937,15 +7929,15 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>US.HiddenPlasticsTradebyPartner</t>
+          <t>US.AssociatedPlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Plastics: Bilateral trade of plastic packaging, synthetic textiles and synthetic rubber - Annual (analytical)</t>
+          <t>Plastics: Bilateral trade of plastics associated products - Annual (analytical)</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -7960,7 +7952,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>Plastics, trade, partner, hs, product</t>
+          <t>Associated plastics, trade, partner</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -7978,7 +7970,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>55831373</v>
+        <v>33181670</v>
       </c>
       <c r="N84" s="5" t="n">
         <v>0</v>
@@ -8025,48 +8017,48 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>US.AssociatedPlasticsTradebyPartner</t>
+          <t>US.TradeFoodCatByProc</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>2582</v>
+        <v>1676</v>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Plastics: Bilateral trade of plastics associated products - Annual (analytical)</t>
+          <t>Food categories: Bilateral trade by processing level - Annual (analytical)</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Plastics trade</t>
+          <t>International trade</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Environment and related trade &gt; Trade in plastic-based products</t>
+          <t>International trade &gt; Food trade by processing level</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Associated plastics, trade, partner</t>
+          <t>Food processing, food category, trade</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T12:05:00</t>
+          <t>2025-03-20T12:39:00</t>
         </is>
       </c>
       <c r="J85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K85" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>33181670</v>
+        <v>2582634489</v>
       </c>
       <c r="N85" s="5" t="n">
         <v>0</v>
@@ -8113,15 +8105,15 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodCatByProc</t>
+          <t>US.TradeFoodProcByCat</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Food categories: Bilateral trade by processing level - Annual (analytical)</t>
+          <t>Food processing: Bilateral trade by food category - Annual (analytical)</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -8154,7 +8146,7 @@
         <v>2</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>2582634489</v>
+        <v>2285091980</v>
       </c>
       <c r="N86" s="5" t="n">
         <v>0</v>
@@ -8201,48 +8193,48 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodProcByCat</t>
+          <t>US.CreativeGoodsValue</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>1677</v>
+        <v>2222</v>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Food processing: Bilateral trade by food category - Annual (analytical)</t>
+          <t>Creative goods: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>International trade</t>
+          <t>Creative economy</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Food trade by processing level</t>
+          <t>International trade &gt; Trade in creative goods and services</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Food processing, food category, trade</t>
+          <t>Creative goods, trade, exports, imports</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>2025-03-20T12:39:00</t>
+          <t>2026-04-02T15:01:00</t>
         </is>
       </c>
       <c r="J87" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K87" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>2285091980</v>
+        <v>335041684</v>
       </c>
       <c r="N87" s="5" t="n">
         <v>0</v>
@@ -8289,15 +8281,15 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeGoodsValue</t>
+          <t>US.CreativeGoodsGR</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Creative goods: Bilateral trade by product group - Annual (analytical)</t>
+          <t>Creative goods: Bilateral trade by product group - Growth rates - Annual (analytical)</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -8312,7 +8304,7 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Creative goods, trade, exports, imports</t>
+          <t>Creative goods, trade, exports, imports, growth rates</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -8330,7 +8322,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>335041684</v>
+        <v>196623315</v>
       </c>
       <c r="N88" s="5" t="n">
         <v>0</v>
@@ -8377,15 +8369,15 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeGoodsGR</t>
+          <t>US.CreativeServ_Group_E</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>2220</v>
+        <v>2072</v>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Creative goods: Bilateral trade by product group - Growth rates - Annual (analytical)</t>
+          <t>Creative services: exports of selected groups of economies - Annual (analytical)</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -8400,25 +8392,25 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Creative goods, trade, exports, imports, growth rates</t>
+          <t>Creative, services, trade, international, economy</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>2026-04-02T15:01:00</t>
+          <t>2026-04-02T15:05:00</t>
         </is>
       </c>
       <c r="J89" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>196623315</v>
+        <v>15132</v>
       </c>
       <c r="N89" s="5" t="n">
         <v>0</v>
@@ -8427,7 +8419,7 @@
       <c r="P89" s="4" t="inlineStr"/>
       <c r="Q89" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R89" s="4" t="inlineStr"/>
@@ -8465,48 +8457,48 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeServ_Group_E</t>
+          <t>US.CriticalMinerals_TradeByPart</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>2072</v>
+        <v>2502</v>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Creative services: exports of selected groups of economies - Annual (analytical)</t>
+          <t>Critical minerals: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Creative economy</t>
+          <t>International trade</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in creative goods and services</t>
+          <t>International trade &gt; Trade in critical minerals</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Creative, services, trade, international, economy</t>
+          <t>Trade, bilateral trade, exports, imports, merchandise trade, critical minerals, energy transition minerals, minerals, commodities, HS, products</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>2026-04-02T15:05:00</t>
+          <t>2026-07-14T09:51:00</t>
         </is>
       </c>
       <c r="J90" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>15132</v>
+        <v>544826561</v>
       </c>
       <c r="N90" s="5" t="n">
         <v>0</v>
@@ -8515,7 +8507,7 @@
       <c r="P90" s="4" t="inlineStr"/>
       <c r="Q90" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R90" s="4" t="inlineStr"/>
@@ -8553,15 +8545,15 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>US.CriticalMinerals_TradeByPart</t>
+          <t>US.GSTP_TradeMatrix</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>2502</v>
+        <v>2592</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Critical minerals: Bilateral trade by product group - Annual (analytical)</t>
+          <t>GSTP: Merchandise trade matrix - Annual (analytical)</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -8571,17 +8563,17 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in critical minerals</t>
+          <t>International trade &gt; Trade in merchandise</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Trade, bilateral trade, exports, imports, merchandise trade, critical minerals, energy transition minerals, minerals, commodities, HS, products</t>
+          <t>International trade, structure, partner, economy, product, group, GSTP, Global System of Trade Preferences</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14T09:51:00</t>
+          <t>2026-07-14T07:18:00</t>
         </is>
       </c>
       <c r="J91" s="5" t="n">
@@ -8594,7 +8586,7 @@
         <v>1</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>544826561</v>
+        <v>371715547</v>
       </c>
       <c r="N91" s="5" t="n">
         <v>0</v>
@@ -8641,20 +8633,20 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>US.GSTP_TradeMatrix</t>
+          <t>US.IntraTrade</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>2592</v>
+        <v>2588</v>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>GSTP: Merchandise trade matrix - Annual (analytical)</t>
+          <t>Merchandise: Intra- and extra-trade of country groups by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>International trade</t>
+          <t>International trade in goods and services</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -8664,12 +8656,12 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>International trade, structure, partner, economy, product, group, GSTP, Global System of Trade Preferences</t>
+          <t>Intra-trade, extra-trade, value, share, group, region</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14T07:18:00</t>
+          <t>2026-06-30T07:17:00</t>
         </is>
       </c>
       <c r="J92" s="5" t="n">
@@ -8682,7 +8674,7 @@
         <v>1</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>371715547</v>
+        <v>64011500</v>
       </c>
       <c r="N92" s="5" t="n">
         <v>0</v>
@@ -8729,20 +8721,20 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>US.IntraTrade</t>
+          <t>US.ConcentStructIndices</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>2588</v>
+        <v>2463</v>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Intra- and extra-trade of country groups by product - Annual (analytical)</t>
+          <t>Merchandise: Market concentration and structural change indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>International trade</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -8752,25 +8744,25 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Intra-trade, extra-trade, value, share, group, region</t>
+          <t>Indices, imports, exports, concentration, structural, trade</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30T07:17:00</t>
+          <t>2026-07-09T11:36:00</t>
         </is>
       </c>
       <c r="J93" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>64011500</v>
+        <v>210324</v>
       </c>
       <c r="N93" s="5" t="n">
         <v>0</v>
@@ -8779,7 +8771,7 @@
       <c r="P93" s="4" t="inlineStr"/>
       <c r="Q93" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R93" s="4" t="inlineStr"/>
@@ -8817,20 +8809,20 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>US.ConcentStructIndices</t>
+          <t>US.TradeMatrix</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>2463</v>
+        <v>2590</v>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Market concentration and structural change indices - Annual (analytical)</t>
+          <t>Merchandise: Trade matrix - Annual (analytical)</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>International trade</t>
+          <t>International trade in goods and services</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -8840,25 +8832,25 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Indices, imports, exports, concentration, structural, trade</t>
+          <t>International trade, structure, partner, economy, product, group</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09T11:36:00</t>
+          <t>2026-06-30T07:17:00</t>
         </is>
       </c>
       <c r="J94" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>210324</v>
+        <v>10989114010</v>
       </c>
       <c r="N94" s="5" t="n">
         <v>0</v>
@@ -8867,7 +8859,7 @@
       <c r="P94" s="4" t="inlineStr"/>
       <c r="Q94" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R94" s="4" t="inlineStr"/>
@@ -8905,15 +8897,15 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>US.TradeMatrix</t>
+          <t>US.TradePriceIndices_Q</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>2590</v>
+        <v>2487</v>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade matrix - Annual (analytical)</t>
+          <t>Merchandise: Trade price index – Quarterly (analytical)</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -8928,25 +8920,25 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>International trade, structure, partner, economy, product, group</t>
+          <t>Merchandises, Trade, Indices, Prices</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30T07:17:00</t>
+          <t>2026-07-10T15:13:00</t>
         </is>
       </c>
       <c r="J95" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>10989114010</v>
+        <v>114018</v>
       </c>
       <c r="N95" s="5" t="n">
         <v>0</v>
@@ -8955,7 +8947,7 @@
       <c r="P95" s="4" t="inlineStr"/>
       <c r="Q95" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R95" s="4" t="inlineStr"/>
@@ -8993,15 +8985,15 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>US.TradePriceIndices_Q</t>
+          <t>US.TradeServCatByPartner</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>2487</v>
+        <v>2545</v>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade price index - Quarterly (analytical)</t>
+          <t>Services: Bilateral trade by category - Annual</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -9011,30 +9003,30 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in merchandise</t>
+          <t>International trade &gt; Trade in services</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>Merchandises, Trade, Indices, Prices</t>
+          <t>services, exports, imports, trade, bilateral, partner, transport, travel, sector, category</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10T15:13:00</t>
+          <t>2026-07-23T11:34:00</t>
         </is>
       </c>
       <c r="J96" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>114018</v>
+        <v>85648480</v>
       </c>
       <c r="N96" s="5" t="n">
         <v>0</v>
@@ -9043,7 +9035,7 @@
       <c r="P96" s="4" t="inlineStr"/>
       <c r="Q96" s="4" t="inlineStr">
         <is>
-          <t>Sin valores descargados para Venezuela</t>
+          <t>Solo catalogado por tamaño de bulk</t>
         </is>
       </c>
       <c r="R96" s="4" t="inlineStr"/>
@@ -9081,48 +9073,48 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServCatByPartner</t>
+          <t>US.TransportCosts</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>2545</v>
+        <v>1107</v>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Services: Bilateral trade by category - Annual</t>
+          <t>Trade and transport: By destination, mode and product group  - Annual (analytical)</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>International trade in goods and services</t>
+          <t>International trade</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>International trade &gt; Trade in services</t>
+          <t>Maritime and other transport &gt; Global transport of merchandise trade</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>services, exports, imports, trade, bilateral, partner, transport, travel, sector, category</t>
+          <t>international, trade, transport, cost, merchandise, product, destination, origin</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T11:34:00</t>
+          <t>2024-05-22T09:00:00</t>
         </is>
       </c>
       <c r="J97" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K97" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>85648480</v>
+        <v>34008028962</v>
       </c>
       <c r="N97" s="5" t="n">
         <v>0</v>
@@ -9169,48 +9161,48 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>US.TransportCosts</t>
+          <t>US.PortCallsArrivals</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>1107</v>
+        <v>1065</v>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Trade and transport: By destination, mode and product group  - Annual (analytical)</t>
+          <t>Port calls: Calls by commercial market - Annual (analytical)</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>International trade</t>
+          <t>Maritime transport</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Global transport of merchandise trade</t>
+          <t>Maritime and other transport &gt; Port calls and performance</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>international, trade, transport, cost, merchandise, product, destination, origin</t>
+          <t>ships, port, maritime, transport, port calls, ports, time in port, vessels, services, container</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22T09:00:00</t>
+          <t>2024-03-28T16:25:00</t>
         </is>
       </c>
       <c r="J98" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>34008028962</v>
+        <v>20304</v>
       </c>
       <c r="N98" s="5" t="n">
         <v>0</v>
@@ -9219,7 +9211,7 @@
       <c r="P98" s="4" t="inlineStr"/>
       <c r="Q98" s="4" t="inlineStr">
         <is>
-          <t>Solo catalogado por tamaño de bulk</t>
+          <t>Sin valores descargados para Venezuela</t>
         </is>
       </c>
       <c r="R98" s="4" t="inlineStr"/>
@@ -9257,15 +9249,15 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>US.PortCallsArrivals</t>
+          <t>US.PortCallsArrivals_S</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Port calls: Calls by commercial market - Annual (analytical)</t>
+          <t>Port calls: Calls by commercial market - Semi-annual (analytical)</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -9298,7 +9290,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>20304</v>
+        <v>38910</v>
       </c>
       <c r="N99" s="5" t="n">
         <v>0</v>
@@ -9345,15 +9337,15 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>US.PortCallsArrivals_S</t>
+          <t>US.PortCalls</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Port calls: Calls by commercial market - Semi-annual (analytical)</t>
+          <t>Port calls: Performance indicators - Annual (analytical)</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -9373,7 +9365,7 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>2024-03-28T16:25:00</t>
+          <t>2024-03-28T16:47:00</t>
         </is>
       </c>
       <c r="J100" s="5" t="n">
@@ -9386,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>38910</v>
+        <v>19373</v>
       </c>
       <c r="N100" s="5" t="n">
         <v>0</v>
@@ -9433,15 +9425,15 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>US.PortCalls</t>
+          <t>US.PortCalls_S</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Port calls: Performance indicators - Annual (analytical)</t>
+          <t>Port calls: Performance indicators - Semi-annual (analytical)</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -9474,7 +9466,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>19373</v>
+        <v>36462</v>
       </c>
       <c r="N101" s="5" t="n">
         <v>0</v>
@@ -9521,35 +9513,35 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>US.PortCalls_S</t>
+          <t>US.Gender_DomesticValueAdded</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>1066</v>
+        <v>1315</v>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Port calls: Performance indicators - Semi-annual (analytical)</t>
+          <t>Gender: Domestic value added in gross exports by sex and broad sector - Annual (analytical)</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Maritime transport</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Maritime and other transport &gt; Port calls and performance</t>
+          <t>Population and inclusiveness &gt; Gender and trade</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>ships, port, maritime, transport, port calls, ports, time in port, vessels, services, container</t>
+          <t>Trade, gender, gap, equality, employment, earnings, wages, domestic value added, export</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>2024-03-28T16:47:00</t>
+          <t>2024-10-10T12:39:00</t>
         </is>
       </c>
       <c r="J102" s="5" t="n">
@@ -9562,7 +9554,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>36462</v>
+        <v>97680</v>
       </c>
       <c r="N102" s="5" t="n">
         <v>0</v>
@@ -9609,35 +9601,35 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>US.Gender_DomesticValueAdded</t>
+          <t>US.InclusiveGrowth</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>1315</v>
+        <v>1631</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Gender: Domestic value added in gross exports by sex and broad sector - Annual (analytical)</t>
+          <t>Inclusiveness: Inclusive growth index - Annual (analytical)</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Inclusive Growth</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Population and inclusiveness &gt; Gender and trade</t>
+          <t>Population and inclusiveness &gt; Inclusive growth</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>Trade, gender, gap, equality, employment, earnings, wages, domestic value added, export</t>
+          <t>Inclusive Growth Index, IGI, economic development, living conditions, social inclusion, environmental sustainability, equity</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>2024-10-10T12:39:00</t>
+          <t>2025-03-10T14:55:00</t>
         </is>
       </c>
       <c r="J103" s="5" t="n">
@@ -9650,7 +9642,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>97680</v>
+        <v>4221</v>
       </c>
       <c r="N103" s="5" t="n">
         <v>0</v>
@@ -9697,35 +9689,35 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>US.InclusiveGrowth</t>
+          <t>US.IFF_CrimesRelated</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>1631</v>
+        <v>2492</v>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Inclusiveness: Inclusive growth index - Annual (analytical)</t>
+          <t>Indicator 16.4.1: Crime-related illicit financial flows, IFFs - Annual</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Inclusive Growth</t>
+          <t>SDG Indicators</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>Population and inclusiveness &gt; Inclusive growth</t>
+          <t>SDG Indicators &gt; Goal 16</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>Inclusive Growth Index, IGI, economic development, living conditions, social inclusion, environmental sustainability, equity</t>
+          <t>IFF, crime-related, Drug, smuggling, trafficking, SDG 16.4.1, financial, inwards</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>2025-03-10T14:55:00</t>
+          <t>2026-06-09T09:17:00</t>
         </is>
       </c>
       <c r="J104" s="5" t="n">
@@ -9738,7 +9730,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>4221</v>
+        <v>2046</v>
       </c>
       <c r="N104" s="5" t="n">
         <v>0</v>
@@ -9785,15 +9777,15 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>US.IFF_CrimesRelated</t>
+          <t>US.IFF_TradeMisinvoicing</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Indicator 16.4.1: Crime-related illicit financial flows, IFFs - Annual</t>
+          <t xml:space="preserve">Indicator 16.4.1: Trade misinvoicing illicit financial flows, IFFs - Annual </t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -9808,7 +9800,7 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>IFF, crime-related, Drug, smuggling, trafficking, SDG 16.4.1, financial, inwards</t>
+          <t>IFF, IFFs, Trade, misinvoicing, SDG, Tax, SDG</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
@@ -9826,7 +9818,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>2046</v>
+        <v>3342</v>
       </c>
       <c r="N105" s="5" t="n">
         <v>0</v>
@@ -9855,94 +9847,6 @@
         </is>
       </c>
       <c r="V105" s="4" t="inlineStr">
-        <is>
-          <t>https://unctadstat.unctad.org/datacentre/</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>UNCTADstat - UNCTAD</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela (Bolivarian Rep. of)</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>US.IFF_TradeMisinvoicing</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="n">
-        <v>2493</v>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Indicator 16.4.1: Trade misinvoicing illicit financial flows, IFFs - Annual </t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>SDG Indicators</t>
-        </is>
-      </c>
-      <c r="G106" s="4" t="inlineStr">
-        <is>
-          <t>SDG Indicators &gt; Goal 16</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>IFF, IFFs, Trade, misinvoicing, SDG, Tax, SDG</t>
-        </is>
-      </c>
-      <c r="I106" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09T09:17:00</t>
-        </is>
-      </c>
-      <c r="J106" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K106" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="5" t="n">
-        <v>3342</v>
-      </c>
-      <c r="N106" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" s="4" t="inlineStr"/>
-      <c r="P106" s="4" t="inlineStr"/>
-      <c r="Q106" s="4" t="inlineStr">
-        <is>
-          <t>Sin valores descargados para Venezuela</t>
-        </is>
-      </c>
-      <c r="R106" s="4" t="inlineStr"/>
-      <c r="S106" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/unctad/csv/ove_unctadstat_venezuela_valores.csv.gz</t>
-        </is>
-      </c>
-      <c r="T106" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/unctad/catalog/unctad-catalog.json</t>
-        </is>
-      </c>
-      <c r="U106" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx</t>
-        </is>
-      </c>
-      <c r="V106" s="4" t="inlineStr">
         <is>
           <t>https://unctadstat.unctad.org/datacentre/</t>
         </is>
@@ -9960,7 +9864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10071,7 +9975,7 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>424083</v>
+        <v>579937</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
@@ -10082,7 +9986,7 @@
         <v>156</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>312</v>
+        <v>466</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -10098,26 +10002,26 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>US.TradeMerchGR</t>
+          <t>US.TradeMerchBalance</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade - Growth rates - Annual</t>
+          <t>Merchandise: Trade balance - Annual</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>US_TradeMerchGR</t>
+          <t>US_TradeMerchBalance</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>The whole dataset</t>
+          <t>From 1948 to 2025</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>214725</v>
+        <v>239425</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
@@ -10125,14 +10029,14 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMerchGR/US_TradeMerchGR</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMerchBalance/US_TradeMerchBalance</t>
         </is>
       </c>
     </row>
@@ -10144,26 +10048,26 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>US.TradeMerchBalance</t>
+          <t>US.MerchVolumeQuarterly</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade balance - Annual</t>
+          <t>Merchandise: Trade volume - Growth rates - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>US_TradeMerchBalance</t>
+          <t>US_MerchVolumeQuarterly</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>From 1948 to 2025</t>
+          <t>From 2005 to 2026</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>235857</v>
+        <v>644857</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
@@ -10171,14 +10075,14 @@
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>156</v>
+        <v>848</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMerchBalance/US_TradeMerchBalance</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.MerchVolumeQuarterly/US_MerchVolumeQuarterly</t>
         </is>
       </c>
     </row>
@@ -10190,41 +10094,41 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>US.MerchVolumeQuarterly</t>
+          <t>US.TradeMatrix</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade volume - Growth rates - Quarterly (analytical)</t>
+          <t>Merchandise: Trade matrix - Annual (analytical)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>US_MerchVolumeQuarterly</t>
+          <t>US_TradeMatrix_19952000</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2026</t>
+          <t>From 1995 to 2000</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>639637</v>
+        <v>1768893604</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>838</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.MerchVolumeQuarterly/US_MerchVolumeQuarterly</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMatrix/US_TradeMatrix_19952000</t>
         </is>
       </c>
     </row>
@@ -10246,16 +10150,16 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>US_TradeMatrix_19952000</t>
+          <t>US_TradeMatrix_20012005</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2000</t>
+          <t>From 2001 to 2005</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1768893604</v>
+        <v>1679341616</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
@@ -10270,7 +10174,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMatrix/US_TradeMatrix_19952000</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMatrix/US_TradeMatrix_20012005</t>
         </is>
       </c>
     </row>
@@ -10292,16 +10196,16 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>US_TradeMatrix_20012005</t>
+          <t>US_TradeMatrix_20062010</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>From 2001 to 2005</t>
+          <t>From 2006 to 2010</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1679341616</v>
+        <v>1811298102</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
@@ -10316,7 +10220,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMatrix/US_TradeMatrix_20012005</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMatrix/US_TradeMatrix_20062010</t>
         </is>
       </c>
     </row>
@@ -10338,16 +10242,16 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>US_TradeMatrix_20062010</t>
+          <t>US_TradeMatrix_20112015</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>From 2006 to 2010</t>
+          <t>From 2011 to 2015</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1811298102</v>
+        <v>1855996657</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
@@ -10362,7 +10266,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMatrix/US_TradeMatrix_20062010</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMatrix/US_TradeMatrix_20112015</t>
         </is>
       </c>
     </row>
@@ -10384,16 +10288,16 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>US_TradeMatrix_20112015</t>
+          <t>US_TradeMatrix_20162020</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>From 2011 to 2015</t>
+          <t>From 2016 to 2020</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1855996657</v>
+        <v>1903921630</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
@@ -10408,7 +10312,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMatrix/US_TradeMatrix_20112015</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMatrix/US_TradeMatrix_20162020</t>
         </is>
       </c>
     </row>
@@ -10430,16 +10334,16 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>US_TradeMatrix_20162020</t>
+          <t>US_TradeMatrix_20212025</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>From 2016 to 2020</t>
+          <t>From 2021 to 2025</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1903921630</v>
+        <v>1969662401</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
@@ -10454,7 +10358,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMatrix/US_TradeMatrix_20162020</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMatrix/US_TradeMatrix_20212025</t>
         </is>
       </c>
     </row>
@@ -10466,41 +10370,41 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>US.TradeMatrix</t>
+          <t>US.TermsOfTrade</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade matrix - Annual (analytical)</t>
+          <t>Merchandise: Trade indicators - Annual (analytical)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>US_TradeMatrix_20212025</t>
+          <t>US_TermsOfTrade</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>From 2021 to 2025</t>
+          <t>From 2005 to 2025</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>1969662401</v>
+        <v>304595</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeMatrix/US_TradeMatrix_20212025</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TermsOfTrade/US_TermsOfTrade</t>
         </is>
       </c>
     </row>
@@ -10512,41 +10416,41 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>US.TermsOfTrade</t>
+          <t>US.IntraTrade</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade indicators - Annual (analytical)</t>
+          <t>Merchandise: Intra- and extra-trade of country groups by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>US_TermsOfTrade</t>
+          <t>US_IntraTrade</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2025</t>
+          <t>From 1995 to 2025</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>304595</v>
+        <v>64011500</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TermsOfTrade/US_TermsOfTrade</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IntraTrade/US_IntraTrade</t>
         </is>
       </c>
     </row>
@@ -10558,30 +10462,30 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>US.IntraTrade</t>
+          <t>US.TradePriceIndices_Q</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Intra- and extra-trade of country groups by product - Annual (analytical)</t>
+          <t>Merchandise: Trade price index – Quarterly (analytical)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>US_IntraTrade</t>
+          <t>US_TradePriceIndices_Q</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2025</t>
+          <t>From 2005 to 2026</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>64011500</v>
+        <v>114018</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -10592,7 +10496,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IntraTrade/US_IntraTrade</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradePriceIndices_Q/US_TradePriceIndices_Q</t>
         </is>
       </c>
     </row>
@@ -10604,26 +10508,26 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>US.TradePriceIndices_Q</t>
+          <t>US.ConcentDiversIndices</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Trade price index - Quarterly (analytical)</t>
+          <t>Merchandise: Standard product concentration and diversification indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>US_TradePriceIndices_Q</t>
+          <t>US_ConcentDiversIndices</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2026</t>
+          <t>From 1995 to 2025</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>114018</v>
+        <v>189457</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
@@ -10631,14 +10535,14 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradePriceIndices_Q/US_TradePriceIndices_Q</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ConcentDiversIndices/US_ConcentDiversIndices</t>
         </is>
       </c>
     </row>
@@ -10650,17 +10554,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>US.ConcentDiversIndices</t>
+          <t>US.ConcentStructIndices</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Standard product concentration and diversification indices - Annual (analytical)</t>
+          <t>Merchandise: Market concentration and structural change indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>US_ConcentDiversIndices</t>
+          <t>US_ConcentStructIndices</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -10669,7 +10573,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>189457</v>
+        <v>210324</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
@@ -10677,14 +10581,14 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ConcentDiversIndices/US_ConcentDiversIndices</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ConcentStructIndices/US_ConcentStructIndices</t>
         </is>
       </c>
     </row>
@@ -10696,26 +10600,26 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>US.ConcentStructIndices</t>
+          <t>US.MerchTheilIndices</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Market concentration and structural change indices - Annual (analytical)</t>
+          <t>Merchandise: Theil indices of product and market concentration - Annual (analytical)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>US_ConcentStructIndices</t>
+          <t>US_MerchTheilIndices</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2025</t>
+          <t>From 1995 to 2024</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>210324</v>
+        <v>353039</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -10723,14 +10627,14 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ConcentStructIndices/US_ConcentStructIndices</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.MerchTheilIndices/US_MerchTheilIndices</t>
         </is>
       </c>
     </row>
@@ -10742,26 +10646,26 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>US.MerchTheilIndices</t>
+          <t>US.RCA</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Theil indices of product and market concentration - Annual (analytical)</t>
+          <t>Merchandise: Revealed comparative advantage index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>US_MerchTheilIndices</t>
+          <t>US_RCA</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2024</t>
+          <t>From 1995 to 2025</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>353039</v>
+        <v>8931393</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
@@ -10769,14 +10673,14 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>180</v>
+        <v>7772</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>180</v>
+        <v>7772</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.MerchTheilIndices/US_MerchTheilIndices</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.RCA/US_RCA</t>
         </is>
       </c>
     </row>
@@ -10788,26 +10692,26 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>US.RCA</t>
+          <t>US.Tariff</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Revealed comparative advantage index - Annual (analytical)</t>
+          <t>Merchandise: Import tariff rates - Annual</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>US_RCA</t>
+          <t>US_Tariff</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2025</t>
+          <t>From 2019 to 2024</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>8931393</v>
+        <v>521218</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
@@ -10815,14 +10719,14 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>7772</v>
+        <v>230</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>7772</v>
+        <v>460</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.RCA/US_RCA</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Tariff/US_Tariff</t>
         </is>
       </c>
     </row>
@@ -10834,41 +10738,41 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>US.Tariff</t>
+          <t>US.GSTP_TradeMatrix</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Merchandise: Import tariff rates - Annual</t>
+          <t>GSTP: Merchandise trade matrix - Annual (analytical)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>US_Tariff</t>
+          <t>US_GSTP_TradeMatrix</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>From 2019 to 2024</t>
+          <t>From 1995 to 2025</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>521218</v>
+        <v>371715547</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Tariff/US_Tariff</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GSTP_TradeMatrix/US_GSTP_TradeMatrix</t>
         </is>
       </c>
     </row>
@@ -10880,41 +10784,41 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>US.GSTP_TradeMatrix</t>
+          <t>US.TotAndComServicesQuarterly</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>GSTP: Merchandise trade matrix - Annual (analytical)</t>
+          <t>Services: Trade by main category - Quarterly</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>US_GSTP_TradeMatrix</t>
+          <t>US_TotAndComServicesQuarterly</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2025</t>
+          <t>From 2005 to 2026</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>371715547</v>
+        <v>4997704</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0</v>
+        <v>3610</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GSTP_TradeMatrix/US_GSTP_TradeMatrix</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TotAndComServicesQuarterly/US_TotAndComServicesQuarterly</t>
         </is>
       </c>
     </row>
@@ -10926,26 +10830,26 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>US.TotAndComServicesQuarterly</t>
+          <t>US.TradeServCatTotal</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Services: Trade by main category - Quarterly</t>
+          <t>Services: Trade by category - Annual</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>US_TotAndComServicesQuarterly</t>
+          <t>US_TradeServCatTotal</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2026</t>
+          <t>From 2005 to 2025</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>4997704</v>
+        <v>10102418</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
@@ -10953,14 +10857,14 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>1750</v>
+        <v>2949</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>3610</v>
+        <v>4793</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TotAndComServicesQuarterly/US_TotAndComServicesQuarterly</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServCatTotal/US_TradeServCatTotal</t>
         </is>
       </c>
     </row>
@@ -10972,17 +10876,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServCatTotal</t>
+          <t>US.TradeServCatByPartner</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Services: Trade by category - Annual</t>
+          <t>Services: Bilateral trade by category - Annual</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>US_TradeServCatTotal</t>
+          <t>US_TradeServCatByPartner</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -10991,22 +10895,22 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>10102418</v>
+        <v>85648480</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>2949</v>
+        <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>4793</v>
+        <v>0</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServCatTotal/US_TradeServCatTotal</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServCatByPartner/US_TradeServCatByPartner</t>
         </is>
       </c>
     </row>
@@ -11018,26 +10922,26 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServCatByPartner</t>
+          <t>US.CreativeGoodsValue</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Services: Bilateral trade by category - Annual</t>
+          <t>Creative goods: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>US_TradeServCatByPartner</t>
+          <t>US_CreativeGoodsValue</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2025</t>
+          <t>From 2002 to 2024</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>85648480</v>
+        <v>335041684</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
@@ -11052,7 +10956,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServCatByPartner/US_TradeServCatByPartner</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeGoodsValue/US_CreativeGoodsValue</t>
         </is>
       </c>
     </row>
@@ -11064,26 +10968,26 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeGoodsValue</t>
+          <t>US.CreativeGoodsGR</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Creative goods: Bilateral trade by product group - Annual (analytical)</t>
+          <t>Creative goods: Bilateral trade by product group - Growth rates - Annual (analytical)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>US_CreativeGoodsValue</t>
+          <t>US_CreativeGoodsGR</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>From 2002 to 2024</t>
+          <t>The whole dataset</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>335041684</v>
+        <v>196623315</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -11098,7 +11002,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeGoodsValue/US_CreativeGoodsValue</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeGoodsGR/US_CreativeGoodsGR</t>
         </is>
       </c>
     </row>
@@ -11110,41 +11014,41 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeGoodsGR</t>
+          <t>US.CreativeServ_Indiv_Tot</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Creative goods: Bilateral trade by product group - Growth rates - Annual (analytical)</t>
+          <t>Creative services: Trade - Annual (analytical)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>US_CreativeGoodsGR</t>
+          <t>US_CreativeServ_Indiv_Tot</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>The whole dataset</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>196623315</v>
+        <v>62133</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeGoodsGR/US_CreativeGoodsGR</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeServ_Indiv_Tot/US_CreativeServ_Indiv_Tot</t>
         </is>
       </c>
     </row>
@@ -11156,17 +11060,17 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeServ_Indiv_Tot</t>
+          <t>US.CreativeServ_Group_E</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Creative services: Trade - Annual (analytical)</t>
+          <t>Creative services: exports of selected groups of economies - Annual (analytical)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>US_CreativeServ_Indiv_Tot</t>
+          <t>US_CreativeServ_Group_E</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -11175,7 +11079,7 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>62133</v>
+        <v>15132</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
@@ -11183,14 +11087,14 @@
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeServ_Indiv_Tot/US_CreativeServ_Indiv_Tot</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeServ_Group_E/US_CreativeServ_Group_E</t>
         </is>
       </c>
     </row>
@@ -11202,30 +11106,30 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>US.CreativeServ_Group_E</t>
+          <t>US.CriticalMinerals_TradeByPart</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Creative services: exports of selected groups of economies - Annual (analytical)</t>
+          <t>Critical minerals: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>US_CreativeServ_Group_E</t>
+          <t>US_CriticalMinerals_TradeByPart</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2002 to 2024</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>15132</v>
+        <v>544826561</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -11236,7 +11140,7 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CreativeServ_Group_E/US_CreativeServ_Group_E</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CriticalMinerals_TradeByPart/US_CriticalMinerals_TradeByPart</t>
         </is>
       </c>
     </row>
@@ -11248,26 +11152,26 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>US.CriticalMinerals_TradeByPart</t>
+          <t>US.TradeFoodCatByProc</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Critical minerals: Bilateral trade by product group - Annual (analytical)</t>
+          <t>Food categories: Bilateral trade by processing level - Annual (analytical)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>US_CriticalMinerals_TradeByPart</t>
+          <t>US_TradeFoodCatByProc_19952009</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>From 2002 to 2024</t>
+          <t>From 1995 to 2009</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>544826561</v>
+        <v>1242404356</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
@@ -11282,7 +11186,7 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CriticalMinerals_TradeByPart/US_CriticalMinerals_TradeByPart</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodCatByProc/US_TradeFoodCatByProc_19952009</t>
         </is>
       </c>
     </row>
@@ -11304,16 +11208,16 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>US_TradeFoodCatByProc_19952009</t>
+          <t>US_TradeFoodCatByProc_20102023</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2009</t>
+          <t>From 2010 to 2023</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>1242404356</v>
+        <v>1340230133</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
@@ -11328,7 +11232,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodCatByProc/US_TradeFoodCatByProc_19952009</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodCatByProc/US_TradeFoodCatByProc_20102023</t>
         </is>
       </c>
     </row>
@@ -11340,41 +11244,41 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodCatByProc</t>
+          <t>US.TradeFoodProcCat_Cat_RCA</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Food categories: Bilateral trade by processing level - Annual (analytical)</t>
+          <t>Food categories: Revealed comparative advantage index by processing level - Annual (analytical)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>US_TradeFoodCatByProc_20102023</t>
+          <t>US_TradeFoodProcCat_Cat_RCA</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2023</t>
+          <t>From 1995 to 2023</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>1340230133</v>
+        <v>3467211</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0</v>
+        <v>2589</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>0</v>
+        <v>2589</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodCatByProc/US_TradeFoodCatByProc_20102023</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcCat_Cat_RCA/US_TradeFoodProcCat_Cat_RCA</t>
         </is>
       </c>
     </row>
@@ -11386,41 +11290,41 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodProcCat_Cat_RCA</t>
+          <t>US.TradeFoodProcByCat</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Food categories: Revealed comparative advantage index by processing level - Annual (analytical)</t>
+          <t>Food processing: Bilateral trade by food category - Annual (analytical)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>US_TradeFoodProcCat_Cat_RCA</t>
+          <t>US_TradeFoodProcByCat_19952009</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2023</t>
+          <t>From 1995 to 2009</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>3467211</v>
+        <v>1099284426</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>2589</v>
+        <v>0</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>2589</v>
+        <v>0</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcCat_Cat_RCA/US_TradeFoodProcCat_Cat_RCA</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcByCat/US_TradeFoodProcByCat_19952009</t>
         </is>
       </c>
     </row>
@@ -11442,16 +11346,16 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>US_TradeFoodProcByCat_19952009</t>
+          <t>US_TradeFoodProcByCat_20102023</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2009</t>
+          <t>From 2010 to 2023</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>1099284426</v>
+        <v>1185807554</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
@@ -11466,7 +11370,7 @@
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcByCat/US_TradeFoodProcByCat_19952009</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcByCat/US_TradeFoodProcByCat_20102023</t>
         </is>
       </c>
     </row>
@@ -11478,41 +11382,41 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodProcByCat</t>
+          <t>US.TradeFoodProcCat_Proc_RCA</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Food processing: Bilateral trade by food category - Annual (analytical)</t>
+          <t>Food processing: Revealed comparative advantage index by food category - Annual (analytical)</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>US_TradeFoodProcByCat_20102023</t>
+          <t>US_TradeFoodProcCat_Proc_RCA</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2023</t>
+          <t>From 1995 to 2023</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>1185807554</v>
+        <v>3796561</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0</v>
+        <v>2845</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>0</v>
+        <v>2845</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcByCat/US_TradeFoodProcByCat_20102023</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcCat_Proc_RCA/US_TradeFoodProcCat_Proc_RCA</t>
         </is>
       </c>
     </row>
@@ -11524,26 +11428,26 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>US.TradeFoodProcCat_Proc_RCA</t>
+          <t>US.GDPTotal</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Food processing: Revealed comparative advantage index by food category - Annual (analytical)</t>
+          <t>Gross domestic product: Total and per capita - Annual</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>US_TradeFoodProcCat_Proc_RCA</t>
+          <t>US_GDPTotal</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2023</t>
+          <t>From 1970 to 2025</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>3796561</v>
+        <v>425702</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
@@ -11551,14 +11455,14 @@
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>2845</v>
+        <v>56</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>2845</v>
+        <v>332</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeFoodProcCat_Proc_RCA/US_TradeFoodProcCat_Proc_RCA</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GDPTotal/US_GDPTotal</t>
         </is>
       </c>
     </row>
@@ -11570,26 +11474,26 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>US.GDPTotal</t>
+          <t>US.GDPComponent</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product: Total and per capita - Annual</t>
+          <t>Gross domestic product: By expenditure and by sector - Annual</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>US_GDPTotal</t>
+          <t>US_GDPComponent</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>From 1970 to 2025</t>
+          <t>From 1970 to 2024</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>425702</v>
+        <v>4425120</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
@@ -11597,14 +11501,14 @@
         </is>
       </c>
       <c r="H40" s="5" t="n">
-        <v>56</v>
+        <v>1045</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>332</v>
+        <v>3135</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GDPTotal/US_GDPTotal</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GDPComponent/US_GDPComponent</t>
         </is>
       </c>
     </row>
@@ -11616,26 +11520,26 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>US.GDPComponent</t>
+          <t>US.GNI</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product: By expenditure and by sector - Annual</t>
+          <t>DISCONTINUED - Nominal GNI, total and per capita, annual</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>US_GDPComponent</t>
+          <t>US_GNI</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>From 1970 to 2024</t>
+          <t>The whole period</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>4425120</v>
+        <v>145178</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
@@ -11643,14 +11547,14 @@
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>1045</v>
+        <v>51</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>3135</v>
+        <v>102</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GDPComponent/US_GDPComponent</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GNI/US_GNI</t>
         </is>
       </c>
     </row>
@@ -11662,26 +11566,26 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>US.GNI</t>
+          <t>US.GoodsAndServicesBpm6</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Nominal GNI, total and per capita, annual</t>
+          <t>Balance of payments: Goods and services trade - Annual</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>US_GNI</t>
+          <t>US_GoodsAndServicesBpm6</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>The whole period</t>
+          <t>From 2005 to 2025</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>145178</v>
+        <v>380006</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
@@ -11689,14 +11593,14 @@
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GNI/US_GNI</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GoodsAndServicesBpm6/US_GoodsAndServicesBpm6</t>
         </is>
       </c>
     </row>
@@ -11708,17 +11612,17 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>US.GoodsAndServicesBpm6</t>
+          <t>US.GoodsAndServBalanceBpm6</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Balance of payments: Goods and services trade - Annual</t>
+          <t>Balance of payments: Goods and services trade balance indicators - Annual</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>US_GoodsAndServicesBpm6</t>
+          <t>US_GoodsAndServBalanceBpm6</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -11727,7 +11631,7 @@
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>380006</v>
+        <v>321969</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
@@ -11735,14 +11639,14 @@
         </is>
       </c>
       <c r="H43" s="5" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GoodsAndServicesBpm6/US_GoodsAndServicesBpm6</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GoodsAndServBalanceBpm6/US_GoodsAndServBalanceBpm6</t>
         </is>
       </c>
     </row>
@@ -11754,17 +11658,17 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>US.GoodsAndServBalanceBpm6</t>
+          <t>US.GoodsAndServTradeOpennessBpm6</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Balance of payments: Goods and services trade balance indicators - Annual</t>
+          <t>Balance of payments: Goods and services trade openness indicators - Annual</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>US_GoodsAndServBalanceBpm6</t>
+          <t>US_GoodsAndServTradeOpennessBpm6</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -11773,7 +11677,7 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>321969</v>
+        <v>903326</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
@@ -11781,14 +11685,14 @@
         </is>
       </c>
       <c r="H44" s="5" t="n">
-        <v>63</v>
+        <v>252</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GoodsAndServBalanceBpm6/US_GoodsAndServBalanceBpm6</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GoodsAndServTradeOpennessBpm6/US_GoodsAndServTradeOpennessBpm6</t>
         </is>
       </c>
     </row>
@@ -11800,26 +11704,26 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>US.GoodsAndServTradeOpennessBpm6</t>
+          <t>US.CurrAccBalance</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Balance of payments: Goods and services trade openness indicators - Annual</t>
+          <t>Balance of payments: Current account balance - Annual</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>US_GoodsAndServTradeOpennessBpm6</t>
+          <t>US_CurrAccBalance</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2025</t>
+          <t>From 1980 to 2025</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>903326</v>
+        <v>125296</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
@@ -11827,14 +11731,14 @@
         </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>252</v>
+        <v>46</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>360</v>
+        <v>92</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GoodsAndServTradeOpennessBpm6/US_GoodsAndServTradeOpennessBpm6</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CurrAccBalance/US_CurrAccBalance</t>
         </is>
       </c>
     </row>
@@ -11846,26 +11750,26 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>US.CurrAccBalance</t>
+          <t>US.Remittances</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Balance of payments: Current account balance - Annual</t>
+          <t xml:space="preserve">Balance of payments: Personal remittances - Annual </t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>US_CurrAccBalance</t>
+          <t>US_Remittances</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>From 1980 to 2025</t>
+          <t>From 2000 to 2024</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>125296</v>
+        <v>69641</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
@@ -11873,14 +11777,14 @@
         </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CurrAccBalance/US_CurrAccBalance</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Remittances/US_Remittances</t>
         </is>
       </c>
     </row>
@@ -11892,26 +11796,26 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>US.Remittances</t>
+          <t>US.FdiFlowsStock</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Balance of payments: Personal remittances - Annual </t>
+          <t>Investment: Foreign direct investment - Annual</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>US_Remittances</t>
+          <t>US_FdiFlowsStock</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2024</t>
+          <t>From 1990 to 2025</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>69641</v>
+        <v>676265</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
@@ -11919,14 +11823,14 @@
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>40</v>
+        <v>576</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Remittances/US_Remittances</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FdiFlowsStock/US_FdiFlowsStock</t>
         </is>
       </c>
     </row>
@@ -11938,26 +11842,26 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>US.FdiFlowsStock</t>
+          <t>US.PCI</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Investment: Foreign direct investment - Annual</t>
+          <t>Structural transformation: Productive Capacities Index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>US_FdiFlowsStock</t>
+          <t>US_PCI</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>From 1990 to 2025</t>
+          <t>From 2000 to 2024</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>676265</v>
+        <v>292674</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
@@ -11965,14 +11869,14 @@
         </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>144</v>
+        <v>225</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>576</v>
+        <v>225</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FdiFlowsStock/US_FdiFlowsStock</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PCI/US_PCI</t>
         </is>
       </c>
     </row>
@@ -11984,26 +11888,26 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>US.PCI</t>
+          <t>US.Cpi_A</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Structural transformation: Productive Capacities Index - Annual (analytical)</t>
+          <t>Inflation: Consumer price index - Annual</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>US_PCI</t>
+          <t>US_Cpi_A</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2024</t>
+          <t>From 1980 to 2025</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>292674</v>
+        <v>81423</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
@@ -12011,14 +11915,14 @@
         </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>225</v>
+        <v>46</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>225</v>
+        <v>91</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PCI/US_PCI</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Cpi_A/US_Cpi_A</t>
         </is>
       </c>
     </row>
@@ -12030,26 +11934,26 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>US.Cpi_A</t>
+          <t>US.ExchangeRateCrosstab</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Inflation: Consumer price index - Annual</t>
+          <t>Exchange rates: Currency cross rates - Annual</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>US_Cpi_A</t>
+          <t>US_ExchangeRateCrosstab</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>From 1980 to 2025</t>
+          <t>From 1970 to 2025</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>81423</v>
+        <v>18056762</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
@@ -12057,14 +11961,14 @@
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>46</v>
+        <v>26488</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>91</v>
+        <v>23205</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Cpi_A/US_Cpi_A</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ExchangeRateCrosstab/US_ExchangeRateCrosstab</t>
         </is>
       </c>
     </row>
@@ -12076,26 +11980,26 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>US.ExchangeRateCrosstab</t>
+          <t>US.UCPI_A</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Exchange rates: Currency cross rates - Annual</t>
+          <t>Commodity prices: UNCTAD Commodity Price Index - Annual</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>US_ExchangeRateCrosstab</t>
+          <t>US_UCPI_A</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>From 1970 to 2025</t>
+          <t>From 1995 to 2025</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>18056762</v>
+        <v>4615</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
@@ -12103,14 +12007,14 @@
         </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>26488</v>
+        <v>0</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>23205</v>
+        <v>0</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ExchangeRateCrosstab/US_ExchangeRateCrosstab</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.UCPI_A/US_UCPI_A</t>
         </is>
       </c>
     </row>
@@ -12122,26 +12026,26 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>US.UCPI_A</t>
+          <t>US.UCPI_M</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Commodity prices: UNCTAD Commodity Price Index - Annual</t>
+          <t>Commodity prices: UNCTAD Commodity Price Index - Monthly</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>US_UCPI_A</t>
+          <t>US_UCPI_M</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2025</t>
+          <t>From 1995 to 2026</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>4615</v>
+        <v>67024</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
@@ -12156,7 +12060,7 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.UCPI_A/US_UCPI_A</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.UCPI_M/US_UCPI_M</t>
         </is>
       </c>
     </row>
@@ -12168,26 +12072,26 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>US.UCPI_M</t>
+          <t>US.CommodityPriceIndices_A</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Commodity prices: UNCTAD Commodity Price Index - Monthly</t>
+          <t>DISCONTINUED - UNCTAD Commodity Price Index, 1995-2024, annual (2015=100)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>US_UCPI_M</t>
+          <t>US_CommodityPriceIndices_A</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2026</t>
+          <t>From 1995 to 2025</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>67024</v>
+        <v>4522</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
@@ -12202,7 +12106,7 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.UCPI_M/US_UCPI_M</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPriceIndices_A/US_CommodityPriceIndices_A</t>
         </is>
       </c>
     </row>
@@ -12214,17 +12118,17 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPriceIndices_A</t>
+          <t>US.CommodityPriceIndices_M</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - UNCTAD Commodity Price Index, 1995-2024, annual (2015=100)</t>
+          <t>DISCONTINUED - UNCTAD Commodity Price Index, January 1995 - June 2025, monthly (2015=100)</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>US_CommodityPriceIndices_A</t>
+          <t>US_CommodityPriceIndices_M</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -12233,7 +12137,7 @@
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>4522</v>
+        <v>66229</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
@@ -12248,7 +12152,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPriceIndices_A/US_CommodityPriceIndices_A</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPriceIndices_M/US_CommodityPriceIndices_M</t>
         </is>
       </c>
     </row>
@@ -12260,17 +12164,17 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPriceIndices_M</t>
+          <t>US.CommodityPrice_A</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - UNCTAD Commodity Price Index, January 1995 - June 2025, monthly (2015=100)</t>
+          <t>DISCONTINUED - Commodity prices, 1995-2024, annual</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>US_CommodityPriceIndices_M</t>
+          <t>US_CommodityPrice_A</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -12279,7 +12183,7 @@
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>66229</v>
+        <v>9629</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
@@ -12294,7 +12198,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPriceIndices_M/US_CommodityPriceIndices_M</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPrice_A/US_CommodityPrice_A</t>
         </is>
       </c>
     </row>
@@ -12306,17 +12210,17 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPrice_A</t>
+          <t>US.CommodityPrice_M</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Commodity prices, 1995-2024, annual</t>
+          <t>DISCONTINUED - Commodity prices, January 1995 - June 2025, monthly</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>US_CommodityPrice_A</t>
+          <t>US_CommodityPrice_M</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -12325,7 +12229,7 @@
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>9629</v>
+        <v>84674</v>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
@@ -12340,7 +12244,7 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPrice_A/US_CommodityPrice_A</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPrice_M/US_CommodityPrice_M</t>
         </is>
       </c>
     </row>
@@ -12352,26 +12256,26 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>US.CommodityPrice_M</t>
+          <t>US.GovExpenditures</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Commodity prices, January 1995 - June 2025, monthly</t>
+          <t>Government expenditures: By function - Annual</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>US_CommodityPrice_M</t>
+          <t>US_GovExpenditures</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2025</t>
+          <t>The whole period</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>84674</v>
+        <v>248075</v>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
@@ -12386,7 +12290,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.CommodityPrice_M/US_CommodityPrice_M</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GovExpenditures/US_GovExpenditures</t>
         </is>
       </c>
     </row>
@@ -12398,26 +12302,26 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>US.GovExpenditures</t>
+          <t>US.MerchantFleet</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Government expenditures: By function - Annual</t>
+          <t>Merchant fleet: By flag of registration and ship type - Annual (analytical)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>US_GovExpenditures</t>
+          <t>US_MerchantFleet</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>The whole period</t>
+          <t>From 1980 to 2026</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>248075</v>
+        <v>938045</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
@@ -12425,14 +12329,14 @@
         </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>0</v>
+        <v>1102</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.GovExpenditures/US_GovExpenditures</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.MerchantFleet/US_MerchantFleet</t>
         </is>
       </c>
     </row>
@@ -12444,26 +12348,26 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>US.MerchantFleet</t>
+          <t>US.FleetBeneficialOwners</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: By flag of registration and ship type - Annual (analytical)</t>
+          <t>Merchant fleet: By beneficial ownership - Annual (analytical)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>US_MerchantFleet</t>
+          <t>US_FleetBeneficialOwners</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>From 1980 to 2026</t>
+          <t>From 2014 to 2026</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>938045</v>
+        <v>412428</v>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
@@ -12471,14 +12375,14 @@
         </is>
       </c>
       <c r="H59" s="5" t="n">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>1102</v>
+        <v>897</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.MerchantFleet/US_MerchantFleet</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FleetBeneficialOwners/US_FleetBeneficialOwners</t>
         </is>
       </c>
     </row>
@@ -12490,26 +12394,26 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>US.FleetBeneficialOwners</t>
+          <t>US.VesselValueByRegistration</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: By beneficial ownership - Annual (analytical)</t>
+          <t>Merchant fleet: Share by flag of registration - Annual (analytical)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>US_FleetBeneficialOwners</t>
+          <t>US_VesselValueByRegistration</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>From 2014 to 2026</t>
+          <t>From 2019 to 2026</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>412428</v>
+        <v>9782</v>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
@@ -12517,14 +12421,14 @@
         </is>
       </c>
       <c r="H60" s="5" t="n">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>897</v>
+        <v>8</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FleetBeneficialOwners/US_FleetBeneficialOwners</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.VesselValueByRegistration/US_VesselValueByRegistration</t>
         </is>
       </c>
     </row>
@@ -12536,17 +12440,17 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>US.VesselValueByRegistration</t>
+          <t>US.VesselValueByOwnership</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: Share by flag of registration - Annual (analytical)</t>
+          <t>Merchant fleet: Share by beneficial ownership - Annual (analytical)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>US_VesselValueByRegistration</t>
+          <t>US_VesselValueByOwnership</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -12555,7 +12459,7 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>9782</v>
+        <v>9851</v>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
@@ -12570,7 +12474,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.VesselValueByRegistration/US_VesselValueByRegistration</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.VesselValueByOwnership/US_VesselValueByOwnership</t>
         </is>
       </c>
     </row>
@@ -12582,26 +12486,26 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>US.VesselValueByOwnership</t>
+          <t>US.ShipBuilding</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: Share by beneficial ownership - Annual (analytical)</t>
+          <t>Merchant fleet: Ship building - Annual</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>US_VesselValueByOwnership</t>
+          <t>US_ShipBuilding</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>From 2019 to 2026</t>
+          <t>From 2014 to 2025</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>9851</v>
+        <v>11070</v>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
@@ -12609,14 +12513,14 @@
         </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.VesselValueByOwnership/US_VesselValueByOwnership</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ShipBuilding/US_ShipBuilding</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12532,17 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>US.ShipBuilding</t>
+          <t>US.ShipScrapping</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: Ship building - Annual</t>
+          <t>Merchant fleet: Ship recycling - Annual</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>US_ShipBuilding</t>
+          <t>US_ShipScrapping</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -12647,7 +12551,7 @@
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>11070</v>
+        <v>8908</v>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
@@ -12655,14 +12559,14 @@
         </is>
       </c>
       <c r="H63" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ShipBuilding/US_ShipBuilding</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ShipScrapping/US_ShipScrapping</t>
         </is>
       </c>
     </row>
@@ -12674,26 +12578,26 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>US.ShipScrapping</t>
+          <t>US.SeaborneTrade</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Merchant fleet: Ship recycling - Annual</t>
+          <t>Freight: Seaborne trade by cargo type - Annual (analytical)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>US_ShipScrapping</t>
+          <t>US_SeaborneTrade</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>From 2014 to 2025</t>
+          <t>From 2000 to 2024</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>8908</v>
+        <v>462110</v>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
@@ -12701,14 +12605,14 @@
         </is>
       </c>
       <c r="H64" s="5" t="n">
-        <v>5</v>
+        <v>225</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>10</v>
+        <v>225</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ShipScrapping/US_ShipScrapping</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SeaborneTrade/US_SeaborneTrade</t>
         </is>
       </c>
     </row>
@@ -12720,26 +12624,26 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>US.SeaborneTrade</t>
+          <t>US.ContPortThroughput</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Freight: Seaborne trade by cargo type - Annual (analytical)</t>
+          <t>Freight: Container port throughput - Annual (analytical)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>US_SeaborneTrade</t>
+          <t>US_ContPortThroughput</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2024</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>462110</v>
+        <v>16188</v>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
@@ -12747,14 +12651,14 @@
         </is>
       </c>
       <c r="H65" s="5" t="n">
-        <v>225</v>
+        <v>15</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>225</v>
+        <v>12</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SeaborneTrade/US_SeaborneTrade</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ContPortThroughput/US_ContPortThroughput</t>
         </is>
       </c>
     </row>
@@ -12766,26 +12670,26 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>US.ContPortThroughput</t>
+          <t>US.PortCalls</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Freight: Container port throughput - Annual (analytical)</t>
+          <t>Port calls: Performance indicators - Annual (analytical)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>US_ContPortThroughput</t>
+          <t>US_PortCalls</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2018 to 2023</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>16188</v>
+        <v>19373</v>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
@@ -12793,14 +12697,14 @@
         </is>
       </c>
       <c r="H66" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ContPortThroughput/US_ContPortThroughput</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCalls/US_PortCalls</t>
         </is>
       </c>
     </row>
@@ -12812,17 +12716,17 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>US.PortCalls</t>
+          <t>US.PortCalls_S</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Port calls: Performance indicators - Annual (analytical)</t>
+          <t>Port calls: Performance indicators - Semi-annual (analytical)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>US_PortCalls</t>
+          <t>US_PortCalls_S</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -12831,7 +12735,7 @@
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>19373</v>
+        <v>36462</v>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
@@ -12846,7 +12750,7 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCalls/US_PortCalls</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCalls_S/US_PortCalls_S</t>
         </is>
       </c>
     </row>
@@ -12858,17 +12762,17 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>US.PortCalls_S</t>
+          <t>US.PortCallsArrivals</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Port calls: Performance indicators - Semi-annual (analytical)</t>
+          <t>Port calls: Calls by commercial market - Annual (analytical)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>US_PortCalls_S</t>
+          <t>US_PortCallsArrivals</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -12877,7 +12781,7 @@
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>36462</v>
+        <v>20304</v>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
@@ -12892,7 +12796,7 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCalls_S/US_PortCalls_S</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCallsArrivals/US_PortCallsArrivals</t>
         </is>
       </c>
     </row>
@@ -12904,17 +12808,17 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>US.PortCallsArrivals</t>
+          <t>US.PortCallsArrivals_S</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Port calls: Calls by commercial market - Annual (analytical)</t>
+          <t>Port calls: Calls by commercial market - Semi-annual (analytical)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>US_PortCallsArrivals</t>
+          <t>US_PortCallsArrivals_S</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -12923,7 +12827,7 @@
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>20304</v>
+        <v>38910</v>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
@@ -12938,7 +12842,7 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCallsArrivals/US_PortCallsArrivals</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCallsArrivals_S/US_PortCallsArrivals_S</t>
         </is>
       </c>
     </row>
@@ -12950,26 +12854,26 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>US.PortCallsArrivals_S</t>
+          <t>US.LSCI_M</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Port calls: Calls by commercial market - Semi-annual (analytical)</t>
+          <t>Liner shipping: Connectivity index - Monthly (analytical)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>US_PortCallsArrivals_S</t>
+          <t>US_LSCI_M</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>From 2018 to 2023</t>
+          <t>From 2006 to 2026</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>38910</v>
+        <v>215059</v>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
@@ -12977,14 +12881,14 @@
         </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PortCallsArrivals_S/US_PortCallsArrivals_S</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.LSCI_M/US_LSCI_M</t>
         </is>
       </c>
     </row>
@@ -12996,17 +12900,17 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>US.LSCI_M</t>
+          <t>US.LSCI</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Connectivity index - Monthly (analytical)</t>
+          <t>Liner shipping: Connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>US_LSCI_M</t>
+          <t>US_LSCI</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -13015,7 +12919,7 @@
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>215059</v>
+        <v>205865</v>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
@@ -13023,14 +12927,14 @@
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>258</v>
+        <v>327</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.LSCI_M/US_LSCI_M</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.LSCI/US_LSCI</t>
         </is>
       </c>
     </row>
@@ -13042,17 +12946,17 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>US.LSCI</t>
+          <t>US.LSBCI</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Connectivity index - Quarterly (analytical)</t>
+          <t>Liner shipping: Bilateral connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>US_LSCI</t>
+          <t>US_LSBCI</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -13061,7 +12965,7 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>205865</v>
+        <v>3456483</v>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
@@ -13069,14 +12973,14 @@
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>83</v>
+        <v>7565</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>327</v>
+        <v>7398</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.LSCI/US_LSCI</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.LSBCI/US_LSBCI</t>
         </is>
       </c>
     </row>
@@ -13088,17 +12992,17 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>US.LSBCI</t>
+          <t>US.PLSCI</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Bilateral connectivity index - Quarterly (analytical)</t>
+          <t>Liner shipping: Port connectivity index - Quarterly (analytical)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>US_LSBCI</t>
+          <t>US_PLSCI</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -13107,7 +13011,7 @@
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>3456483</v>
+        <v>359436</v>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
@@ -13115,14 +13019,14 @@
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>7565</v>
+        <v>722</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>7398</v>
+        <v>722</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.LSBCI/US_LSBCI</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PLSCI/US_PLSCI</t>
         </is>
       </c>
     </row>
@@ -13134,26 +13038,26 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>US.PLSCI</t>
+          <t>US.Seafarers</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Liner shipping: Port connectivity index - Quarterly (analytical)</t>
+          <t>Seafarer: Supply estimates by rank - Quinquennial (analytical)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>US_PLSCI</t>
+          <t>US_Seafarers</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>From 2006 to 2026</t>
+          <t>From 2015 to 2021</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>359436</v>
+        <v>11519</v>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
@@ -13161,14 +13065,14 @@
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>722</v>
+        <v>6</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>722</v>
+        <v>12</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PLSCI/US_PLSCI</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Seafarers/US_Seafarers</t>
         </is>
       </c>
     </row>
@@ -13180,41 +13084,41 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>US.Seafarers</t>
+          <t>US.TransportCosts</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Seafarer: Supply estimates by rank - Quinquennial (analytical)</t>
+          <t>Trade and transport: By destination, mode and product group  - Annual (analytical)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>US_Seafarers</t>
+          <t>US_TransportCosts_20162016</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>From 2015 to 2021</t>
+          <t>From 2016 to 2016</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>11519</v>
+        <v>5808744649</v>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Seafarers/US_Seafarers</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20162016</t>
         </is>
       </c>
     </row>
@@ -13236,16 +13140,16 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>US_TransportCosts_20162016</t>
+          <t>US_TransportCosts_20172017</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>From 2016 to 2016</t>
+          <t>From 2017 to 2017</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>5808744649</v>
+        <v>5505087830</v>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
@@ -13260,7 +13164,7 @@
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20162016</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20172017</t>
         </is>
       </c>
     </row>
@@ -13282,16 +13186,16 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>US_TransportCosts_20172017</t>
+          <t>US_TransportCosts_20182018</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>From 2017 to 2017</t>
+          <t>From 2018 to 2018</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>5505087830</v>
+        <v>5587492705</v>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
@@ -13306,7 +13210,7 @@
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20172017</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20182018</t>
         </is>
       </c>
     </row>
@@ -13328,16 +13232,16 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>US_TransportCosts_20182018</t>
+          <t>US_TransportCosts_20192019</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>From 2018 to 2018</t>
+          <t>From 2019 to 2019</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>5587492705</v>
+        <v>5666291146</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
@@ -13352,7 +13256,7 @@
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20182018</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20192019</t>
         </is>
       </c>
     </row>
@@ -13374,16 +13278,16 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>US_TransportCosts_20192019</t>
+          <t>US_TransportCosts_20202020</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>From 2019 to 2019</t>
+          <t>From 2020 to 2020</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>5666291146</v>
+        <v>5621158940</v>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
@@ -13398,7 +13302,7 @@
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20192019</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20202020</t>
         </is>
       </c>
     </row>
@@ -13420,16 +13324,16 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>US_TransportCosts_20202020</t>
+          <t>US_TransportCosts_20212021</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>From 2020 to 2020</t>
+          <t>From 2021 to 2021</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>5621158940</v>
+        <v>5819253692</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
@@ -13444,7 +13348,7 @@
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20202020</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20212021</t>
         </is>
       </c>
     </row>
@@ -13456,26 +13360,26 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>US.TransportCosts</t>
+          <t>US.BiotradeMerch</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Trade and transport: By destination, mode and product group  - Annual (analytical)</t>
+          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>US_TransportCosts_20212021</t>
+          <t>US_BiotradeMerch_20102011</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>From 2021 to 2021</t>
+          <t>From 2010 to 2011</t>
         </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>5819253692</v>
+        <v>2156853807</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
@@ -13490,7 +13394,7 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TransportCosts/US_TransportCosts_20212021</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20102011</t>
         </is>
       </c>
     </row>
@@ -13512,16 +13416,16 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20102011</t>
+          <t>US_BiotradeMerch_20122013</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2011</t>
+          <t>From 2012 to 2013</t>
         </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>2156853807</v>
+        <v>2081556293</v>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
@@ -13536,7 +13440,7 @@
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20102011</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20122013</t>
         </is>
       </c>
     </row>
@@ -13558,16 +13462,16 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20122013</t>
+          <t>US_BiotradeMerch_20142015</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>From 2012 to 2013</t>
+          <t>From 2014 to 2015</t>
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>2081556293</v>
+        <v>2085525371</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
@@ -13582,7 +13486,7 @@
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20122013</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20142015</t>
         </is>
       </c>
     </row>
@@ -13604,16 +13508,16 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20142015</t>
+          <t>US_BiotradeMerch_20162017</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>From 2014 to 2015</t>
+          <t>From 2016 to 2017</t>
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2085525371</v>
+        <v>2083255752</v>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
@@ -13628,7 +13532,7 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20142015</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20162017</t>
         </is>
       </c>
     </row>
@@ -13650,16 +13554,16 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20162017</t>
+          <t>US_BiotradeMerch_20182019</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>From 2016 to 2017</t>
+          <t>From 2018 to 2019</t>
         </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>2083255752</v>
+        <v>2046492014</v>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
@@ -13674,7 +13578,7 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20162017</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20182019</t>
         </is>
       </c>
     </row>
@@ -13696,16 +13600,16 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20182019</t>
+          <t>US_BiotradeMerch_20202020</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>From 2018 to 2019</t>
+          <t>From 2020 to 2020</t>
         </is>
       </c>
       <c r="F86" s="5" t="n">
-        <v>2046492014</v>
+        <v>999390394</v>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
@@ -13720,7 +13624,7 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20182019</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20202020</t>
         </is>
       </c>
     </row>
@@ -13742,16 +13646,16 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20202020</t>
+          <t>US_BiotradeMerch_20212021</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>From 2020 to 2020</t>
+          <t>From 2021 to 2021</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>999390394</v>
+        <v>1026527320</v>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
@@ -13766,7 +13670,7 @@
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20202020</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20212021</t>
         </is>
       </c>
     </row>
@@ -13788,16 +13692,16 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20212021</t>
+          <t>US_BiotradeMerch_20222022</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>From 2021 to 2021</t>
+          <t>From 2022 to 2022</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>1026527320</v>
+        <v>1040823870</v>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
@@ -13812,7 +13716,7 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20212021</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20222022</t>
         </is>
       </c>
     </row>
@@ -13834,16 +13738,16 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20222022</t>
+          <t>US_BiotradeMerch_20232023</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>From 2022 to 2022</t>
+          <t>From 2023 to 2023</t>
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>1040823870</v>
+        <v>1038282985</v>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
@@ -13858,7 +13762,7 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20222022</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20232023</t>
         </is>
       </c>
     </row>
@@ -13880,16 +13784,16 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20232023</t>
+          <t>US_BiotradeMerch_20242024</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>From 2023 to 2023</t>
+          <t>From 2024 to 2024</t>
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>1038282985</v>
+        <v>993411533</v>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
@@ -13904,7 +13808,7 @@
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20232023</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20242024</t>
         </is>
       </c>
     </row>
@@ -13916,41 +13820,41 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>US.BiotradeMerch</t>
+          <t>US.BiotradeMerchShare</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Biotrade: Bilateral trade by product - Annual (analytical)</t>
+          <t>Biotrade: Bilateral trade as percentage of total trade - Annual (analytical)</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerch_20242024</t>
+          <t>US_BiotradeMerchShare</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>From 2024 to 2024</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>993411533</v>
+        <v>12702448</v>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
-        <v>0</v>
+        <v>6810</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0</v>
+        <v>6710</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerch/US_BiotradeMerch_20242024</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerchShare/US_BiotradeMerchShare</t>
         </is>
       </c>
     </row>
@@ -13962,17 +13866,17 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>US.BiotradeMerchShare</t>
+          <t>US.BioTradeMerchGDPShare</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Biotrade: Bilateral trade as percentage of total trade - Annual (analytical)</t>
+          <t>Biotrade: Trade as percentage of Gross Domestic Product - Annual (analytical)</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerchShare</t>
+          <t>US_BioTradeMerchGDPShare</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -13981,7 +13885,7 @@
         </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>12702448</v>
+        <v>21748</v>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
@@ -13989,14 +13893,14 @@
         </is>
       </c>
       <c r="H92" s="5" t="n">
-        <v>6810</v>
+        <v>4</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>6710</v>
+        <v>4</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerchShare/US_BiotradeMerchShare</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BioTradeMerchGDPShare/US_BioTradeMerchGDPShare</t>
         </is>
       </c>
     </row>
@@ -14008,17 +13912,17 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>US.BioTradeMerchGDPShare</t>
+          <t>US.BiotradeMerchRCA</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Biotrade: Trade as percentage of Gross Domestic Product - Annual (analytical)</t>
+          <t>DISCONTINUED - Biotrade: Revealed Comparative Advantage index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>US_BioTradeMerchGDPShare</t>
+          <t>US_BiotradeMerchRCA</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -14027,7 +13931,7 @@
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>21748</v>
+        <v>20785250</v>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
@@ -14035,14 +13939,14 @@
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>4</v>
+        <v>2635</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>4</v>
+        <v>2635</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BioTradeMerchGDPShare/US_BioTradeMerchGDPShare</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerchRCA/US_BiotradeMerchRCA</t>
         </is>
       </c>
     </row>
@@ -14054,17 +13958,17 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>US.BiotradeMerchRCA</t>
+          <t>US.BioTradeMerchProdConcent</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Biotrade: Revealed Comparative Advantage index - Annual (analytical)</t>
+          <t>DISCONTINUED - Biotrade: Product concentration index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>US_BiotradeMerchRCA</t>
+          <t>US_BioTradeMerchProdConcent</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -14073,7 +13977,7 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>20785250</v>
+        <v>34933</v>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
@@ -14081,14 +13985,14 @@
         </is>
       </c>
       <c r="H94" s="5" t="n">
-        <v>2635</v>
+        <v>8</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>2635</v>
+        <v>8</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BiotradeMerchRCA/US_BiotradeMerchRCA</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BioTradeMerchProdConcent/US_BioTradeMerchProdConcent</t>
         </is>
       </c>
     </row>
@@ -14100,17 +14004,17 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>US.BioTradeMerchProdConcent</t>
+          <t>US.BioTradeMerchMarketIndices</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Biotrade: Product concentration index - Annual (analytical)</t>
+          <t>DISCONTINUED - Biotrade: Market concentration and structural change indices - Annual (analytical)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>US_BioTradeMerchProdConcent</t>
+          <t>US_BioTradeMerchMarketIndices</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -14119,7 +14023,7 @@
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>34933</v>
+        <v>623798</v>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
@@ -14127,14 +14031,14 @@
         </is>
       </c>
       <c r="H95" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BioTradeMerchProdConcent/US_BioTradeMerchProdConcent</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BioTradeMerchMarketIndices/US_BioTradeMerchMarketIndices</t>
         </is>
       </c>
     </row>
@@ -14146,30 +14050,30 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>US.BioTradeMerchMarketIndices</t>
+          <t>US.OceanTrade</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>DISCONTINUED - Biotrade: Market concentration and structural change indices - Annual (analytical)</t>
+          <t>Ocean goods: Bilateral trade by product group - Annual (analytical)</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>US_BioTradeMerchMarketIndices</t>
+          <t>US_OceanTrade</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2012 to 2025</t>
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>623798</v>
+        <v>572108660</v>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -14180,7 +14084,7 @@
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.BioTradeMerchMarketIndices/US_BioTradeMerchMarketIndices</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.OceanTrade/US_OceanTrade</t>
         </is>
       </c>
     </row>
@@ -14192,41 +14096,41 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>US.OceanTrade</t>
+          <t>US.OceanServices</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Ocean goods: Bilateral trade by product group - Annual (analytical)</t>
+          <t>Ocean services: Trade - Annual (analytical)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>US_OceanTrade</t>
+          <t>US_OceanServices</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>From 2012 to 2025</t>
+          <t>From 2005 to 2025</t>
         </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>572108660</v>
+        <v>403520</v>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.OceanTrade/US_OceanTrade</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.OceanServices/US_OceanServices</t>
         </is>
       </c>
     </row>
@@ -14238,41 +14142,41 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>US.OceanServices</t>
+          <t>US.NonPlasticSubstsTradeByPartner</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Ocean services: Trade - Annual (analytical)</t>
+          <t>Non-plastics: Bilateral trade of non-plastic substitutes - Annual (analytical)</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>US_OceanServices</t>
+          <t>US_NonPlasticSubstsTradeByPartner</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2025</t>
+          <t>From 2005 to 2024</t>
         </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>403520</v>
+        <v>577508294</v>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>348</v>
+        <v>0</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.OceanServices/US_OceanServices</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.NonPlasticSubstsTradeByPartner/US_NonPlasticSubstsTradeByPartner</t>
         </is>
       </c>
     </row>
@@ -14284,26 +14188,26 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>US.NonPlasticSubstsTradeByPartner</t>
+          <t>US.PlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Non-plastics: Bilateral trade of non-plastic substitutes - Annual (analytical)</t>
+          <t>Plastics: Bilateral trade across plastics life-cycle stages - Annual (analytical)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>US_NonPlasticSubstsTradeByPartner</t>
+          <t>US_PlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2023</t>
+          <t>From 2005 to 2024</t>
         </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>511626169</v>
+        <v>90879049</v>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
@@ -14318,7 +14222,7 @@
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.NonPlasticSubstsTradeByPartner/US_NonPlasticSubstsTradeByPartner</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PlasticsTradebyPartner/US_PlasticsTradebyPartner</t>
         </is>
       </c>
     </row>
@@ -14330,17 +14234,17 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>US.PlasticsTradebyPartner</t>
+          <t>US.AssociatedPlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Plastics: Bilateral trade across plastics life-cycle stages - Annual (analytical)</t>
+          <t>Plastics: Bilateral trade of plastics associated products - Annual (analytical)</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>US_PlasticsTradebyPartner</t>
+          <t>US_AssociatedPlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -14349,7 +14253,7 @@
         </is>
       </c>
       <c r="F100" s="5" t="n">
-        <v>90879049</v>
+        <v>33181670</v>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
@@ -14364,7 +14268,7 @@
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PlasticsTradebyPartner/US_PlasticsTradebyPartner</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.AssociatedPlasticsTradebyPartner/US_AssociatedPlasticsTradebyPartner</t>
         </is>
       </c>
     </row>
@@ -14376,17 +14280,17 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>US.AssociatedPlasticsTradebyPartner</t>
+          <t>US.HiddenPlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Plastics: Bilateral trade of plastics associated products - Annual (analytical)</t>
+          <t>Plastics: Bilateral trade of plastic packaging, synthetic textiles and synthetic rubber - Annual (analytical)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>US_AssociatedPlasticsTradebyPartner</t>
+          <t>US_HiddenPlasticsTradebyPartner</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -14395,7 +14299,7 @@
         </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>33181670</v>
+        <v>55831373</v>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
@@ -14410,7 +14314,7 @@
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.AssociatedPlasticsTradebyPartner/US_AssociatedPlasticsTradebyPartner</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.HiddenPlasticsTradebyPartner/US_HiddenPlasticsTradebyPartner</t>
         </is>
       </c>
     </row>
@@ -14422,41 +14326,41 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>US.HiddenPlasticsTradebyPartner</t>
+          <t>US.EnvironmentalGoodsTrade</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Plastics: Bilateral trade of plastic packaging, synthetic textiles and synthetic rubber - Annual (analytical)</t>
+          <t>Green industrial goods: Trade - Annual (Analytical)</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>US_HiddenPlasticsTradebyPartner</t>
+          <t>US_EnvironmentalGoodsTrade</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2024</t>
+          <t>From 1995 to 2024</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>55831373</v>
+        <v>2673479</v>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>0</v>
+        <v>1716</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.HiddenPlasticsTradebyPartner/US_HiddenPlasticsTradebyPartner</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.EnvironmentalGoodsTrade/US_EnvironmentalGoodsTrade</t>
         </is>
       </c>
     </row>
@@ -14468,17 +14372,17 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>US.EnvironmentalGoodsTrade</t>
+          <t>US.EnvironmentalGoodsRCA</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Green industrial goods: Trade - Annual (Analytical)</t>
+          <t>Green industrial goods: Revealed comparative advantage index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>US_EnvironmentalGoodsTrade</t>
+          <t>US_EnvironmentalGoodsRCA</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -14487,7 +14391,7 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>2673479</v>
+        <v>1021401</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -14498,11 +14402,11 @@
         <v>439</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>1716</v>
+        <v>439</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.EnvironmentalGoodsTrade/US_EnvironmentalGoodsTrade</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.EnvironmentalGoodsRCA/US_EnvironmentalGoodsRCA</t>
         </is>
       </c>
     </row>
@@ -14514,17 +14418,17 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>US.EnvironmentalGoodsRCA</t>
+          <t>US.WastewaterTreatment</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Green industrial goods: Revealed comparative advantage index - Annual (analytical)</t>
+          <t>Industrial wastewater treatment: Trade of associated products - Annul (ananlytical)</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>US_EnvironmentalGoodsRCA</t>
+          <t>US_WastewaterTreatment</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -14533,7 +14437,7 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>1021401</v>
+        <v>241521</v>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
@@ -14541,14 +14445,14 @@
         </is>
       </c>
       <c r="H104" s="5" t="n">
-        <v>439</v>
+        <v>37</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>439</v>
+        <v>145</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.EnvironmentalGoodsRCA/US_EnvironmentalGoodsRCA</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.WastewaterTreatment/US_WastewaterTreatment</t>
         </is>
       </c>
     </row>
@@ -14560,26 +14464,26 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>US.WastewaterTreatment</t>
+          <t>US.IctProductionSector</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Industrial wastewater treatment: Trade of associated products - Annul (ananlytical)</t>
+          <t>ICT producing sector: Workforce involved and value added - Annual</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>US_WastewaterTreatment</t>
+          <t>US_IctProductionSector</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>From 1995 to 2024</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
-        <v>241521</v>
+        <v>6495</v>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
@@ -14587,14 +14491,14 @@
         </is>
       </c>
       <c r="H105" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.WastewaterTreatment/US_WastewaterTreatment</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctProductionSector/US_IctProductionSector</t>
         </is>
       </c>
     </row>
@@ -14606,30 +14510,30 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>US.IctProductionSector</t>
+          <t>US.IctGoods</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>ICT producing sector: Workforce involved and value added - Annual</t>
+          <t>ICT goods: Bilateral trade by category - Annual</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>US_IctProductionSector</t>
+          <t>US_IctGoods</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2000 to 2024</t>
         </is>
       </c>
       <c r="F106" s="5" t="n">
-        <v>6495</v>
+        <v>115739203</v>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>Omitido por tamaño &gt; 20971520 bytes</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -14640,7 +14544,7 @@
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctProductionSector/US_IctProductionSector</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctGoods/US_IctGoods</t>
         </is>
       </c>
     </row>
@@ -14652,30 +14556,30 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>US.IctGoods</t>
+          <t>US.IctUseTotal</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>ICT goods: Bilateral trade by category - Annual</t>
+          <t>ICT use in business: Core indicators - Annual</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>US_IctGoods</t>
+          <t>US_IctUseTotal</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2024</t>
+          <t>From 2015 to 2025</t>
         </is>
       </c>
       <c r="F107" s="5" t="n">
-        <v>115739203</v>
+        <v>29937</v>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>Omitido por tamaño &gt; 20971520 bytes</t>
+          <t>Procesado</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -14686,7 +14590,7 @@
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctGoods/US_IctGoods</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseTotal/US_IctUseTotal</t>
         </is>
       </c>
     </row>
@@ -14698,26 +14602,26 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseTotal</t>
+          <t>US.IctUseLocation</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators - Annual</t>
+          <t>ICT use in business: Core indicators by location type - Annual</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>US_IctUseTotal</t>
+          <t>US_IctUseLocation</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>From 2015 to 2025</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F108" s="5" t="n">
-        <v>29937</v>
+        <v>8295</v>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
@@ -14732,7 +14636,7 @@
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseTotal/US_IctUseTotal</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseLocation/US_IctUseLocation</t>
         </is>
       </c>
     </row>
@@ -14744,26 +14648,26 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseLocation</t>
+          <t>US.IctUseEnterprSize</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by location type - Annual</t>
+          <t>ICT use in business: Core indicators by enterprise size - Annual</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>US_IctUseLocation</t>
+          <t>US_IctUseEnterprSize</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2010 to 2025</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>8295</v>
+        <v>222567</v>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
@@ -14778,7 +14682,7 @@
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseLocation/US_IctUseLocation</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEnterprSize/US_IctUseEnterprSize</t>
         </is>
       </c>
     </row>
@@ -14790,17 +14694,17 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEnterprSize</t>
+          <t>US.IctUseEconActivity_Isic4</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by enterprise size - Annual</t>
+          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 4) - Annual</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>US_IctUseEnterprSize</t>
+          <t>US_IctUseEconActivity_Isic4</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -14809,7 +14713,7 @@
         </is>
       </c>
       <c r="F110" s="5" t="n">
-        <v>222567</v>
+        <v>663946</v>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
@@ -14824,7 +14728,7 @@
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEnterprSize/US_IctUseEnterprSize</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEconActivity_Isic4/US_IctUseEconActivity_Isic4</t>
         </is>
       </c>
     </row>
@@ -14836,26 +14740,26 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEconActivity_Isic4</t>
+          <t>US.IctUseEconActivity</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 4) - Annual</t>
+          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 3.1) - Annual</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>US_IctUseEconActivity_Isic4</t>
+          <t>US_IctUseEconActivity</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2025</t>
+          <t>From 2010 to 2021</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
-        <v>663946</v>
+        <v>83239</v>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
@@ -14870,7 +14774,7 @@
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEconActivity_Isic4/US_IctUseEconActivity_Isic4</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEconActivity/US_IctUseEconActivity</t>
         </is>
       </c>
     </row>
@@ -14882,26 +14786,26 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>US.IctUseEconActivity</t>
+          <t>US.DigitallyDeliverableServices</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>ICT use in business: Core indicators by economic activity (ISIC Rev. 3.1) - Annual</t>
+          <t>Digitally deliverable services: Trade - Annual (analytical)</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>US_IctUseEconActivity</t>
+          <t>US_DigitallyDeliverableServices</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2021</t>
+          <t>From 2010 to 2025</t>
         </is>
       </c>
       <c r="F112" s="5" t="n">
-        <v>83239</v>
+        <v>1410808</v>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
@@ -14909,14 +14813,14 @@
         </is>
       </c>
       <c r="H112" s="5" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IctUseEconActivity/US_IctUseEconActivity</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.DigitallyDeliverableServices/US_DigitallyDeliverableServices</t>
         </is>
       </c>
     </row>
@@ -14928,26 +14832,26 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>US.DigitallyDeliverableServices</t>
+          <t>US.TradeServICT</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Digitally deliverable services: Trade - Annual (analytical)</t>
+          <t>ICT services: Trade - Annual</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>US_DigitallyDeliverableServices</t>
+          <t>US_TradeServICT</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2005 to 2025</t>
         </is>
       </c>
       <c r="F113" s="5" t="n">
-        <v>1525091</v>
+        <v>146069</v>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
@@ -14955,14 +14859,14 @@
         </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>420</v>
+        <v>42</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>577</v>
+        <v>94</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.DigitallyDeliverableServices/US_DigitallyDeliverableServices</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServICT/US_TradeServICT</t>
         </is>
       </c>
     </row>
@@ -14974,26 +14878,26 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>US.TradeServICT</t>
+          <t>US.ECommerceTotal</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>ICT services: Trade - Annual</t>
+          <t>E-commerce: Domestic and international sales - Annual (analytical)</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>US_TradeServICT</t>
+          <t>US_ECommerceTotal</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>From 2005 to 2024</t>
+          <t>From 2012 to 2025</t>
         </is>
       </c>
       <c r="F114" s="5" t="n">
-        <v>141178</v>
+        <v>906006</v>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
@@ -15001,14 +14905,14 @@
         </is>
       </c>
       <c r="H114" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.TradeServICT/US_TradeServICT</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ECommerceTotal/US_ECommerceTotal</t>
         </is>
       </c>
     </row>
@@ -15020,26 +14924,26 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>US.ECommerceTotal</t>
+          <t>US.ECommerceInternational</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: Domestic and international sales - Annual (analytical)</t>
+          <t>E-commerce: International digitally ordered trade, bilateral – Annual (analytical)</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>US_ECommerceTotal</t>
+          <t>US_ECommerceInternational</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>From 2012 to 2025</t>
+          <t>From 2015 to 2024</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
-        <v>906006</v>
+        <v>139183</v>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
@@ -15054,7 +14958,7 @@
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ECommerceTotal/US_ECommerceTotal</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ECommerceInternational/US_ECommerceInternational</t>
         </is>
       </c>
     </row>
@@ -15066,26 +14970,26 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>US.ECommerceInternational</t>
+          <t>US.FTRI</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>E-commerce: International digitally ordered trade, bilateral - Annual (analytical)</t>
+          <t>Technology: Frontier technology readiness index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>US_ECommerceInternational</t>
+          <t>US_FTRI</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>From 2015 to 2024</t>
+          <t>From 2010 to 2023</t>
         </is>
       </c>
       <c r="F116" s="5" t="n">
-        <v>139183</v>
+        <v>62747</v>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
@@ -15093,14 +14997,14 @@
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.ECommerceInternational/US_ECommerceInternational</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FTRI/US_FTRI</t>
         </is>
       </c>
     </row>
@@ -15112,26 +15016,26 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>US.FTRI</t>
+          <t>US.PopTotal</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Technology: Frontier technology readiness index - Annual (analytical)</t>
+          <t>Population: Total - Annual</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>US_FTRI</t>
+          <t>US_PopTotal</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2023</t>
+          <t>From 1950 to 2050</t>
         </is>
       </c>
       <c r="F117" s="5" t="n">
-        <v>62747</v>
+        <v>374021</v>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
@@ -15139,14 +15043,14 @@
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>84</v>
+        <v>302</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.FTRI/US_FTRI</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopTotal/US_PopTotal</t>
         </is>
       </c>
     </row>
@@ -15158,17 +15062,17 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>US.PopTotal</t>
+          <t>US.PopAgeStruct</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Population: Total - Annual</t>
+          <t>Population: Structure by gender and age group - Annual</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>US_PopTotal</t>
+          <t>US_PopAgeStruct</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -15177,7 +15081,7 @@
         </is>
       </c>
       <c r="F118" s="5" t="n">
-        <v>374021</v>
+        <v>12550832</v>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
@@ -15185,14 +15089,14 @@
         </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>101</v>
+        <v>6666</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>302</v>
+        <v>6666</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopTotal/US_PopTotal</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopAgeStruct/US_PopAgeStruct</t>
         </is>
       </c>
     </row>
@@ -15204,17 +15108,17 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>US.PopAgeStruct</t>
+          <t>US.PopDependency</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Population: Structure by gender and age group - Annual</t>
+          <t>Population: Dependency ratios - Annual</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>US_PopAgeStruct</t>
+          <t>US_PopDependency</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -15223,7 +15127,7 @@
         </is>
       </c>
       <c r="F119" s="5" t="n">
-        <v>12550832</v>
+        <v>494161</v>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
@@ -15231,14 +15135,14 @@
         </is>
       </c>
       <c r="H119" s="5" t="n">
-        <v>6666</v>
+        <v>303</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>6666</v>
+        <v>303</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopAgeStruct/US_PopAgeStruct</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopDependency/US_PopDependency</t>
         </is>
       </c>
     </row>
@@ -15250,26 +15154,26 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>US.PopDependency</t>
+          <t>US.InclusiveGrowth</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Population: Dependency ratios - Annual</t>
+          <t>Inclusiveness: Inclusive growth index - Annual (analytical)</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>US_PopDependency</t>
+          <t>US_InclusiveGrowth</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>From 1950 to 2050</t>
+          <t>From 2023 to 2023</t>
         </is>
       </c>
       <c r="F120" s="5" t="n">
-        <v>494161</v>
+        <v>4221</v>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
@@ -15277,14 +15181,14 @@
         </is>
       </c>
       <c r="H120" s="5" t="n">
-        <v>303</v>
+        <v>0</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>303</v>
+        <v>0</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.PopDependency/US_PopDependency</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.InclusiveGrowth/US_InclusiveGrowth</t>
         </is>
       </c>
     </row>
@@ -15296,26 +15200,26 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>US.InclusiveGrowth</t>
+          <t>US.Gender_DomesticValueAdded</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Inclusiveness: Inclusive growth index - Annual (analytical)</t>
+          <t>Gender: Domestic value added in gross exports by sex and broad sector - Annual (analytical)</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>US_InclusiveGrowth</t>
+          <t>US_Gender_DomesticValueAdded</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>From 2023 to 2023</t>
+          <t>From 2000 to 2020</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
-        <v>4221</v>
+        <v>97680</v>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
@@ -15330,7 +15234,7 @@
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.InclusiveGrowth/US_InclusiveGrowth</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Gender_DomesticValueAdded/US_Gender_DomesticValueAdded</t>
         </is>
       </c>
     </row>
@@ -15342,26 +15246,26 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>US.Gender_DomesticValueAdded</t>
+          <t>US.Gender_TradableIndustries</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Gender: Domestic value added in gross exports by sex and broad sector - Annual (analytical)</t>
+          <t>Gender: Employment and earnings by sex - Annual (analytical)</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>US_Gender_DomesticValueAdded</t>
+          <t>US_Gender_TradableIndustries</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2020</t>
+          <t>From 2000 to 2023</t>
         </is>
       </c>
       <c r="F122" s="5" t="n">
-        <v>97680</v>
+        <v>176441</v>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
@@ -15369,14 +15273,14 @@
         </is>
       </c>
       <c r="H122" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Gender_DomesticValueAdded/US_Gender_DomesticValueAdded</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Gender_TradableIndustries/US_Gender_TradableIndustries</t>
         </is>
       </c>
     </row>
@@ -15388,26 +15292,26 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>US.Gender_TradableIndustries</t>
+          <t>US.SDG_LULFRG</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Gender: Employment and earnings by sex - Annual (analytical)</t>
+          <t>Indicator 9.1.2: Freight loaded and unloaded - Annual</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>US_Gender_TradableIndustries</t>
+          <t>US_SDG_LULFRG</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2023</t>
+          <t>From 2000 to 2024</t>
         </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>176441</v>
+        <v>46857</v>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
@@ -15415,14 +15319,14 @@
         </is>
       </c>
       <c r="H123" s="5" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.Gender_TradableIndustries/US_Gender_TradableIndustries</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SDG_LULFRG/US_SDG_LULFRG</t>
         </is>
       </c>
     </row>
@@ -15434,26 +15338,26 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>US.SDG_LULFRG</t>
+          <t>US.SDG_PORFVOL</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2: Freight loaded and unloaded - Annual</t>
+          <t>Indicator 9.1.2: Container port traffic - Annual</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>US_SDG_LULFRG</t>
+          <t>US_SDG_PORFVOL</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>From 2000 to 2024</t>
+          <t>From 2010 to 2024</t>
         </is>
       </c>
       <c r="F124" s="5" t="n">
-        <v>46857</v>
+        <v>15386</v>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
@@ -15461,14 +15365,14 @@
         </is>
       </c>
       <c r="H124" s="5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SDG_LULFRG/US_SDG_LULFRG</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SDG_PORFVOL/US_SDG_PORFVOL</t>
         </is>
       </c>
     </row>
@@ -15480,26 +15384,26 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>US.SDG_PORFVOL</t>
+          <t>US.IFF_TradeMisinvoicing</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Indicator 9.1.2: Container port traffic - Annual</t>
+          <t xml:space="preserve">Indicator 16.4.1: Trade misinvoicing illicit financial flows, IFFs - Annual </t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>US_SDG_PORFVOL</t>
+          <t>US_IFF_TradeMisinvoicing</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>From 2010 to 2024</t>
+          <t>From 2011 to 2024</t>
         </is>
       </c>
       <c r="F125" s="5" t="n">
-        <v>15386</v>
+        <v>3342</v>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
@@ -15507,14 +15411,14 @@
         </is>
       </c>
       <c r="H125" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.SDG_PORFVOL/US_SDG_PORFVOL</t>
+          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IFF_TradeMisinvoicing/US_IFF_TradeMisinvoicing</t>
         </is>
       </c>
     </row>
@@ -15526,26 +15430,26 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>US.IFF_TradeMisinvoicing</t>
+          <t>US.IFF_CrimesRelated</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indicator 16.4.1: Trade misinvoicing illicit financial flows, IFFs - Annual </t>
+          <t>Indicator 16.4.1: Crime-related illicit financial flows, IFFs - Annual</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>US_IFF_TradeMisinvoicing</t>
+          <t>US_IFF_CrimesRelated</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>From 2011 to 2024</t>
+          <t>From 2015 to 2025</t>
         </is>
       </c>
       <c r="F126" s="5" t="n">
-        <v>3342</v>
+        <v>2046</v>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
@@ -15559,52 +15463,6 @@
         <v>0</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>https://unctadstat-api.unctad.org/bulkdownload/US.IFF_TradeMisinvoicing/US_IFF_TradeMisinvoicing</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>UNCTADstat - UNCTAD</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>US.IFF_CrimesRelated</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>Indicator 16.4.1: Crime-related illicit financial flows, IFFs - Annual</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>US_IFF_CrimesRelated</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>From 2015 to 2025</t>
-        </is>
-      </c>
-      <c r="F127" s="5" t="n">
-        <v>2046</v>
-      </c>
-      <c r="G127" s="4" t="inlineStr">
-        <is>
-          <t>Procesado</t>
-        </is>
-      </c>
-      <c r="H127" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
         <is>
           <t>https://unctadstat-api.unctad.org/bulkdownload/US.IFF_CrimesRelated/US_IFF_CrimesRelated</t>
         </is>
@@ -15690,7 +15548,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -15773,7 +15631,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -15783,7 +15641,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -15793,7 +15651,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
@@ -15803,7 +15661,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>83628</v>
+        <v>83901</v>
       </c>
     </row>
     <row r="20">

--- a/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
+++ b/assets/data/unctad/catalog/catalogo_dataset_web_ove_unctadstat.xlsx
@@ -1577,20 +1577,20 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>US.Remittances</t>
+          <t>US.FdiFlowsStock</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1994</v>
+        <v>2559</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Balance of payments: Personal remittances - Annual </t>
+          <t>Investment: Foreign direct investment - Annual</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>External financial resources</t>
+          <t>Foreign direct investment</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>remittances, transfers, personal, compensation, employees, payments, receipts</t>
+          <t>foreign, direct, investment, flow, stock, inward, outward, FDI</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>2025-11-05T13:07:00</t>
+          <t>2026-08-17T12:15:00</t>
         </is>
       </c>
       <c r="J16" s="5" t="n">
@@ -1618,19 +1618,19 @@
         <v>0</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>69641</v>
+        <v>676265</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>40</v>
+        <v>576</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
@@ -1673,20 +1673,20 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>US.FdiFlowsStock</t>
+          <t>US.Remittances</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2559</v>
+        <v>1994</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Investment: Foreign direct investment - Annual</t>
+          <t>Personal remittances: receipts and payments, annual</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Foreign direct investment</t>
+          <t>External financial resources</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>foreign, direct, investment, flow, stock, inward, outward, FDI</t>
+          <t>remittances, transfers, personal, compensation, employees, payments, receipts</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T12:15:00</t>
+          <t>2025-11-05T13:07:00</t>
         </is>
       </c>
       <c r="J17" s="5" t="n">
@@ -1714,19 +1714,19 @@
         <v>0</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>676265</v>
+        <v>69641</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>576</v>
+        <v>40</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>2529</v>
+        <v>2656</v>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T08:57:00</t>
+          <t>2026-10-14T15:16:00</t>
         </is>
       </c>
       <c r="J69" s="5" t="n">
@@ -6650,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>906006</v>
+        <v>911427</v>
       </c>
       <c r="N69" s="5" t="n">
         <v>0</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>2530</v>
+        <v>2657</v>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T08:57:00</t>
+          <t>2026-10-14T15:16:00</t>
         </is>
       </c>
       <c r="J70" s="5" t="n">
@@ -6738,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>139183</v>
+        <v>142831</v>
       </c>
       <c r="N70" s="5" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>2597</v>
+        <v>2642</v>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T12:02:00</t>
+          <t>2026-10-09T14:30:00</t>
         </is>
       </c>
       <c r="J72" s="5" t="n">
@@ -6914,7 +6914,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>67024</v>
+        <v>67214</v>
       </c>
       <c r="N72" s="5" t="n">
         <v>0</v>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Balance of payments: Personal remittances - Annual </t>
+          <t>Personal remittances: receipts and payments, annual</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>67024</v>
+        <v>67214</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
@@ -14893,11 +14893,11 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>From 2012 to 2025</t>
+          <t>From 2012 to 2024</t>
         </is>
       </c>
       <c r="F114" s="5" t="n">
-        <v>906006</v>
+        <v>911427</v>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
@@ -14939,11 +14939,11 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>From 2015 to 2024</t>
+          <t>From 2012 to 2024</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
-        <v>139183</v>
+        <v>142831</v>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
